--- a/BY_Trans.xlsx
+++ b/BY_Trans.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30203"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\KiNESYS_BatteryCircularity\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\KiNESYS_BattCircularity-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95F37B8A-634E-4E6B-AD67-EAD62C95364F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11F8CF1B-DC4F-4277-9E3F-D3AF43A33330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Elec" sheetId="22" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="135">
   <si>
     <t>~md-v_s:</t>
   </si>
@@ -491,7 +491,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -806,6 +806,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8" applyFont="1"/>
   </cellXfs>
   <cellStyles count="12">
+    <cellStyle name="Good" xfId="5" builtinId="26"/>
+    <cellStyle name="Input" xfId="6" builtinId="20"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 10" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Normal 2 2" xfId="4" xr:uid="{1226D20D-DD5A-46E6-8986-2C43794EB266}"/>
@@ -814,10 +817,7 @@
     <cellStyle name="Normal 5" xfId="9" xr:uid="{AF616BAE-5479-4CFB-BBF6-F1DA6C91F59D}"/>
     <cellStyle name="Normal 6" xfId="11" xr:uid="{706D549B-A868-4CC9-AB1C-5821BBB7BE1A}"/>
     <cellStyle name="Normale_Scen_UC_IND-StrucConst" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="好" xfId="5" builtinId="26"/>
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="注释" xfId="10" builtinId="10"/>
-    <cellStyle name="输入" xfId="6" builtinId="20"/>
+    <cellStyle name="Note" xfId="10" builtinId="10"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -835,7 +835,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="zh-CN"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4160,20 +4160,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801E4010-C144-4149-95F4-80A0F3B7A676}">
   <dimension ref="A1:J30"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.73046875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.1328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -4181,12 +4181,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>3</v>
       </c>
@@ -4215,10 +4215,13 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>12</v>
       </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
       <c r="E5" t="s">
         <v>13</v>
       </c>
@@ -4232,7 +4235,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>15</v>
       </c>
@@ -4246,7 +4249,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>16</v>
       </c>
@@ -4263,7 +4266,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>17</v>
       </c>
@@ -4286,7 +4289,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>17</v>
       </c>
@@ -4309,7 +4312,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>17</v>
       </c>
@@ -4333,7 +4336,7 @@
         <v>-ELCHYD,-ELCBIO,-ELCWAS,-ELCSPV,-ELCWIN</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>22</v>
       </c>
@@ -4344,12 +4347,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>3</v>
       </c>
@@ -4375,7 +4378,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>24</v>
       </c>
@@ -4386,7 +4389,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="2:10">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>24</v>
       </c>
@@ -4397,12 +4400,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="2:10">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="2:10">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>3</v>
       </c>
@@ -4431,7 +4434,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="2:10">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>27</v>
       </c>
@@ -4448,7 +4451,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="2:10">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>27</v>
       </c>
@@ -4465,7 +4468,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="2:10">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>27</v>
       </c>
@@ -4482,7 +4485,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="2:10">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>34</v>
       </c>
@@ -4502,20 +4505,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13D5AD98-417C-4AC9-A358-3DC2CA78B755}">
   <dimension ref="B1:O41"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.86328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.59765625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.1328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.3984375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.265625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15">
+    <row r="1" spans="2:15" x14ac:dyDescent="0.35">
       <c r="J1" s="20" t="s">
         <v>36</v>
       </c>
@@ -4523,13 +4526,13 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="2:15">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.35">
       <c r="J2" s="1">
         <f>AVERAGE(J6:J25)</f>
         <v>0.59355138297991616</v>
       </c>
     </row>
-    <row r="4" spans="2:15">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>38</v>
       </c>
@@ -4540,7 +4543,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="2:15">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>40</v>
       </c>
@@ -4578,7 +4581,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="2:15">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>16</v>
       </c>
@@ -4619,7 +4622,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="2:15">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>16</v>
       </c>
@@ -4649,7 +4652,7 @@
         <v>0.92543928353195037</v>
       </c>
     </row>
-    <row r="8" spans="2:15">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>16</v>
       </c>
@@ -4679,7 +4682,7 @@
         <v>0.91012836450520007</v>
       </c>
     </row>
-    <row r="9" spans="2:15">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>16</v>
       </c>
@@ -4709,7 +4712,7 @@
         <v>0.89186179542568333</v>
       </c>
     </row>
-    <row r="10" spans="2:15">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>16</v>
       </c>
@@ -4739,7 +4742,7 @@
         <v>0.87015557311559599</v>
       </c>
     </row>
-    <row r="11" spans="2:15">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>16</v>
       </c>
@@ -4769,7 +4772,7 @@
         <v>0.84448643429821824</v>
       </c>
     </row>
-    <row r="12" spans="2:15">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>16</v>
       </c>
@@ -4799,7 +4802,7 @@
         <v>0.81430870620488494</v>
       </c>
     </row>
-    <row r="13" spans="2:15">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>16</v>
       </c>
@@ -4829,7 +4832,7 @@
         <v>0.77908286056025622</v>
       </c>
     </row>
-    <row r="14" spans="2:15">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>16</v>
       </c>
@@ -4859,7 +4862,7 @@
         <v>0.73831952387107802</v>
       </c>
     </row>
-    <row r="15" spans="2:15">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>16</v>
       </c>
@@ -4889,7 +4892,7 @@
         <v>0.69164258360715825</v>
       </c>
     </row>
-    <row r="16" spans="2:15">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>16</v>
       </c>
@@ -4919,7 +4922,7 @@
         <v>0.63887380360138246</v>
       </c>
     </row>
-    <row r="17" spans="2:10">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>16</v>
       </c>
@@ -4949,7 +4952,7 @@
         <v>0.58013822356972422</v>
       </c>
     </row>
-    <row r="18" spans="2:10">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>16</v>
       </c>
@@ -4979,7 +4982,7 @@
         <v>0.51598362885532811</v>
       </c>
     </row>
-    <row r="19" spans="2:10">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>16</v>
       </c>
@@ -5009,7 +5012,7 @@
         <v>0.44749780699687264</v>
       </c>
     </row>
-    <row r="20" spans="2:10">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>16</v>
       </c>
@@ -5039,7 +5042,7 @@
         <v>0.37639440585896222</v>
       </c>
     </row>
-    <row r="21" spans="2:10">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>16</v>
       </c>
@@ -5069,7 +5072,7 @@
         <v>0.30502449527464032</v>
       </c>
     </row>
-    <row r="22" spans="2:10">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>16</v>
       </c>
@@ -5099,7 +5102,7 @@
         <v>0.23626275789890977</v>
       </c>
     </row>
-    <row r="23" spans="2:10">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>16</v>
       </c>
@@ -5129,7 +5132,7 @@
         <v>0.17322545586628948</v>
       </c>
     </row>
-    <row r="24" spans="2:10">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>16</v>
       </c>
@@ -5159,7 +5162,7 @@
         <v>0.11881473880556002</v>
       </c>
     </row>
-    <row r="25" spans="2:10">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
         <v>16</v>
       </c>
@@ -5189,7 +5192,7 @@
         <v>7.515638719166616E-2</v>
       </c>
     </row>
-    <row r="26" spans="2:10">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.35">
       <c r="G26" t="s">
         <v>48</v>
       </c>
@@ -5205,7 +5208,7 @@
         <v>4.3089488779698863E-2</v>
       </c>
     </row>
-    <row r="27" spans="2:10">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.35">
       <c r="G27" t="s">
         <v>48</v>
       </c>
@@ -5221,7 +5224,7 @@
         <v>2.192601488061072E-2</v>
       </c>
     </row>
-    <row r="28" spans="2:10">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.35">
       <c r="G28" t="s">
         <v>48</v>
       </c>
@@ -5237,7 +5240,7 @@
         <v>9.6531612512389987E-3</v>
       </c>
     </row>
-    <row r="29" spans="2:10">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.35">
       <c r="G29" t="s">
         <v>48</v>
       </c>
@@ -5252,7 +5255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:10">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.35">
       <c r="G30" t="s">
         <v>48</v>
       </c>
@@ -5267,7 +5270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:10">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.35">
       <c r="G31" t="s">
         <v>48</v>
       </c>
@@ -5282,7 +5285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:10">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.35">
       <c r="G32" t="s">
         <v>48</v>
       </c>
@@ -5297,7 +5300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="7:10">
+    <row r="33" spans="7:10" x14ac:dyDescent="0.35">
       <c r="G33" t="s">
         <v>48</v>
       </c>
@@ -5312,7 +5315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="7:10">
+    <row r="34" spans="7:10" x14ac:dyDescent="0.35">
       <c r="G34" t="s">
         <v>48</v>
       </c>
@@ -5327,7 +5330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="7:10">
+    <row r="35" spans="7:10" x14ac:dyDescent="0.35">
       <c r="G35" t="s">
         <v>48</v>
       </c>
@@ -5342,7 +5345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="7:10">
+    <row r="36" spans="7:10" x14ac:dyDescent="0.35">
       <c r="G36" t="s">
         <v>48</v>
       </c>
@@ -5357,7 +5360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="7:10">
+    <row r="37" spans="7:10" x14ac:dyDescent="0.35">
       <c r="G37" t="s">
         <v>48</v>
       </c>
@@ -5372,7 +5375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="7:10">
+    <row r="38" spans="7:10" x14ac:dyDescent="0.35">
       <c r="G38" t="s">
         <v>48</v>
       </c>
@@ -5387,7 +5390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="7:10">
+    <row r="39" spans="7:10" x14ac:dyDescent="0.35">
       <c r="G39" t="s">
         <v>48</v>
       </c>
@@ -5402,7 +5405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="7:10">
+    <row r="40" spans="7:10" x14ac:dyDescent="0.35">
       <c r="G40" t="s">
         <v>48</v>
       </c>
@@ -5417,7 +5420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="7:10">
+    <row r="41" spans="7:10" x14ac:dyDescent="0.35">
       <c r="G41" t="s">
         <v>48</v>
       </c>
@@ -5440,12 +5443,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E7CDDB-DFE3-45FD-BAA0-32A9B03D9D40}">
   <dimension ref="A4:K57"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="3"/>
+    <col min="1" max="16384" width="9.1328125" style="3"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B4" s="4" t="s">
         <v>49</v>
       </c>
@@ -5463,7 +5466,7 @@
       </c>
       <c r="G4" s="5"/>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B5" s="4" t="s">
         <v>50</v>
       </c>
@@ -5481,7 +5484,7 @@
       </c>
       <c r="G5" s="5"/>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B7" s="6" t="s">
         <v>51</v>
       </c>
@@ -5505,7 +5508,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" s="3">
         <v>1</v>
       </c>
@@ -5530,7 +5533,7 @@
       </c>
       <c r="G8" s="10"/>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" s="3">
         <v>2</v>
       </c>
@@ -5555,7 +5558,7 @@
       </c>
       <c r="G9" s="10"/>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" s="3">
         <v>3</v>
       </c>
@@ -5580,7 +5583,7 @@
       </c>
       <c r="G10" s="10"/>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" s="3">
         <v>4</v>
       </c>
@@ -5605,7 +5608,7 @@
       </c>
       <c r="G11" s="10"/>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" s="3">
         <v>5</v>
       </c>
@@ -5630,7 +5633,7 @@
       </c>
       <c r="G12" s="10"/>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" s="3">
         <v>6</v>
       </c>
@@ -5655,7 +5658,7 @@
       </c>
       <c r="G13" s="10"/>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" s="3">
         <v>7</v>
       </c>
@@ -5680,7 +5683,7 @@
       </c>
       <c r="G14" s="10"/>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" s="3">
         <v>8</v>
       </c>
@@ -5705,7 +5708,7 @@
       </c>
       <c r="G15" s="10"/>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" s="3">
         <v>9</v>
       </c>
@@ -5730,7 +5733,7 @@
       </c>
       <c r="G16" s="10"/>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" s="3">
         <v>10</v>
       </c>
@@ -5755,7 +5758,7 @@
       </c>
       <c r="G17" s="10"/>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="3">
         <v>11</v>
       </c>
@@ -5780,7 +5783,7 @@
       </c>
       <c r="G18" s="10"/>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" s="3">
         <v>12</v>
       </c>
@@ -5805,7 +5808,7 @@
       </c>
       <c r="G19" s="10"/>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" s="3">
         <v>13</v>
       </c>
@@ -5830,7 +5833,7 @@
       </c>
       <c r="G20" s="10"/>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" s="3">
         <v>14</v>
       </c>
@@ -5855,7 +5858,7 @@
       </c>
       <c r="G21" s="10"/>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" s="3">
         <v>15</v>
       </c>
@@ -5880,7 +5883,7 @@
       </c>
       <c r="G22" s="10"/>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" s="3">
         <v>16</v>
       </c>
@@ -5905,7 +5908,7 @@
       </c>
       <c r="G23" s="10"/>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" s="3">
         <v>17</v>
       </c>
@@ -5930,7 +5933,7 @@
       </c>
       <c r="G24" s="10"/>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" s="3">
         <v>18</v>
       </c>
@@ -5955,7 +5958,7 @@
       </c>
       <c r="G25" s="10"/>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" s="3">
         <v>19</v>
       </c>
@@ -5980,7 +5983,7 @@
       </c>
       <c r="G26" s="10"/>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" s="3">
         <v>20</v>
       </c>
@@ -6005,7 +6008,7 @@
       </c>
       <c r="G27" s="10"/>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" s="3">
         <v>21</v>
       </c>
@@ -6030,7 +6033,7 @@
       </c>
       <c r="G28" s="10"/>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" s="3">
         <v>22</v>
       </c>
@@ -6055,7 +6058,7 @@
       </c>
       <c r="G29" s="10"/>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" s="3">
         <v>23</v>
       </c>
@@ -6080,7 +6083,7 @@
       </c>
       <c r="G30" s="10"/>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" s="3">
         <v>24</v>
       </c>
@@ -6105,7 +6108,7 @@
       </c>
       <c r="G31" s="10"/>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" s="3">
         <v>25</v>
       </c>
@@ -6130,7 +6133,7 @@
       </c>
       <c r="G32" s="10"/>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A33" s="3">
         <v>26</v>
       </c>
@@ -6155,7 +6158,7 @@
       </c>
       <c r="G33" s="10"/>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A34" s="3">
         <v>27</v>
       </c>
@@ -6180,7 +6183,7 @@
       </c>
       <c r="G34" s="10"/>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A35" s="3">
         <v>28</v>
       </c>
@@ -6205,7 +6208,7 @@
       </c>
       <c r="G35" s="10"/>
     </row>
-    <row r="36" spans="1:11" ht="15.75" thickBot="1">
+    <row r="36" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A36" s="3">
         <v>29</v>
       </c>
@@ -6230,7 +6233,7 @@
       </c>
       <c r="G36" s="10"/>
     </row>
-    <row r="37" spans="1:11" ht="15.75">
+    <row r="37" spans="1:11" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A37" s="3">
         <v>30</v>
       </c>
@@ -6262,7 +6265,7 @@
       </c>
       <c r="K37" s="13"/>
     </row>
-    <row r="38" spans="1:11" ht="16.5" thickBot="1">
+    <row r="38" spans="1:11" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="3">
         <v>31</v>
       </c>
@@ -6294,7 +6297,7 @@
       </c>
       <c r="K38" s="16"/>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A39" s="3">
         <v>32</v>
       </c>
@@ -6319,7 +6322,7 @@
       </c>
       <c r="G39" s="10"/>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A40" s="3">
         <v>33</v>
       </c>
@@ -6344,7 +6347,7 @@
       </c>
       <c r="G40" s="10"/>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A41" s="3">
         <v>34</v>
       </c>
@@ -6369,7 +6372,7 @@
       </c>
       <c r="G41" s="10"/>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A42" s="3">
         <v>35</v>
       </c>
@@ -6394,7 +6397,7 @@
       </c>
       <c r="G42" s="10"/>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A43" s="3">
         <v>36</v>
       </c>
@@ -6419,7 +6422,7 @@
       </c>
       <c r="G43" s="10"/>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A44" s="3">
         <v>37</v>
       </c>
@@ -6444,7 +6447,7 @@
       </c>
       <c r="G44" s="10"/>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A45" s="3">
         <v>38</v>
       </c>
@@ -6469,7 +6472,7 @@
       </c>
       <c r="G45" s="10"/>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A46" s="3">
         <v>39</v>
       </c>
@@ -6494,7 +6497,7 @@
       </c>
       <c r="G46" s="10"/>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A47" s="3">
         <v>40</v>
       </c>
@@ -6519,7 +6522,7 @@
       </c>
       <c r="G47" s="10"/>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A48" s="3">
         <v>41</v>
       </c>
@@ -6544,7 +6547,7 @@
       </c>
       <c r="G48" s="10"/>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A49" s="3">
         <v>42</v>
       </c>
@@ -6569,7 +6572,7 @@
       </c>
       <c r="G49" s="10"/>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A50" s="3">
         <v>43</v>
       </c>
@@ -6594,7 +6597,7 @@
       </c>
       <c r="G50" s="10"/>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A51" s="3">
         <v>44</v>
       </c>
@@ -6619,7 +6622,7 @@
       </c>
       <c r="G51" s="10"/>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A52" s="3">
         <v>45</v>
       </c>
@@ -6644,7 +6647,7 @@
       </c>
       <c r="G52" s="10"/>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A53" s="3">
         <v>46</v>
       </c>
@@ -6669,7 +6672,7 @@
       </c>
       <c r="G53" s="10"/>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A54" s="3">
         <v>47</v>
       </c>
@@ -6694,7 +6697,7 @@
       </c>
       <c r="G54" s="10"/>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A55" s="3">
         <v>48</v>
       </c>
@@ -6719,7 +6722,7 @@
       </c>
       <c r="G55" s="10"/>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A56" s="3">
         <v>49</v>
       </c>
@@ -6744,7 +6747,7 @@
       </c>
       <c r="G56" s="10"/>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A57" s="3">
         <v>50</v>
       </c>
@@ -6778,21 +6781,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFD65BF2-23B8-46EE-9250-1196FF234EA1}">
   <dimension ref="B3:I31"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="20.42578125" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.3984375" customWidth="1"/>
+    <col min="3" max="3" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.86328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.73046875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:9">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="2:9">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>40</v>
       </c>
@@ -6806,7 +6809,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="2:9">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>56</v>
       </c>
@@ -6820,12 +6823,12 @@
         <v>99999</v>
       </c>
     </row>
-    <row r="8" spans="2:9">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="2:9">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>42</v>
       </c>
@@ -6836,7 +6839,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="2:9">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B10">
         <v>2100</v>
       </c>
@@ -6847,20 +6850,20 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="2:9" ht="15">
+    <row r="14" spans="2:9" ht="14.25" x14ac:dyDescent="0.45">
       <c r="C14" s="26"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
     </row>
-    <row r="15" spans="2:9" ht="15">
+    <row r="15" spans="2:9" ht="14.25" x14ac:dyDescent="0.45">
       <c r="C15" s="26"/>
       <c r="D15" s="26"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="I15" s="17"/>
     </row>
-    <row r="16" spans="2:9" ht="15">
+    <row r="16" spans="2:9" ht="14.25" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
         <v>62</v>
       </c>
@@ -6870,7 +6873,7 @@
       <c r="F16" s="3"/>
       <c r="I16" s="17"/>
     </row>
-    <row r="17" spans="2:8">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>55</v>
       </c>
@@ -6881,7 +6884,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="2:8">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>65</v>
       </c>
@@ -6892,7 +6895,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>68</v>
       </c>
@@ -6903,12 +6906,12 @@
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>40</v>
       </c>
@@ -6922,7 +6925,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="2:8">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>70</v>
       </c>
@@ -6936,7 +6939,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="25" spans="2:8">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
         <v>70</v>
       </c>
@@ -6951,12 +6954,12 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>40</v>
       </c>
@@ -6973,7 +6976,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B31" t="s">
         <v>73</v>
       </c>
@@ -7002,31 +7005,31 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B305A000-B663-4CCB-B7CD-D7C7D23A015C}">
   <dimension ref="A1:L18"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="2" width="9.140625" style="18"/>
+    <col min="1" max="2" width="9.1328125" style="18"/>
     <col min="3" max="3" width="26" style="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.85546875" style="18" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.7109375" style="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" style="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.86328125" style="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.73046875" style="18" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.265625" style="18" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="26" style="18" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.5703125" style="18" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" style="18"/>
-    <col min="10" max="10" width="6.85546875" style="18" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="18"/>
+    <col min="8" max="8" width="9.59765625" style="18" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.1328125" style="18"/>
+    <col min="10" max="10" width="6.86328125" style="18" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.1328125" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" s="21" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="C3" s="18" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="C4" s="18" t="s">
         <v>40</v>
       </c>
@@ -7055,7 +7058,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="C5" s="18" t="s">
         <v>81</v>
       </c>
@@ -7074,7 +7077,7 @@
         <v>ELC</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="C6" s="18" t="s">
         <v>84</v>
       </c>
@@ -7092,7 +7095,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="C7" s="18" t="s">
         <v>84</v>
       </c>
@@ -7113,7 +7116,7 @@
         <v>ELC</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="C8" s="18" t="s">
         <v>84</v>
       </c>
@@ -7134,7 +7137,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="C9" s="18" t="s">
         <v>89</v>
       </c>
@@ -7145,7 +7148,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="C10" s="18" t="s">
         <v>90</v>
       </c>
@@ -7167,7 +7170,7 @@
         <v>ELC</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="C11" s="18" t="s">
         <v>81</v>
       </c>
@@ -7189,7 +7192,7 @@
         <v>INDELC</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="C12" s="18" t="s">
         <v>84</v>
       </c>
@@ -7213,7 +7216,7 @@
         <v>INDELC</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="C13" s="18" t="s">
         <v>90</v>
       </c>
@@ -7239,12 +7242,12 @@
         <v>INDELC</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="C16" s="18" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="3:5">
+    <row r="17" spans="3:5" x14ac:dyDescent="0.45">
       <c r="C17" s="18" t="s">
         <v>55</v>
       </c>
@@ -7255,7 +7258,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="3:5">
+    <row r="18" spans="3:5" x14ac:dyDescent="0.45">
       <c r="C18" s="18" t="str">
         <f>G10</f>
         <v>E?_HYD_PS-HY*,E?_ELC-HY_PS*</v>
@@ -7276,18 +7279,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A2C5748-51A3-47F0-B1D9-5AA712A09B00}">
   <dimension ref="C3:M39"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="9.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:13">
+    <row r="3" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C3" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="4" spans="3:13" ht="15.75">
+    <row r="4" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C4" s="24" t="s">
         <v>97</v>
       </c>
@@ -7322,7 +7325,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="5" spans="3:13" ht="15.75">
+    <row r="5" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C5" s="24" t="s">
         <v>99</v>
       </c>
@@ -7357,7 +7360,7 @@
         <v>3795.927703803337</v>
       </c>
     </row>
-    <row r="6" spans="3:13" ht="15.75">
+    <row r="6" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C6" s="24" t="s">
         <v>101</v>
       </c>
@@ -7392,7 +7395,7 @@
         <v>3278.0224960696114</v>
       </c>
     </row>
-    <row r="7" spans="3:13" ht="15.75">
+    <row r="7" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C7" s="24" t="s">
         <v>102</v>
       </c>
@@ -7427,7 +7430,7 @@
         <v>1316.3397571060802</v>
       </c>
     </row>
-    <row r="8" spans="3:13" ht="15.75">
+    <row r="8" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C8" s="24" t="s">
         <v>103</v>
       </c>
@@ -7462,7 +7465,7 @@
         <v>282.41626856114499</v>
       </c>
     </row>
-    <row r="9" spans="3:13" ht="15.75">
+    <row r="9" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C9" s="24" t="s">
         <v>104</v>
       </c>
@@ -7497,7 +7500,7 @@
         <v>115.39242587002472</v>
       </c>
     </row>
-    <row r="10" spans="3:13" ht="15.75">
+    <row r="10" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C10" s="24" t="s">
         <v>105</v>
       </c>
@@ -7532,7 +7535,7 @@
         <v>917.8622085991841</v>
       </c>
     </row>
-    <row r="11" spans="3:13" ht="15.75">
+    <row r="11" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C11" s="24" t="s">
         <v>106</v>
       </c>
@@ -7567,7 +7570,7 @@
         <v>4246.9743952864465</v>
       </c>
     </row>
-    <row r="12" spans="3:13" ht="15.75">
+    <row r="12" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C12" s="24" t="s">
         <v>107</v>
       </c>
@@ -7602,7 +7605,7 @@
         <v>29909.149581400656</v>
       </c>
     </row>
-    <row r="13" spans="3:13" ht="15.75">
+    <row r="13" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C13" s="24" t="s">
         <v>108</v>
       </c>
@@ -7637,7 +7640,7 @@
         <v>145.79172464431582</v>
       </c>
     </row>
-    <row r="14" spans="3:13" ht="15.75">
+    <row r="14" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C14" s="24" t="s">
         <v>109</v>
       </c>
@@ -7672,7 +7675,7 @@
         <v>402.87369420741277</v>
       </c>
     </row>
-    <row r="15" spans="3:13" ht="15.75">
+    <row r="15" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C15" s="24" t="s">
         <v>110</v>
       </c>
@@ -7707,7 +7710,7 @@
         <v>1964.2988303777586</v>
       </c>
     </row>
-    <row r="16" spans="3:13" ht="15.75">
+    <row r="16" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C16" s="24" t="s">
         <v>111</v>
       </c>
@@ -7742,7 +7745,7 @@
         <v>2203.626193933072</v>
       </c>
     </row>
-    <row r="17" spans="3:13" ht="15.75">
+    <row r="17" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C17" s="24" t="s">
         <v>112</v>
       </c>
@@ -7777,7 +7780,7 @@
         <v>292.16744740905256</v>
       </c>
     </row>
-    <row r="18" spans="3:13" ht="15.75">
+    <row r="18" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C18" s="24" t="s">
         <v>113</v>
       </c>
@@ -7812,7 +7815,7 @@
         <v>601.32479506483764</v>
       </c>
     </row>
-    <row r="19" spans="3:13" ht="15.75">
+    <row r="19" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C19" s="24" t="s">
         <v>114</v>
       </c>
@@ -7847,7 +7850,7 @@
         <v>112.218052947304</v>
       </c>
     </row>
-    <row r="20" spans="3:13" ht="15.75">
+    <row r="20" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C20" s="24" t="s">
         <v>115</v>
       </c>
@@ -7882,7 +7885,7 @@
         <v>18404.055717985004</v>
       </c>
     </row>
-    <row r="21" spans="3:13" ht="15.75">
+    <row r="21" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C21" s="24" t="s">
         <v>116</v>
       </c>
@@ -7917,7 +7920,7 @@
         <v>168.94452047206218</v>
       </c>
     </row>
-    <row r="22" spans="3:13" ht="15.75">
+    <row r="22" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C22" s="24" t="s">
         <v>117</v>
       </c>
@@ -7952,7 +7955,7 @@
         <v>1249.221215374082</v>
       </c>
     </row>
-    <row r="23" spans="3:13" ht="15.75">
+    <row r="23" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C23" s="24" t="s">
         <v>118</v>
       </c>
@@ -7987,7 +7990,7 @@
         <v>4027.394544797934</v>
       </c>
     </row>
-    <row r="24" spans="3:13" ht="15.75">
+    <row r="24" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C24" s="24" t="s">
         <v>119</v>
       </c>
@@ -8022,7 +8025,7 @@
         <v>4820.8975175147025</v>
       </c>
     </row>
-    <row r="25" spans="3:13" ht="15.75">
+    <row r="25" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C25" s="24" t="s">
         <v>120</v>
       </c>
@@ -8057,7 +8060,7 @@
         <v>6304.3460358293869</v>
       </c>
     </row>
-    <row r="26" spans="3:13" ht="15.75">
+    <row r="26" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C26" s="24" t="s">
         <v>121</v>
       </c>
@@ -8092,7 +8095,7 @@
         <v>22450.162330151325</v>
       </c>
     </row>
-    <row r="27" spans="3:13" ht="15.75">
+    <row r="27" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C27" s="24" t="s">
         <v>122</v>
       </c>
@@ -8127,7 +8130,7 @@
         <v>582.17574012868954</v>
       </c>
     </row>
-    <row r="28" spans="3:13" ht="15.75">
+    <row r="28" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C28" s="24" t="s">
         <v>123</v>
       </c>
@@ -8162,7 +8165,7 @@
         <v>789.49197589240487</v>
       </c>
     </row>
-    <row r="29" spans="3:13" ht="15.75">
+    <row r="29" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C29" s="24" t="s">
         <v>124</v>
       </c>
@@ -8197,7 +8200,7 @@
         <v>23441.765290077503</v>
       </c>
     </row>
-    <row r="30" spans="3:13" ht="15.75">
+    <row r="30" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C30" s="24" t="s">
         <v>125</v>
       </c>
@@ -8232,7 +8235,7 @@
         <v>3875.8955806692529</v>
       </c>
     </row>
-    <row r="31" spans="3:13" ht="15.75">
+    <row r="31" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C31" s="24" t="s">
         <v>126</v>
       </c>
@@ -8267,7 +8270,7 @@
         <v>1753.5396742825753</v>
       </c>
     </row>
-    <row r="32" spans="3:13" ht="15.75">
+    <row r="32" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C32" s="24" t="s">
         <v>127</v>
       </c>
@@ -8302,7 +8305,7 @@
         <v>1295.8482577436666</v>
       </c>
     </row>
-    <row r="33" spans="3:13" ht="15.75">
+    <row r="33" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C33" s="24" t="s">
         <v>128</v>
       </c>
@@ -8337,7 +8340,7 @@
         <v>1423.2936999667922</v>
       </c>
     </row>
-    <row r="34" spans="3:13" ht="15.75">
+    <row r="34" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C34" s="24" t="s">
         <v>129</v>
       </c>
@@ -8372,7 +8375,7 @@
         <v>1111.7695348668212</v>
       </c>
     </row>
-    <row r="35" spans="3:13" ht="15.75">
+    <row r="35" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C35" s="24" t="s">
         <v>130</v>
       </c>
@@ -8407,7 +8410,7 @@
         <v>239.79020951356867</v>
       </c>
     </row>
-    <row r="36" spans="3:13" ht="15.75">
+    <row r="36" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C36" s="24" t="s">
         <v>131</v>
       </c>
@@ -8442,7 +8445,7 @@
         <v>1497.0814520140805</v>
       </c>
     </row>
-    <row r="37" spans="3:13" ht="15.75">
+    <row r="37" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C37" s="24" t="s">
         <v>132</v>
       </c>
@@ -8477,7 +8480,7 @@
         <v>1567.335319626412</v>
       </c>
     </row>
-    <row r="38" spans="3:13" ht="15.75">
+    <row r="38" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C38" s="24" t="s">
         <v>133</v>
       </c>
@@ -8512,7 +8515,7 @@
         <v>893.52071666851668</v>
       </c>
     </row>
-    <row r="39" spans="3:13" ht="15.75">
+    <row r="39" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C39" s="24" t="s">
         <v>134</v>
       </c>

--- a/BY_Trans.xlsx
+++ b/BY_Trans.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\KiNESYS_BattCircularity-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11F8CF1B-DC4F-4277-9E3F-D3AF43A33330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC45DBF7-6061-412E-B4B5-6495937DCE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -120,9 +120,6 @@
     <t>FX</t>
   </si>
   <si>
-    <t>ELE,CHP,STS</t>
-  </si>
-  <si>
     <t>PRC_CAPACT</t>
   </si>
   <si>
@@ -481,6 +478,9 @@
   </si>
   <si>
     <t>WestBalkans</t>
+  </si>
+  <si>
+    <t>ELE,CHP,STS,STG</t>
   </si>
 </sst>
 </file>
@@ -4220,7 +4220,7 @@
         <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E5" t="s">
         <v>13</v>
@@ -4232,29 +4232,29 @@
         <v>2</v>
       </c>
       <c r="H5" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
         <v>15</v>
-      </c>
-      <c r="D6" t="s">
-        <v>16</v>
       </c>
       <c r="G6" s="1">
         <v>31.536000000000001</v>
       </c>
       <c r="H6" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -4263,18 +4263,18 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s">
         <v>17</v>
-      </c>
-      <c r="D8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" t="s">
-        <v>18</v>
       </c>
       <c r="F8">
         <v>2025</v>
@@ -4283,21 +4283,21 @@
         <v>0</v>
       </c>
       <c r="H8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" s="23" t="s">
         <v>19</v>
-      </c>
-      <c r="J8" s="23" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
         <v>17</v>
-      </c>
-      <c r="D9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" t="s">
-        <v>18</v>
       </c>
       <c r="F9">
         <v>2030</v>
@@ -4306,21 +4306,21 @@
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" t="s">
         <v>17</v>
-      </c>
-      <c r="D10" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" t="s">
-        <v>18</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -4329,7 +4329,7 @@
         <v>4</v>
       </c>
       <c r="H10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J10" t="str">
         <f>J8</f>
@@ -4338,18 +4338,18 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G11">
         <v>1</v>
       </c>
       <c r="H11" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
@@ -4380,24 +4380,24 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G16">
         <v>0.32</v>
       </c>
       <c r="I16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G17">
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.35">
@@ -4436,64 +4436,64 @@
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" t="s">
         <v>27</v>
-      </c>
-      <c r="C27" t="s">
-        <v>28</v>
       </c>
       <c r="G27" s="2">
         <v>2882.65777101602</v>
       </c>
       <c r="H27" t="s">
+        <v>28</v>
+      </c>
+      <c r="J27" t="s">
         <v>29</v>
-      </c>
-      <c r="J27" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" t="s">
         <v>27</v>
-      </c>
-      <c r="C28" t="s">
-        <v>28</v>
       </c>
       <c r="G28" s="2">
         <v>893.70913654846424</v>
       </c>
       <c r="H28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" t="s">
         <v>27</v>
-      </c>
-      <c r="C29" t="s">
-        <v>28</v>
       </c>
       <c r="G29" s="2">
         <v>3000</v>
       </c>
       <c r="H29" t="s">
+        <v>31</v>
+      </c>
+      <c r="J29" t="s">
         <v>32</v>
-      </c>
-      <c r="J29" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G30">
         <v>30</v>
       </c>
       <c r="J30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -4520,10 +4520,10 @@
   <sheetData>
     <row r="1" spans="2:15" x14ac:dyDescent="0.35">
       <c r="J1" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="K1" t="s">
         <v>36</v>
-      </c>
-      <c r="K1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="2" spans="2:15" x14ac:dyDescent="0.35">
@@ -4534,59 +4534,59 @@
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G4" t="s">
         <v>2</v>
       </c>
       <c r="L4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" t="s">
         <v>40</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>41</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>42</v>
       </c>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" t="s">
         <v>43</v>
       </c>
-      <c r="G5" t="s">
+      <c r="I5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L5" t="s">
+        <v>39</v>
+      </c>
+      <c r="M5" t="s">
         <v>40</v>
       </c>
-      <c r="H5" t="s">
+      <c r="N5" t="s">
         <v>44</v>
       </c>
-      <c r="I5" t="s">
+      <c r="O5" t="s">
         <v>45</v>
-      </c>
-      <c r="J5" t="s">
-        <v>46</v>
-      </c>
-      <c r="L5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M5" t="s">
-        <v>41</v>
-      </c>
-      <c r="N5" t="s">
-        <v>45</v>
-      </c>
-      <c r="O5" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D6">
         <v>2019</v>
@@ -4596,7 +4596,7 @@
         <v>*0.0842387052473464</v>
       </c>
       <c r="G6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H6">
         <v>15</v>
@@ -4613,7 +4613,7 @@
         <v>12</v>
       </c>
       <c r="M6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -4624,10 +4624,10 @@
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D7">
         <f>D6-1</f>
@@ -4638,7 +4638,7 @@
         <v>*0.0842387052473464</v>
       </c>
       <c r="G7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H7">
         <v>15</v>
@@ -4654,10 +4654,10 @@
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D8">
         <f t="shared" ref="D8:D25" si="1">D7-1</f>
@@ -4668,7 +4668,7 @@
         <v>*0.0842387052473464</v>
       </c>
       <c r="G8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H8">
         <v>15</v>
@@ -4684,10 +4684,10 @@
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D9">
         <f t="shared" si="1"/>
@@ -4698,7 +4698,7 @@
         <v>*0.0842387052473464</v>
       </c>
       <c r="G9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H9">
         <v>15</v>
@@ -4714,10 +4714,10 @@
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D10">
         <f t="shared" si="1"/>
@@ -4728,7 +4728,7 @@
         <v>*0.0842387052473464</v>
       </c>
       <c r="G10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H10">
         <v>15</v>
@@ -4744,10 +4744,10 @@
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D11">
         <f t="shared" si="1"/>
@@ -4758,7 +4758,7 @@
         <v>*0.0842387052473464</v>
       </c>
       <c r="G11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H11">
         <v>15</v>
@@ -4774,10 +4774,10 @@
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D12">
         <f t="shared" si="1"/>
@@ -4788,7 +4788,7 @@
         <v>*0.0842387052473464</v>
       </c>
       <c r="G12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H12">
         <v>15</v>
@@ -4804,10 +4804,10 @@
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D13">
         <f t="shared" si="1"/>
@@ -4818,7 +4818,7 @@
         <v>*0.0842387052473464</v>
       </c>
       <c r="G13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H13">
         <v>15</v>
@@ -4834,10 +4834,10 @@
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D14">
         <f t="shared" si="1"/>
@@ -4848,7 +4848,7 @@
         <v>*0.0842387052473464</v>
       </c>
       <c r="G14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H14">
         <v>15</v>
@@ -4864,10 +4864,10 @@
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D15">
         <f t="shared" si="1"/>
@@ -4878,7 +4878,7 @@
         <v>*0.0842387052473464</v>
       </c>
       <c r="G15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H15">
         <v>15</v>
@@ -4894,10 +4894,10 @@
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16">
         <f t="shared" si="1"/>
@@ -4908,7 +4908,7 @@
         <v>*0.0842387052473464</v>
       </c>
       <c r="G16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H16">
         <v>15</v>
@@ -4924,10 +4924,10 @@
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D17">
         <f t="shared" si="1"/>
@@ -4938,7 +4938,7 @@
         <v>*0.0842387052473464</v>
       </c>
       <c r="G17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H17">
         <v>15</v>
@@ -4954,10 +4954,10 @@
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D18">
         <f t="shared" si="1"/>
@@ -4968,7 +4968,7 @@
         <v>*0.0842387052473464</v>
       </c>
       <c r="G18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H18">
         <v>15</v>
@@ -4984,10 +4984,10 @@
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D19">
         <f t="shared" si="1"/>
@@ -4998,7 +4998,7 @@
         <v>*0.0842387052473464</v>
       </c>
       <c r="G19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H19">
         <v>15</v>
@@ -5014,10 +5014,10 @@
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D20">
         <f t="shared" si="1"/>
@@ -5028,7 +5028,7 @@
         <v>*0.0842387052473464</v>
       </c>
       <c r="G20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H20">
         <v>15</v>
@@ -5044,10 +5044,10 @@
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D21">
         <f t="shared" si="1"/>
@@ -5058,7 +5058,7 @@
         <v>*0.0842387052473464</v>
       </c>
       <c r="G21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H21">
         <v>15</v>
@@ -5074,10 +5074,10 @@
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D22">
         <f t="shared" si="1"/>
@@ -5088,7 +5088,7 @@
         <v>*0.0842387052473464</v>
       </c>
       <c r="G22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H22">
         <v>15</v>
@@ -5104,10 +5104,10 @@
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D23">
         <f t="shared" si="1"/>
@@ -5118,7 +5118,7 @@
         <v>*0.0842387052473464</v>
       </c>
       <c r="G23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H23">
         <v>15</v>
@@ -5134,10 +5134,10 @@
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C24" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D24">
         <f t="shared" si="1"/>
@@ -5148,7 +5148,7 @@
         <v>*0.0842387052473464</v>
       </c>
       <c r="G24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H24">
         <v>15</v>
@@ -5164,10 +5164,10 @@
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D25">
         <f t="shared" si="1"/>
@@ -5178,7 +5178,7 @@
         <v>*0.0842387052473464</v>
       </c>
       <c r="G25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H25">
         <v>15</v>
@@ -5194,7 +5194,7 @@
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.35">
       <c r="G26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H26">
         <v>15</v>
@@ -5210,7 +5210,7 @@
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.35">
       <c r="G27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H27">
         <v>15</v>
@@ -5226,7 +5226,7 @@
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.35">
       <c r="G28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H28">
         <v>15</v>
@@ -5242,7 +5242,7 @@
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.35">
       <c r="G29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H29">
         <v>15</v>
@@ -5257,7 +5257,7 @@
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.35">
       <c r="G30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H30">
         <v>15</v>
@@ -5272,7 +5272,7 @@
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.35">
       <c r="G31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H31">
         <v>15</v>
@@ -5287,7 +5287,7 @@
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.35">
       <c r="G32" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H32">
         <v>15</v>
@@ -5302,7 +5302,7 @@
     </row>
     <row r="33" spans="7:10" x14ac:dyDescent="0.35">
       <c r="G33" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H33">
         <v>15</v>
@@ -5317,7 +5317,7 @@
     </row>
     <row r="34" spans="7:10" x14ac:dyDescent="0.35">
       <c r="G34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H34">
         <v>15</v>
@@ -5332,7 +5332,7 @@
     </row>
     <row r="35" spans="7:10" x14ac:dyDescent="0.35">
       <c r="G35" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H35">
         <v>15</v>
@@ -5347,7 +5347,7 @@
     </row>
     <row r="36" spans="7:10" x14ac:dyDescent="0.35">
       <c r="G36" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H36">
         <v>15</v>
@@ -5362,7 +5362,7 @@
     </row>
     <row r="37" spans="7:10" x14ac:dyDescent="0.35">
       <c r="G37" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H37">
         <v>15</v>
@@ -5377,7 +5377,7 @@
     </row>
     <row r="38" spans="7:10" x14ac:dyDescent="0.35">
       <c r="G38" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H38">
         <v>15</v>
@@ -5392,7 +5392,7 @@
     </row>
     <row r="39" spans="7:10" x14ac:dyDescent="0.35">
       <c r="G39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H39">
         <v>15</v>
@@ -5407,7 +5407,7 @@
     </row>
     <row r="40" spans="7:10" x14ac:dyDescent="0.35">
       <c r="G40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H40">
         <v>15</v>
@@ -5422,7 +5422,7 @@
     </row>
     <row r="41" spans="7:10" x14ac:dyDescent="0.35">
       <c r="G41" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H41">
         <v>15</v>
@@ -5450,7 +5450,7 @@
   <sheetData>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B4" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C4" s="5">
         <v>0.192</v>
@@ -5468,7 +5468,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B5" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C5" s="5">
         <v>1200</v>
@@ -5486,7 +5486,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B7" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C7" s="6">
         <f t="shared" ref="C7:E7" si="0">SUM(C8:C32)</f>
@@ -5505,7 +5505,7 @@
         <v>15.036067741000499</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
@@ -6261,7 +6261,7 @@
         <v>20</v>
       </c>
       <c r="J37" s="12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K37" s="13"/>
     </row>
@@ -6293,7 +6293,7 @@
         <v>15</v>
       </c>
       <c r="J38" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K38" s="16"/>
     </row>
@@ -6792,32 +6792,32 @@
   <sheetData>
     <row r="3" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" t="s">
         <v>45</v>
-      </c>
-      <c r="D4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C5">
         <v>2018</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E5">
         <v>99999</v>
@@ -6825,18 +6825,18 @@
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
@@ -6844,10 +6844,10 @@
         <v>2100</v>
       </c>
       <c r="C10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" t="s">
         <v>60</v>
-      </c>
-      <c r="D10" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="14" spans="2:9" ht="14.25" x14ac:dyDescent="0.45">
@@ -6865,7 +6865,7 @@
     </row>
     <row r="16" spans="2:9" ht="14.25" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C16" s="26"/>
       <c r="D16" s="26"/>
@@ -6875,35 +6875,35 @@
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C17" t="s">
+        <v>62</v>
+      </c>
+      <c r="D17" t="s">
         <v>63</v>
-      </c>
-      <c r="D17" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" t="s">
         <v>65</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>66</v>
-      </c>
-      <c r="D18" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" t="s">
         <v>68</v>
-      </c>
-      <c r="C19" t="s">
-        <v>66</v>
-      </c>
-      <c r="D19" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.35">
@@ -6913,27 +6913,27 @@
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C23" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D23" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" t="s">
         <v>70</v>
-      </c>
-      <c r="C24" t="s">
-        <v>65</v>
-      </c>
-      <c r="D24" t="s">
-        <v>71</v>
       </c>
       <c r="E24">
         <v>2150</v>
@@ -6941,14 +6941,14 @@
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C25" t="str">
         <f>B19</f>
         <v>SUP_OilSupply</v>
       </c>
       <c r="D25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E25">
         <v>2150</v>
@@ -6956,32 +6956,32 @@
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C30" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D30" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30" t="s">
+        <v>41</v>
+      </c>
+      <c r="F30" t="s">
         <v>45</v>
-      </c>
-      <c r="E30" t="s">
-        <v>42</v>
-      </c>
-      <c r="F30" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B31" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" t="s">
         <v>73</v>
-      </c>
-      <c r="C31" t="s">
-        <v>74</v>
       </c>
       <c r="D31">
         <v>2020</v>
@@ -6990,10 +6990,10 @@
         <v>2019</v>
       </c>
       <c r="F31" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H31" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -7021,7 +7021,7 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.45">
@@ -7031,46 +7031,46 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="C4" s="18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E4" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="G4" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="H4" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="I4" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="F4" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="G4" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="H4" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="I4" s="27" t="s">
+      <c r="J4" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="J4" s="27" t="s">
+      <c r="L4" s="18" t="s">
         <v>79</v>
-      </c>
-      <c r="L4" s="18" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="C5" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" s="18" t="s">
         <v>81</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>82</v>
       </c>
       <c r="F5" s="19">
         <f>6/24</f>
         <v>0.25</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J5" s="18" t="str">
         <f>D5</f>
@@ -7079,37 +7079,37 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="C6" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="D6" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="E6" s="18" t="s">
         <v>85</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>86</v>
       </c>
       <c r="F6" s="19">
         <f>6/24/F9</f>
         <v>0.3125</v>
       </c>
       <c r="G6" s="27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="C7" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F7" s="19">
         <v>1</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J7" s="18" t="str">
         <f>D7</f>
@@ -7118,52 +7118,52 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="C8" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F8" s="19">
         <f>6/9</f>
         <v>0.66666666666666663</v>
       </c>
       <c r="G8" s="27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L8" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="C9" s="18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F9" s="19">
         <v>0.8</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="C10" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D10" s="18" t="s">
         <v>90</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>91</v>
       </c>
       <c r="F10" s="18">
         <f>1/F9</f>
         <v>1.25</v>
       </c>
       <c r="G10" s="27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H10" s="18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J10" s="18" t="str">
         <f>H10</f>
@@ -7172,20 +7172,20 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="C11" s="18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F11" s="19">
         <f>6/24</f>
         <v>0.25</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I11" s="27" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J11" s="18" t="str">
         <f>D11</f>
@@ -7194,22 +7194,22 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="C12" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F12" s="19">
         <v>1</v>
       </c>
       <c r="G12" s="27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I12" s="27" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J12" s="18" t="str">
         <f>D12</f>
@@ -7218,20 +7218,20 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="C13" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13" s="18" t="s">
         <v>90</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>91</v>
       </c>
       <c r="F13" s="18">
         <f>F10</f>
         <v>1.25</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H13" s="27" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I13" s="27" t="str">
         <f>I12</f>
@@ -7244,18 +7244,18 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="C16" s="18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="3:5" x14ac:dyDescent="0.45">
       <c r="C17" s="18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="3:5" x14ac:dyDescent="0.45">
@@ -7268,7 +7268,7 @@
         <v>AuxStoOUT</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -7287,15 +7287,15 @@
   <sheetData>
     <row r="3" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C4" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" s="24" t="s">
         <v>97</v>
-      </c>
-      <c r="D4" s="24" t="s">
-        <v>98</v>
       </c>
       <c r="E4" s="24">
         <v>2019</v>
@@ -7327,10 +7327,10 @@
     </row>
     <row r="5" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C5" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5" s="24" t="s">
         <v>99</v>
-      </c>
-      <c r="D5" s="24" t="s">
-        <v>100</v>
       </c>
       <c r="E5" s="25">
         <v>1015.5778521971276</v>
@@ -7362,10 +7362,10 @@
     </row>
     <row r="6" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C6" s="24" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E6" s="25">
         <v>700.50639018911227</v>
@@ -7397,10 +7397,10 @@
     </row>
     <row r="7" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C7" s="24" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E7" s="25">
         <v>811.76071002500203</v>
@@ -7432,10 +7432,10 @@
     </row>
     <row r="8" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C8" s="24" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E8" s="25">
         <v>224.68456877269512</v>
@@ -7467,10 +7467,10 @@
     </row>
     <row r="9" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C9" s="24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E9" s="25">
         <v>91.321320636454715</v>
@@ -7502,10 +7502,10 @@
     </row>
     <row r="10" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C10" s="24" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E10" s="25">
         <v>720.05690688478478</v>
@@ -7537,10 +7537,10 @@
     </row>
     <row r="11" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C11" s="24" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E11" s="25">
         <v>1889.6294955429962</v>
@@ -7572,10 +7572,10 @@
     </row>
     <row r="12" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C12" s="24" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E12" s="25">
         <v>22744.233908352184</v>
@@ -7607,10 +7607,10 @@
     </row>
     <row r="13" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C13" s="24" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E13" s="25">
         <v>106.71394978007027</v>
@@ -7642,10 +7642,10 @@
     </row>
     <row r="14" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C14" s="24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E14" s="25">
         <v>298.43161012117599</v>
@@ -7677,10 +7677,10 @@
     </row>
     <row r="15" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C15" s="24" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E15" s="25">
         <v>1523.3183094251776</v>
@@ -7712,10 +7712,10 @@
     </row>
     <row r="16" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C16" s="24" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E16" s="25">
         <v>1751.8277005767352</v>
@@ -7747,10 +7747,10 @@
     </row>
     <row r="17" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C17" s="24" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E17" s="25">
         <v>202.96571942318286</v>
@@ -7782,10 +7782,10 @@
     </row>
     <row r="18" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C18" s="24" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E18" s="25">
         <v>422.15486345591631</v>
@@ -7817,10 +7817,10 @@
     </row>
     <row r="19" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C19" s="24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E19" s="25">
         <v>60.453957297471518</v>
@@ -7852,10 +7852,10 @@
     </row>
     <row r="20" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C20" s="24" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E20" s="25">
         <v>4502.3802020512258</v>
@@ -7887,10 +7887,10 @@
     </row>
     <row r="21" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C21" s="24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E21" s="25">
         <v>101.5141995121252</v>
@@ -7922,10 +7922,10 @@
     </row>
     <row r="22" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C22" s="24" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E22" s="25">
         <v>1015.3084151432117</v>
@@ -7957,10 +7957,10 @@
     </row>
     <row r="23" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C23" s="24" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E23" s="25">
         <v>3272.7165337572983</v>
@@ -7992,10 +7992,10 @@
     </row>
     <row r="24" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C24" s="24" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E24" s="25">
         <v>1881.501357308103</v>
@@ -8027,10 +8027,10 @@
     </row>
     <row r="25" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C25" s="24" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D25" s="24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E25" s="25">
         <v>2675.2580995881326</v>
@@ -8062,10 +8062,10 @@
     </row>
     <row r="26" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C26" s="24" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E26" s="25">
         <v>17145.405261099833</v>
@@ -8097,10 +8097,10 @@
     </row>
     <row r="27" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C27" s="24" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E27" s="25">
         <v>424.95130472783899</v>
@@ -8132,10 +8132,10 @@
     </row>
     <row r="28" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C28" s="24" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E28" s="25">
         <v>518.43406512570868</v>
@@ -8167,10 +8167,10 @@
     </row>
     <row r="29" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C29" s="24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D29" s="24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E29" s="25">
         <v>9220.1745491436777</v>
@@ -8202,10 +8202,10 @@
     </row>
     <row r="30" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C30" s="24" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E30" s="25">
         <v>3015.830857597492</v>
@@ -8237,10 +8237,10 @@
     </row>
     <row r="31" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C31" s="24" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E31" s="25">
         <v>1127.9375661538616</v>
@@ -8272,10 +8272,10 @@
     </row>
     <row r="32" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C32" s="24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E32" s="25">
         <v>688.37087468549555</v>
@@ -8307,10 +8307,10 @@
     </row>
     <row r="33" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C33" s="24" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E33" s="25">
         <v>1011.5972956086001</v>
@@ -8342,10 +8342,10 @@
     </row>
     <row r="34" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C34" s="24" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E34" s="25">
         <v>837.06165177959838</v>
@@ -8377,10 +8377,10 @@
     </row>
     <row r="35" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C35" s="24" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D35" s="24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E35" s="25">
         <v>191.44130079511348</v>
@@ -8412,10 +8412,10 @@
     </row>
     <row r="36" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C36" s="24" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D36" s="24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E36" s="25">
         <v>902.99225707081837</v>
@@ -8447,10 +8447,10 @@
     </row>
     <row r="37" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C37" s="24" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D37" s="24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E37" s="25">
         <v>1059.4924708932501</v>
@@ -8482,10 +8482,10 @@
     </row>
     <row r="38" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C38" s="24" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D38" s="24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E38" s="25">
         <v>422.37829471301865</v>
@@ -8517,10 +8517,10 @@
     </row>
     <row r="39" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C39" s="24" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D39" s="24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E39" s="25">
         <v>220.41235503124381</v>

--- a/BY_Trans.xlsx
+++ b/BY_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\KiNESYS_BattCircularity-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC45DBF7-6061-412E-B4B5-6495937DCE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87CE23FE-8F80-422B-8E8F-673CF94C160A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Elec" sheetId="22" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="135">
   <si>
     <t>~md-v_s:</t>
   </si>
@@ -309,9 +309,6 @@
     <t>timeslice</t>
   </si>
   <si>
-    <t>pset_pd</t>
-  </si>
-  <si>
     <t>pset_co</t>
   </si>
   <si>
@@ -324,9 +321,6 @@
     <t>ELC</t>
   </si>
   <si>
-    <t>E?_HYD_PS-HY*,E?_ELC-HY_PS*</t>
-  </si>
-  <si>
     <t>NCAP_AFC</t>
   </si>
   <si>
@@ -354,9 +348,6 @@
     <t>INDELC</t>
   </si>
   <si>
-    <t>AutoP*</t>
-  </si>
-  <si>
     <t>~TFM_TOPINS-A</t>
   </si>
   <si>
@@ -481,6 +472,15 @@
   </si>
   <si>
     <t>ELE,CHP,STS,STG</t>
+  </si>
+  <si>
+    <t>EP_HPS*</t>
+  </si>
+  <si>
+    <t>EA_HPS*</t>
+  </si>
+  <si>
+    <t>E?_HPS*</t>
   </si>
 </sst>
 </file>
@@ -491,7 +491,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -628,8 +628,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -657,8 +663,14 @@
         <fgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -758,6 +770,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -773,7 +803,7 @@
     <xf numFmtId="0" fontId="18" fillId="5" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -795,15 +825,18 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="7" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="8"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="10" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="10" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="8" xfId="10" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="11"/>
     <xf numFmtId="2" fontId="19" fillId="0" borderId="0" xfId="11" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="7" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="8" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" xfId="8" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="8" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="20" fillId="0" borderId="9" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="20" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="8" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="Good" xfId="5" builtinId="26"/>
@@ -4174,7 +4207,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -4232,7 +4265,7 @@
         <v>2</v>
       </c>
       <c r="H5" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4246,7 +4279,7 @@
         <v>31.536000000000001</v>
       </c>
       <c r="H6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
@@ -4263,7 +4296,7 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
@@ -4285,7 +4318,7 @@
       <c r="H8" t="s">
         <v>18</v>
       </c>
-      <c r="J8" s="23" t="s">
+      <c r="J8" s="21" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4344,7 +4377,7 @@
         <v>1</v>
       </c>
       <c r="H11" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
@@ -4519,7 +4552,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="J1" s="20" t="s">
+      <c r="J1" s="19" t="s">
         <v>35</v>
       </c>
       <c r="K1" t="s">
@@ -6851,14 +6884,14 @@
       </c>
     </row>
     <row r="14" spans="2:9" ht="14.25" x14ac:dyDescent="0.45">
-      <c r="C14" s="26"/>
+      <c r="C14" s="24"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
     </row>
     <row r="15" spans="2:9" ht="14.25" x14ac:dyDescent="0.45">
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="I15" s="17"/>
@@ -6867,8 +6900,8 @@
       <c r="B16" t="s">
         <v>61</v>
       </c>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="I16" s="17"/>
@@ -6992,7 +7025,7 @@
       <c r="F31" t="s">
         <v>59</v>
       </c>
-      <c r="H31" s="22" t="s">
+      <c r="H31" s="20" t="s">
         <v>74</v>
       </c>
     </row>
@@ -7020,256 +7053,382 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="25" t="s">
         <v>75</v>
       </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A2" s="25"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="C3" s="18" t="s">
+      <c r="A3" s="25"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="26" t="s">
         <v>2</v>
       </c>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="C4" s="18" t="s">
+      <c r="A4" s="25"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="H4" s="18" t="s">
+      <c r="H4" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="I4" s="27" t="s">
+      <c r="I4" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="J4" s="27" t="s">
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="L4" s="18" t="s">
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A5" s="25"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="27" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="C5" s="18" t="s">
+      <c r="D5" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="E5" s="27"/>
+      <c r="F5" s="28">
+        <v>0.25</v>
+      </c>
+      <c r="G5" s="27" t="s">
+        <v>132</v>
+      </c>
+      <c r="H5" s="27"/>
+      <c r="I5" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="25"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A6" s="25"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="E6" s="25"/>
+      <c r="F6" s="29">
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="H6" s="25"/>
+      <c r="I6" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="L6" s="25"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A7" s="25"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="F5" s="19">
-        <f>6/24</f>
-        <v>0.25</v>
-      </c>
-      <c r="G5" s="27" t="s">
+      <c r="D7" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="J5" s="18" t="str">
-        <f>D5</f>
-        <v>ELC</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="C6" s="18" t="s">
+      <c r="E7" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="F7" s="29">
+        <v>0.31</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A8" s="25"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="F8" s="29">
+        <v>1</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="H8" s="25"/>
+      <c r="I8" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="25"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A9" s="25"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="F9" s="29">
+        <v>1</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="H9" s="25"/>
+      <c r="I9" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="25"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A10" s="25"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E10" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="F10" s="29">
+        <v>0.67</v>
+      </c>
+      <c r="G10" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="F6" s="19">
-        <f>6/24/F9</f>
-        <v>0.3125</v>
-      </c>
-      <c r="G6" s="27" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="C7" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="F7" s="19">
-        <v>1</v>
-      </c>
-      <c r="G7" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="J7" s="18" t="str">
-        <f>D7</f>
-        <v>ELC</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="C8" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="D8" s="18" t="s">
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A11" s="25"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="E8" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="F8" s="19">
-        <f>6/9</f>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="G8" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="L8" s="18" t="s">
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="29">
+        <v>0.8</v>
+      </c>
+      <c r="G11" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="25"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A12" s="25"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="C9" s="18" t="s">
+      <c r="D12" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="F9" s="19">
+      <c r="E12" s="25"/>
+      <c r="F12" s="25">
+        <v>1.25</v>
+      </c>
+      <c r="G12" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="H12" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="I12" s="25"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="25"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A13" s="25"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="D13" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30">
         <v>0.8</v>
       </c>
-      <c r="G9" s="27" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="C10" s="18" t="s">
+      <c r="G13" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="H13" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="I13" s="30"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="25"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A14" s="25"/>
+      <c r="B14" s="25"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="25"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A15" s="25"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="25"/>
+      <c r="K15" s="25"/>
+      <c r="L15" s="25"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A16" s="25"/>
+      <c r="B16" s="25"/>
+      <c r="C16" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="F10" s="18">
-        <f>1/F9</f>
-        <v>1.25</v>
-      </c>
-      <c r="G10" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="H10" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="J10" s="18" t="str">
-        <f>H10</f>
-        <v>ELC</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="C11" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="D11" s="27" t="s">
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="25"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A17" s="25"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="25"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="25"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A18" s="25"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="E18" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="F11" s="19">
-        <f>6/24</f>
-        <v>0.25</v>
-      </c>
-      <c r="G11" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="I11" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="J11" s="18" t="str">
-        <f>D11</f>
-        <v>INDELC</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="C12" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="D12" s="27" t="s">
-        <v>91</v>
-      </c>
-      <c r="E12" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="F12" s="19">
-        <v>1</v>
-      </c>
-      <c r="G12" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="I12" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="J12" s="18" t="str">
-        <f>D12</f>
-        <v>INDELC</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="C13" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="F13" s="18">
-        <f>F10</f>
-        <v>1.25</v>
-      </c>
-      <c r="G13" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="H13" s="27" t="s">
-        <v>91</v>
-      </c>
-      <c r="I13" s="27" t="str">
-        <f>I12</f>
-        <v>AutoP*</v>
-      </c>
-      <c r="J13" s="27" t="str">
-        <f>J12</f>
-        <v>INDELC</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="C16" s="18" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="17" spans="3:5" x14ac:dyDescent="0.45">
-      <c r="C17" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="E17" s="18" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="3:5" x14ac:dyDescent="0.45">
-      <c r="C18" s="18" t="str">
-        <f>G10</f>
-        <v>E?_HYD_PS-HY*,E?_ELC-HY_PS*</v>
-      </c>
-      <c r="D18" s="18" t="str">
-        <f>D10</f>
-        <v>AuxStoOUT</v>
-      </c>
-      <c r="E18" s="18" t="s">
-        <v>94</v>
-      </c>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="25"/>
+      <c r="K18" s="25"/>
+      <c r="L18" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7287,1266 +7446,1266 @@
   <sheetData>
     <row r="3" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="C4" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="E4" s="22">
+        <v>2019</v>
+      </c>
+      <c r="F4" s="22">
+        <v>2020</v>
+      </c>
+      <c r="G4" s="22">
+        <v>2023</v>
+      </c>
+      <c r="H4" s="22">
+        <v>2025</v>
+      </c>
+      <c r="I4" s="22">
+        <v>2030</v>
+      </c>
+      <c r="J4" s="22">
+        <v>2035</v>
+      </c>
+      <c r="K4" s="22">
+        <v>2040</v>
+      </c>
+      <c r="L4" s="22">
+        <v>2045</v>
+      </c>
+      <c r="M4" s="22">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="5" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="C5" s="22" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="4" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="C4" s="24" t="s">
+      <c r="D5" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="E5" s="23">
+        <v>1015.5778521971276</v>
+      </c>
+      <c r="F5" s="23">
+        <v>1037.014736980615</v>
+      </c>
+      <c r="G5" s="23">
+        <v>1127.6186676989064</v>
+      </c>
+      <c r="H5" s="23">
+        <v>1192.8945186459694</v>
+      </c>
+      <c r="I5" s="23">
+        <v>1370.0567717361366</v>
+      </c>
+      <c r="J5" s="23">
+        <v>1665.8841362805642</v>
+      </c>
+      <c r="K5" s="23">
+        <v>2199.3436201368027</v>
+      </c>
+      <c r="L5" s="23">
+        <v>2925.8763722626745</v>
+      </c>
+      <c r="M5" s="23">
+        <v>3795.927703803337</v>
+      </c>
+    </row>
+    <row r="6" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="C6" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="E4" s="24">
-        <v>2019</v>
-      </c>
-      <c r="F4" s="24">
-        <v>2020</v>
-      </c>
-      <c r="G4" s="24">
-        <v>2023</v>
-      </c>
-      <c r="H4" s="24">
-        <v>2025</v>
-      </c>
-      <c r="I4" s="24">
-        <v>2030</v>
-      </c>
-      <c r="J4" s="24">
-        <v>2035</v>
-      </c>
-      <c r="K4" s="24">
-        <v>2040</v>
-      </c>
-      <c r="L4" s="24">
-        <v>2045</v>
-      </c>
-      <c r="M4" s="24">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="5" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="C5" s="24" t="s">
+      <c r="D6" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E6" s="23">
+        <v>700.50639018911227</v>
+      </c>
+      <c r="F6" s="23">
+        <v>708.18742329287818</v>
+      </c>
+      <c r="G6" s="23">
+        <v>763.45629108954472</v>
+      </c>
+      <c r="H6" s="23">
+        <v>809.88023468647168</v>
+      </c>
+      <c r="I6" s="23">
+        <v>984.30001310220393</v>
+      </c>
+      <c r="J6" s="23">
+        <v>1267.9045873095483</v>
+      </c>
+      <c r="K6" s="23">
+        <v>1745.4710844508595</v>
+      </c>
+      <c r="L6" s="23">
+        <v>2427.9606817478152</v>
+      </c>
+      <c r="M6" s="23">
+        <v>3278.0224960696114</v>
+      </c>
+    </row>
+    <row r="7" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="C7" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="D5" s="24" t="s">
+      <c r="D7" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" s="23">
+        <v>811.76071002500203</v>
+      </c>
+      <c r="F7" s="23">
+        <v>803.64438125403058</v>
+      </c>
+      <c r="G7" s="23">
+        <v>816.73514471249246</v>
+      </c>
+      <c r="H7" s="23">
+        <v>828.38482385545979</v>
+      </c>
+      <c r="I7" s="23">
+        <v>866.15624018891037</v>
+      </c>
+      <c r="J7" s="23">
+        <v>932.44705958416796</v>
+      </c>
+      <c r="K7" s="23">
+        <v>1036.6708384092494</v>
+      </c>
+      <c r="L7" s="23">
+        <v>1169.7692484641191</v>
+      </c>
+      <c r="M7" s="23">
+        <v>1316.3397571060802</v>
+      </c>
+    </row>
+    <row r="8" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="C8" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="E5" s="25">
-        <v>1015.5778521971276</v>
-      </c>
-      <c r="F5" s="25">
-        <v>1037.014736980615</v>
-      </c>
-      <c r="G5" s="25">
-        <v>1127.6186676989064</v>
-      </c>
-      <c r="H5" s="25">
-        <v>1192.8945186459694</v>
-      </c>
-      <c r="I5" s="25">
-        <v>1370.0567717361366</v>
-      </c>
-      <c r="J5" s="25">
-        <v>1665.8841362805642</v>
-      </c>
-      <c r="K5" s="25">
-        <v>2199.3436201368027</v>
-      </c>
-      <c r="L5" s="25">
-        <v>2925.8763722626745</v>
-      </c>
-      <c r="M5" s="25">
-        <v>3795.927703803337</v>
-      </c>
-    </row>
-    <row r="6" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="C6" s="24" t="s">
+      <c r="D8" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E8" s="23">
+        <v>224.68456877269512</v>
+      </c>
+      <c r="F8" s="23">
+        <v>221.65882161899953</v>
+      </c>
+      <c r="G8" s="23">
+        <v>229.21145854264432</v>
+      </c>
+      <c r="H8" s="23">
+        <v>230.39403715374203</v>
+      </c>
+      <c r="I8" s="23">
+        <v>232.43860601888574</v>
+      </c>
+      <c r="J8" s="23">
+        <v>238.37880229281316</v>
+      </c>
+      <c r="K8" s="23">
+        <v>247.64092606372165</v>
+      </c>
+      <c r="L8" s="23">
+        <v>265.37343028948482</v>
+      </c>
+      <c r="M8" s="23">
+        <v>282.41626856114499</v>
+      </c>
+    </row>
+    <row r="9" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="C9" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="D6" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E6" s="25">
-        <v>700.50639018911227</v>
-      </c>
-      <c r="F6" s="25">
-        <v>708.18742329287818</v>
-      </c>
-      <c r="G6" s="25">
-        <v>763.45629108954472</v>
-      </c>
-      <c r="H6" s="25">
-        <v>809.88023468647168</v>
-      </c>
-      <c r="I6" s="25">
-        <v>984.30001310220393</v>
-      </c>
-      <c r="J6" s="25">
-        <v>1267.9045873095483</v>
-      </c>
-      <c r="K6" s="25">
-        <v>1745.4710844508595</v>
-      </c>
-      <c r="L6" s="25">
-        <v>2427.9606817478152</v>
-      </c>
-      <c r="M6" s="25">
-        <v>3278.0224960696114</v>
-      </c>
-    </row>
-    <row r="7" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="C7" s="24" t="s">
+      <c r="D9" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E9" s="23">
+        <v>91.321320636454715</v>
+      </c>
+      <c r="F9" s="23">
+        <v>92.640484093776735</v>
+      </c>
+      <c r="G9" s="23">
+        <v>92.598442052458878</v>
+      </c>
+      <c r="H9" s="23">
+        <v>91.489815842260143</v>
+      </c>
+      <c r="I9" s="23">
+        <v>93.55527409481779</v>
+      </c>
+      <c r="J9" s="23">
+        <v>95.955938066183123</v>
+      </c>
+      <c r="K9" s="23">
+        <v>101.20916661948286</v>
+      </c>
+      <c r="L9" s="23">
+        <v>109.27139702813284</v>
+      </c>
+      <c r="M9" s="23">
+        <v>115.39242587002472</v>
+      </c>
+    </row>
+    <row r="10" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="C10" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="D7" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E7" s="25">
-        <v>811.76071002500203</v>
-      </c>
-      <c r="F7" s="25">
-        <v>803.64438125403058</v>
-      </c>
-      <c r="G7" s="25">
-        <v>816.73514471249246</v>
-      </c>
-      <c r="H7" s="25">
-        <v>828.38482385545979</v>
-      </c>
-      <c r="I7" s="25">
-        <v>866.15624018891037</v>
-      </c>
-      <c r="J7" s="25">
-        <v>932.44705958416796</v>
-      </c>
-      <c r="K7" s="25">
-        <v>1036.6708384092494</v>
-      </c>
-      <c r="L7" s="25">
-        <v>1169.7692484641191</v>
-      </c>
-      <c r="M7" s="25">
-        <v>1316.3397571060802</v>
-      </c>
-    </row>
-    <row r="8" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="C8" s="24" t="s">
+      <c r="D10" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E10" s="23">
+        <v>720.05690688478478</v>
+      </c>
+      <c r="F10" s="23">
+        <v>719.55662707801343</v>
+      </c>
+      <c r="G10" s="23">
+        <v>733.37395642764295</v>
+      </c>
+      <c r="H10" s="23">
+        <v>742.08853382134771</v>
+      </c>
+      <c r="I10" s="23">
+        <v>755.51097475529457</v>
+      </c>
+      <c r="J10" s="23">
+        <v>772.1434831515262</v>
+      </c>
+      <c r="K10" s="23">
+        <v>808.86083588247675</v>
+      </c>
+      <c r="L10" s="23">
+        <v>859.57858059460079</v>
+      </c>
+      <c r="M10" s="23">
+        <v>917.8622085991841</v>
+      </c>
+    </row>
+    <row r="11" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="C11" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="D8" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E8" s="25">
-        <v>224.68456877269512</v>
-      </c>
-      <c r="F8" s="25">
-        <v>221.65882161899953</v>
-      </c>
-      <c r="G8" s="25">
-        <v>229.21145854264432</v>
-      </c>
-      <c r="H8" s="25">
-        <v>230.39403715374203</v>
-      </c>
-      <c r="I8" s="25">
-        <v>232.43860601888574</v>
-      </c>
-      <c r="J8" s="25">
-        <v>238.37880229281316</v>
-      </c>
-      <c r="K8" s="25">
-        <v>247.64092606372165</v>
-      </c>
-      <c r="L8" s="25">
-        <v>265.37343028948482</v>
-      </c>
-      <c r="M8" s="25">
-        <v>282.41626856114499</v>
-      </c>
-    </row>
-    <row r="9" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="C9" s="24" t="s">
+      <c r="D11" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E11" s="23">
+        <v>1889.6294955429962</v>
+      </c>
+      <c r="F11" s="23">
+        <v>1859.9687751163956</v>
+      </c>
+      <c r="G11" s="23">
+        <v>1981.7803329199098</v>
+      </c>
+      <c r="H11" s="23">
+        <v>2049.7911244766378</v>
+      </c>
+      <c r="I11" s="23">
+        <v>2098.7810592473361</v>
+      </c>
+      <c r="J11" s="23">
+        <v>2290.1173406322778</v>
+      </c>
+      <c r="K11" s="23">
+        <v>2754.8077138289591</v>
+      </c>
+      <c r="L11" s="23">
+        <v>3444.8998046383404</v>
+      </c>
+      <c r="M11" s="23">
+        <v>4246.9743952864465</v>
+      </c>
+    </row>
+    <row r="12" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="C12" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="D9" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E9" s="25">
-        <v>91.321320636454715</v>
-      </c>
-      <c r="F9" s="25">
-        <v>92.640484093776735</v>
-      </c>
-      <c r="G9" s="25">
-        <v>92.598442052458878</v>
-      </c>
-      <c r="H9" s="25">
-        <v>91.489815842260143</v>
-      </c>
-      <c r="I9" s="25">
-        <v>93.55527409481779</v>
-      </c>
-      <c r="J9" s="25">
-        <v>95.955938066183123</v>
-      </c>
-      <c r="K9" s="25">
-        <v>101.20916661948286</v>
-      </c>
-      <c r="L9" s="25">
-        <v>109.27139702813284</v>
-      </c>
-      <c r="M9" s="25">
-        <v>115.39242587002472</v>
-      </c>
-    </row>
-    <row r="10" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="C10" s="24" t="s">
+      <c r="D12" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" s="23">
+        <v>22744.233908352184</v>
+      </c>
+      <c r="F12" s="23">
+        <v>23606.966500548649</v>
+      </c>
+      <c r="G12" s="23">
+        <v>24450.255093409709</v>
+      </c>
+      <c r="H12" s="23">
+        <v>25084.42249670966</v>
+      </c>
+      <c r="I12" s="23">
+        <v>26155.04169140146</v>
+      </c>
+      <c r="J12" s="23">
+        <v>26842.478716291665</v>
+      </c>
+      <c r="K12" s="23">
+        <v>27770.807802552692</v>
+      </c>
+      <c r="L12" s="23">
+        <v>28938.699660285718</v>
+      </c>
+      <c r="M12" s="23">
+        <v>29909.149581400656</v>
+      </c>
+    </row>
+    <row r="13" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="C13" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="D10" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E10" s="25">
-        <v>720.05690688478478</v>
-      </c>
-      <c r="F10" s="25">
-        <v>719.55662707801343</v>
-      </c>
-      <c r="G10" s="25">
-        <v>733.37395642764295</v>
-      </c>
-      <c r="H10" s="25">
-        <v>742.08853382134771</v>
-      </c>
-      <c r="I10" s="25">
-        <v>755.51097475529457</v>
-      </c>
-      <c r="J10" s="25">
-        <v>772.1434831515262</v>
-      </c>
-      <c r="K10" s="25">
-        <v>808.86083588247675</v>
-      </c>
-      <c r="L10" s="25">
-        <v>859.57858059460079</v>
-      </c>
-      <c r="M10" s="25">
-        <v>917.8622085991841</v>
-      </c>
-    </row>
-    <row r="11" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="C11" s="24" t="s">
+      <c r="D13" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E13" s="23">
+        <v>106.71394978007027</v>
+      </c>
+      <c r="F13" s="23">
+        <v>105.86114713288038</v>
+      </c>
+      <c r="G13" s="23">
+        <v>111.76960471054292</v>
+      </c>
+      <c r="H13" s="23">
+        <v>115.43662316554607</v>
+      </c>
+      <c r="I13" s="23">
+        <v>120.4333698537162</v>
+      </c>
+      <c r="J13" s="23">
+        <v>125.53400071485034</v>
+      </c>
+      <c r="K13" s="23">
+        <v>133.21591848104546</v>
+      </c>
+      <c r="L13" s="23">
+        <v>140.23184696456153</v>
+      </c>
+      <c r="M13" s="23">
+        <v>145.79172464431582</v>
+      </c>
+    </row>
+    <row r="14" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="C14" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="D11" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E11" s="25">
-        <v>1889.6294955429962</v>
-      </c>
-      <c r="F11" s="25">
-        <v>1859.9687751163956</v>
-      </c>
-      <c r="G11" s="25">
-        <v>1981.7803329199098</v>
-      </c>
-      <c r="H11" s="25">
-        <v>2049.7911244766378</v>
-      </c>
-      <c r="I11" s="25">
-        <v>2098.7810592473361</v>
-      </c>
-      <c r="J11" s="25">
-        <v>2290.1173406322778</v>
-      </c>
-      <c r="K11" s="25">
-        <v>2754.8077138289591</v>
-      </c>
-      <c r="L11" s="25">
-        <v>3444.8998046383404</v>
-      </c>
-      <c r="M11" s="25">
-        <v>4246.9743952864465</v>
-      </c>
-    </row>
-    <row r="12" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="C12" s="24" t="s">
+      <c r="D14" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E14" s="23">
+        <v>298.43161012117599</v>
+      </c>
+      <c r="F14" s="23">
+        <v>302.89153677225721</v>
+      </c>
+      <c r="G14" s="23">
+        <v>303.59097220218871</v>
+      </c>
+      <c r="H14" s="23">
+        <v>306.28757665296195</v>
+      </c>
+      <c r="I14" s="23">
+        <v>309.52117854463438</v>
+      </c>
+      <c r="J14" s="23">
+        <v>317.51446567527375</v>
+      </c>
+      <c r="K14" s="23">
+        <v>349.88429790285545</v>
+      </c>
+      <c r="L14" s="23">
+        <v>374.42806955483837</v>
+      </c>
+      <c r="M14" s="23">
+        <v>402.87369420741277</v>
+      </c>
+    </row>
+    <row r="15" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="C15" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="D12" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E12" s="25">
-        <v>22744.233908352184</v>
-      </c>
-      <c r="F12" s="25">
-        <v>23606.966500548649</v>
-      </c>
-      <c r="G12" s="25">
-        <v>24450.255093409709</v>
-      </c>
-      <c r="H12" s="25">
-        <v>25084.42249670966</v>
-      </c>
-      <c r="I12" s="25">
-        <v>26155.04169140146</v>
-      </c>
-      <c r="J12" s="25">
-        <v>26842.478716291665</v>
-      </c>
-      <c r="K12" s="25">
-        <v>27770.807802552692</v>
-      </c>
-      <c r="L12" s="25">
-        <v>28938.699660285718</v>
-      </c>
-      <c r="M12" s="25">
-        <v>29909.149581400656</v>
-      </c>
-    </row>
-    <row r="13" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="C13" s="24" t="s">
+      <c r="D15" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E15" s="23">
+        <v>1523.3183094251776</v>
+      </c>
+      <c r="F15" s="23">
+        <v>1518.0330600255188</v>
+      </c>
+      <c r="G15" s="23">
+        <v>1551.1040718843719</v>
+      </c>
+      <c r="H15" s="23">
+        <v>1590.2874016479886</v>
+      </c>
+      <c r="I15" s="23">
+        <v>1565.0360985444559</v>
+      </c>
+      <c r="J15" s="23">
+        <v>1579.3312473102258</v>
+      </c>
+      <c r="K15" s="23">
+        <v>1626.5637138541779</v>
+      </c>
+      <c r="L15" s="23">
+        <v>1782.145551160261</v>
+      </c>
+      <c r="M15" s="23">
+        <v>1964.2988303777586</v>
+      </c>
+    </row>
+    <row r="16" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="C16" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="D13" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E13" s="25">
-        <v>106.71394978007027</v>
-      </c>
-      <c r="F13" s="25">
-        <v>105.86114713288038</v>
-      </c>
-      <c r="G13" s="25">
-        <v>111.76960471054292</v>
-      </c>
-      <c r="H13" s="25">
-        <v>115.43662316554607</v>
-      </c>
-      <c r="I13" s="25">
-        <v>120.4333698537162</v>
-      </c>
-      <c r="J13" s="25">
-        <v>125.53400071485034</v>
-      </c>
-      <c r="K13" s="25">
-        <v>133.21591848104546</v>
-      </c>
-      <c r="L13" s="25">
-        <v>140.23184696456153</v>
-      </c>
-      <c r="M13" s="25">
-        <v>145.79172464431582</v>
-      </c>
-    </row>
-    <row r="14" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="C14" s="24" t="s">
+      <c r="D16" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E16" s="23">
+        <v>1751.8277005767352</v>
+      </c>
+      <c r="F16" s="23">
+        <v>1741.2249177167487</v>
+      </c>
+      <c r="G16" s="23">
+        <v>1748.5898670648537</v>
+      </c>
+      <c r="H16" s="23">
+        <v>1773.6772374557461</v>
+      </c>
+      <c r="I16" s="23">
+        <v>1746.7848473139816</v>
+      </c>
+      <c r="J16" s="23">
+        <v>1764.4405183308197</v>
+      </c>
+      <c r="K16" s="23">
+        <v>1885.7519826550686</v>
+      </c>
+      <c r="L16" s="23">
+        <v>2091.1458873942261</v>
+      </c>
+      <c r="M16" s="23">
+        <v>2203.626193933072</v>
+      </c>
+    </row>
+    <row r="17" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="C17" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="D14" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E14" s="25">
-        <v>298.43161012117599</v>
-      </c>
-      <c r="F14" s="25">
-        <v>302.89153677225721</v>
-      </c>
-      <c r="G14" s="25">
-        <v>303.59097220218871</v>
-      </c>
-      <c r="H14" s="25">
-        <v>306.28757665296195</v>
-      </c>
-      <c r="I14" s="25">
-        <v>309.52117854463438</v>
-      </c>
-      <c r="J14" s="25">
-        <v>317.51446567527375</v>
-      </c>
-      <c r="K14" s="25">
-        <v>349.88429790285545</v>
-      </c>
-      <c r="L14" s="25">
-        <v>374.42806955483837</v>
-      </c>
-      <c r="M14" s="25">
-        <v>402.87369420741277</v>
-      </c>
-    </row>
-    <row r="15" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="C15" s="24" t="s">
+      <c r="D17" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E17" s="23">
+        <v>202.96571942318286</v>
+      </c>
+      <c r="F17" s="23">
+        <v>200.79651358447089</v>
+      </c>
+      <c r="G17" s="23">
+        <v>211.69815104408869</v>
+      </c>
+      <c r="H17" s="23">
+        <v>219.36178837713379</v>
+      </c>
+      <c r="I17" s="23">
+        <v>223.69518922757689</v>
+      </c>
+      <c r="J17" s="23">
+        <v>232.49884923211803</v>
+      </c>
+      <c r="K17" s="23">
+        <v>250.21104449379808</v>
+      </c>
+      <c r="L17" s="23">
+        <v>271.69384039195836</v>
+      </c>
+      <c r="M17" s="23">
+        <v>292.16744740905256</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="C18" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="D15" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E15" s="25">
-        <v>1523.3183094251776</v>
-      </c>
-      <c r="F15" s="25">
-        <v>1518.0330600255188</v>
-      </c>
-      <c r="G15" s="25">
-        <v>1551.1040718843719</v>
-      </c>
-      <c r="H15" s="25">
-        <v>1590.2874016479886</v>
-      </c>
-      <c r="I15" s="25">
-        <v>1565.0360985444559</v>
-      </c>
-      <c r="J15" s="25">
-        <v>1579.3312473102258</v>
-      </c>
-      <c r="K15" s="25">
-        <v>1626.5637138541779</v>
-      </c>
-      <c r="L15" s="25">
-        <v>1782.145551160261</v>
-      </c>
-      <c r="M15" s="25">
-        <v>1964.2988303777586</v>
-      </c>
-    </row>
-    <row r="16" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="C16" s="24" t="s">
+      <c r="D18" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E18" s="23">
+        <v>422.15486345591631</v>
+      </c>
+      <c r="F18" s="23">
+        <v>424.20792463817554</v>
+      </c>
+      <c r="G18" s="23">
+        <v>438.13237778477918</v>
+      </c>
+      <c r="H18" s="23">
+        <v>448.44058500308654</v>
+      </c>
+      <c r="I18" s="23">
+        <v>467.98648310157478</v>
+      </c>
+      <c r="J18" s="23">
+        <v>493.92795822648162</v>
+      </c>
+      <c r="K18" s="23">
+        <v>531.22260593379065</v>
+      </c>
+      <c r="L18" s="23">
+        <v>570.40947401297194</v>
+      </c>
+      <c r="M18" s="23">
+        <v>601.32479506483764</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="C19" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="D16" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E16" s="25">
-        <v>1751.8277005767352</v>
-      </c>
-      <c r="F16" s="25">
-        <v>1741.2249177167487</v>
-      </c>
-      <c r="G16" s="25">
-        <v>1748.5898670648537</v>
-      </c>
-      <c r="H16" s="25">
-        <v>1773.6772374557461</v>
-      </c>
-      <c r="I16" s="25">
-        <v>1746.7848473139816</v>
-      </c>
-      <c r="J16" s="25">
-        <v>1764.4405183308197</v>
-      </c>
-      <c r="K16" s="25">
-        <v>1885.7519826550686</v>
-      </c>
-      <c r="L16" s="25">
-        <v>2091.1458873942261</v>
-      </c>
-      <c r="M16" s="25">
-        <v>2203.626193933072</v>
-      </c>
-    </row>
-    <row r="17" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="C17" s="24" t="s">
+      <c r="D19" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E19" s="23">
+        <v>60.453957297471518</v>
+      </c>
+      <c r="F19" s="23">
+        <v>60.592462959259962</v>
+      </c>
+      <c r="G19" s="23">
+        <v>65.381641659210871</v>
+      </c>
+      <c r="H19" s="23">
+        <v>68.713111596703456</v>
+      </c>
+      <c r="I19" s="23">
+        <v>76.382605194331532</v>
+      </c>
+      <c r="J19" s="23">
+        <v>84.846336603125053</v>
+      </c>
+      <c r="K19" s="23">
+        <v>94.102759106965252</v>
+      </c>
+      <c r="L19" s="23">
+        <v>103.01688704252507</v>
+      </c>
+      <c r="M19" s="23">
+        <v>112.218052947304</v>
+      </c>
+    </row>
+    <row r="20" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="C20" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="D17" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E17" s="25">
-        <v>202.96571942318286</v>
-      </c>
-      <c r="F17" s="25">
-        <v>200.79651358447089</v>
-      </c>
-      <c r="G17" s="25">
-        <v>211.69815104408869</v>
-      </c>
-      <c r="H17" s="25">
-        <v>219.36178837713379</v>
-      </c>
-      <c r="I17" s="25">
-        <v>223.69518922757689</v>
-      </c>
-      <c r="J17" s="25">
-        <v>232.49884923211803</v>
-      </c>
-      <c r="K17" s="25">
-        <v>250.21104449379808</v>
-      </c>
-      <c r="L17" s="25">
-        <v>271.69384039195836</v>
-      </c>
-      <c r="M17" s="25">
-        <v>292.16744740905256</v>
-      </c>
-    </row>
-    <row r="18" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="C18" s="24" t="s">
+      <c r="D20" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E20" s="23">
+        <v>4502.3802020512258</v>
+      </c>
+      <c r="F20" s="23">
+        <v>4572.6050712765209</v>
+      </c>
+      <c r="G20" s="23">
+        <v>5494.7164607516879</v>
+      </c>
+      <c r="H20" s="23">
+        <v>6074.711257529636</v>
+      </c>
+      <c r="I20" s="23">
+        <v>7626.5520416464014</v>
+      </c>
+      <c r="J20" s="23">
+        <v>9561.4403506467952</v>
+      </c>
+      <c r="K20" s="23">
+        <v>12130.927922905901</v>
+      </c>
+      <c r="L20" s="23">
+        <v>15065.525769793749</v>
+      </c>
+      <c r="M20" s="23">
+        <v>18404.055717985004</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="C21" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="D18" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E18" s="25">
-        <v>422.15486345591631</v>
-      </c>
-      <c r="F18" s="25">
-        <v>424.20792463817554</v>
-      </c>
-      <c r="G18" s="25">
-        <v>438.13237778477918</v>
-      </c>
-      <c r="H18" s="25">
-        <v>448.44058500308654</v>
-      </c>
-      <c r="I18" s="25">
-        <v>467.98648310157478</v>
-      </c>
-      <c r="J18" s="25">
-        <v>493.92795822648162</v>
-      </c>
-      <c r="K18" s="25">
-        <v>531.22260593379065</v>
-      </c>
-      <c r="L18" s="25">
-        <v>570.40947401297194</v>
-      </c>
-      <c r="M18" s="25">
-        <v>601.32479506483764</v>
-      </c>
-    </row>
-    <row r="19" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="C19" s="24" t="s">
+      <c r="D21" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E21" s="23">
+        <v>101.5141995121252</v>
+      </c>
+      <c r="F21" s="23">
+        <v>107.04018891048096</v>
+      </c>
+      <c r="G21" s="23">
+        <v>110.33674817539078</v>
+      </c>
+      <c r="H21" s="23">
+        <v>114.96915766046013</v>
+      </c>
+      <c r="I21" s="23">
+        <v>117.76876821500565</v>
+      </c>
+      <c r="J21" s="23">
+        <v>122.60522965965828</v>
+      </c>
+      <c r="K21" s="23">
+        <v>134.14950775687768</v>
+      </c>
+      <c r="L21" s="23">
+        <v>151.57831027394735</v>
+      </c>
+      <c r="M21" s="23">
+        <v>168.94452047206218</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="C22" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="D19" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E19" s="25">
-        <v>60.453957297471518</v>
-      </c>
-      <c r="F19" s="25">
-        <v>60.592462959259962</v>
-      </c>
-      <c r="G19" s="25">
-        <v>65.381641659210871</v>
-      </c>
-      <c r="H19" s="25">
-        <v>68.713111596703456</v>
-      </c>
-      <c r="I19" s="25">
-        <v>76.382605194331532</v>
-      </c>
-      <c r="J19" s="25">
-        <v>84.846336603125053</v>
-      </c>
-      <c r="K19" s="25">
-        <v>94.102759106965252</v>
-      </c>
-      <c r="L19" s="25">
-        <v>103.01688704252507</v>
-      </c>
-      <c r="M19" s="25">
-        <v>112.218052947304</v>
-      </c>
-    </row>
-    <row r="20" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="C20" s="24" t="s">
+      <c r="D22" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E22" s="23">
+        <v>1015.3084151432117</v>
+      </c>
+      <c r="F22" s="23">
+        <v>1002.5626024235855</v>
+      </c>
+      <c r="G22" s="23">
+        <v>1019.5294315774552</v>
+      </c>
+      <c r="H22" s="23">
+        <v>1031.9562958696542</v>
+      </c>
+      <c r="I22" s="23">
+        <v>1002.4260062198492</v>
+      </c>
+      <c r="J22" s="23">
+        <v>1029.7275688251482</v>
+      </c>
+      <c r="K22" s="23">
+        <v>1088.3009665028339</v>
+      </c>
+      <c r="L22" s="23">
+        <v>1164.2516051674943</v>
+      </c>
+      <c r="M22" s="23">
+        <v>1249.221215374082</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="C23" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="D20" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E20" s="25">
-        <v>4502.3802020512258</v>
-      </c>
-      <c r="F20" s="25">
-        <v>4572.6050712765209</v>
-      </c>
-      <c r="G20" s="25">
-        <v>5494.7164607516879</v>
-      </c>
-      <c r="H20" s="25">
-        <v>6074.711257529636</v>
-      </c>
-      <c r="I20" s="25">
-        <v>7626.5520416464014</v>
-      </c>
-      <c r="J20" s="25">
-        <v>9561.4403506467952</v>
-      </c>
-      <c r="K20" s="25">
-        <v>12130.927922905901</v>
-      </c>
-      <c r="L20" s="25">
-        <v>15065.525769793749</v>
-      </c>
-      <c r="M20" s="25">
-        <v>18404.055717985004</v>
-      </c>
-    </row>
-    <row r="21" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="C21" s="24" t="s">
+      <c r="D23" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E23" s="23">
+        <v>3272.7165337572983</v>
+      </c>
+      <c r="F23" s="23">
+        <v>3211.5971023348725</v>
+      </c>
+      <c r="G23" s="23">
+        <v>3239.8291514612752</v>
+      </c>
+      <c r="H23" s="23">
+        <v>3238.6208781162736</v>
+      </c>
+      <c r="I23" s="23">
+        <v>3213.9089166209469</v>
+      </c>
+      <c r="J23" s="23">
+        <v>3256.1271080757706</v>
+      </c>
+      <c r="K23" s="23">
+        <v>3456.4015716033955</v>
+      </c>
+      <c r="L23" s="23">
+        <v>3742.0336776993768</v>
+      </c>
+      <c r="M23" s="23">
+        <v>4027.394544797934</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="C24" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="D21" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E21" s="25">
-        <v>101.5141995121252</v>
-      </c>
-      <c r="F21" s="25">
-        <v>107.04018891048096</v>
-      </c>
-      <c r="G21" s="25">
-        <v>110.33674817539078</v>
-      </c>
-      <c r="H21" s="25">
-        <v>114.96915766046013</v>
-      </c>
-      <c r="I21" s="25">
-        <v>117.76876821500565</v>
-      </c>
-      <c r="J21" s="25">
-        <v>122.60522965965828</v>
-      </c>
-      <c r="K21" s="25">
-        <v>134.14950775687768</v>
-      </c>
-      <c r="L21" s="25">
-        <v>151.57831027394735</v>
-      </c>
-      <c r="M21" s="25">
-        <v>168.94452047206218</v>
-      </c>
-    </row>
-    <row r="22" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="C22" s="24" t="s">
+      <c r="D24" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E24" s="23">
+        <v>1881.501357308103</v>
+      </c>
+      <c r="F24" s="23">
+        <v>1905.6331219769049</v>
+      </c>
+      <c r="G24" s="23">
+        <v>1996.3434397169906</v>
+      </c>
+      <c r="H24" s="23">
+        <v>2105.6564943234371</v>
+      </c>
+      <c r="I24" s="23">
+        <v>2347.3774265895627</v>
+      </c>
+      <c r="J24" s="23">
+        <v>2732.7680573898037</v>
+      </c>
+      <c r="K24" s="23">
+        <v>3313.664055620392</v>
+      </c>
+      <c r="L24" s="23">
+        <v>4015.7235602304545</v>
+      </c>
+      <c r="M24" s="23">
+        <v>4820.8975175147025</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="C25" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="D22" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E22" s="25">
-        <v>1015.3084151432117</v>
-      </c>
-      <c r="F22" s="25">
-        <v>1002.5626024235855</v>
-      </c>
-      <c r="G22" s="25">
-        <v>1019.5294315774552</v>
-      </c>
-      <c r="H22" s="25">
-        <v>1031.9562958696542</v>
-      </c>
-      <c r="I22" s="25">
-        <v>1002.4260062198492</v>
-      </c>
-      <c r="J22" s="25">
-        <v>1029.7275688251482</v>
-      </c>
-      <c r="K22" s="25">
-        <v>1088.3009665028339</v>
-      </c>
-      <c r="L22" s="25">
-        <v>1164.2516051674943</v>
-      </c>
-      <c r="M22" s="25">
-        <v>1249.221215374082</v>
-      </c>
-    </row>
-    <row r="23" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="C23" s="24" t="s">
+      <c r="D25" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E25" s="23">
+        <v>2675.2580995881326</v>
+      </c>
+      <c r="F25" s="23">
+        <v>2679.6316721042108</v>
+      </c>
+      <c r="G25" s="23">
+        <v>2853.9931298677743</v>
+      </c>
+      <c r="H25" s="23">
+        <v>3015.0394541095702</v>
+      </c>
+      <c r="I25" s="23">
+        <v>3321.7260765402652</v>
+      </c>
+      <c r="J25" s="23">
+        <v>3774.2478715123148</v>
+      </c>
+      <c r="K25" s="23">
+        <v>4537.4452815488203</v>
+      </c>
+      <c r="L25" s="23">
+        <v>5464.7940339166444</v>
+      </c>
+      <c r="M25" s="23">
+        <v>6304.3460358293869</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="C26" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="D23" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E23" s="25">
-        <v>3272.7165337572983</v>
-      </c>
-      <c r="F23" s="25">
-        <v>3211.5971023348725</v>
-      </c>
-      <c r="G23" s="25">
-        <v>3239.8291514612752</v>
-      </c>
-      <c r="H23" s="25">
-        <v>3238.6208781162736</v>
-      </c>
-      <c r="I23" s="25">
-        <v>3213.9089166209469</v>
-      </c>
-      <c r="J23" s="25">
-        <v>3256.1271080757706</v>
-      </c>
-      <c r="K23" s="25">
-        <v>3456.4015716033955</v>
-      </c>
-      <c r="L23" s="25">
-        <v>3742.0336776993768</v>
-      </c>
-      <c r="M23" s="25">
-        <v>4027.394544797934</v>
-      </c>
-    </row>
-    <row r="24" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="C24" s="24" t="s">
+      <c r="D26" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E26" s="23">
+        <v>17145.405261099833</v>
+      </c>
+      <c r="F26" s="23">
+        <v>17104.193509052409</v>
+      </c>
+      <c r="G26" s="23">
+        <v>17311.070724486741</v>
+      </c>
+      <c r="H26" s="23">
+        <v>17524.916290063335</v>
+      </c>
+      <c r="I26" s="23">
+        <v>17486.590657990007</v>
+      </c>
+      <c r="J26" s="23">
+        <v>17861.516204535394</v>
+      </c>
+      <c r="K26" s="23">
+        <v>19209.18258733529</v>
+      </c>
+      <c r="L26" s="23">
+        <v>20872.595036384395</v>
+      </c>
+      <c r="M26" s="23">
+        <v>22450.162330151325</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="C27" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="D24" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E24" s="25">
-        <v>1881.501357308103</v>
-      </c>
-      <c r="F24" s="25">
-        <v>1905.6331219769049</v>
-      </c>
-      <c r="G24" s="25">
-        <v>1996.3434397169906</v>
-      </c>
-      <c r="H24" s="25">
-        <v>2105.6564943234371</v>
-      </c>
-      <c r="I24" s="25">
-        <v>2347.3774265895627</v>
-      </c>
-      <c r="J24" s="25">
-        <v>2732.7680573898037</v>
-      </c>
-      <c r="K24" s="25">
-        <v>3313.664055620392</v>
-      </c>
-      <c r="L24" s="25">
-        <v>4015.7235602304545</v>
-      </c>
-      <c r="M24" s="25">
-        <v>4820.8975175147025</v>
-      </c>
-    </row>
-    <row r="25" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="C25" s="24" t="s">
+      <c r="D27" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E27" s="23">
+        <v>424.95130472783899</v>
+      </c>
+      <c r="F27" s="23">
+        <v>427.74022857287895</v>
+      </c>
+      <c r="G27" s="23">
+        <v>439.15459499397741</v>
+      </c>
+      <c r="H27" s="23">
+        <v>450.03121517399376</v>
+      </c>
+      <c r="I27" s="23">
+        <v>455.98010156530995</v>
+      </c>
+      <c r="J27" s="23">
+        <v>466.07629584265476</v>
+      </c>
+      <c r="K27" s="23">
+        <v>496.08036550802018</v>
+      </c>
+      <c r="L27" s="23">
+        <v>539.52940512733824</v>
+      </c>
+      <c r="M27" s="23">
+        <v>582.17574012868954</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="C28" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="D25" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E25" s="25">
-        <v>2675.2580995881326</v>
-      </c>
-      <c r="F25" s="25">
-        <v>2679.6316721042108</v>
-      </c>
-      <c r="G25" s="25">
-        <v>2853.9931298677743</v>
-      </c>
-      <c r="H25" s="25">
-        <v>3015.0394541095702</v>
-      </c>
-      <c r="I25" s="25">
-        <v>3321.7260765402652</v>
-      </c>
-      <c r="J25" s="25">
-        <v>3774.2478715123148</v>
-      </c>
-      <c r="K25" s="25">
-        <v>4537.4452815488203</v>
-      </c>
-      <c r="L25" s="25">
-        <v>5464.7940339166444</v>
-      </c>
-      <c r="M25" s="25">
-        <v>6304.3460358293869</v>
-      </c>
-    </row>
-    <row r="26" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="C26" s="24" t="s">
+      <c r="D28" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E28" s="23">
+        <v>518.43406512570868</v>
+      </c>
+      <c r="F28" s="23">
+        <v>528.07535776992859</v>
+      </c>
+      <c r="G28" s="23">
+        <v>557.20106448667832</v>
+      </c>
+      <c r="H28" s="23">
+        <v>571.33240616188664</v>
+      </c>
+      <c r="I28" s="23">
+        <v>608.93531714370909</v>
+      </c>
+      <c r="J28" s="23">
+        <v>641.11080892305472</v>
+      </c>
+      <c r="K28" s="23">
+        <v>667.68208063794214</v>
+      </c>
+      <c r="L28" s="23">
+        <v>700.02392561793147</v>
+      </c>
+      <c r="M28" s="23">
+        <v>789.49197589240487</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="C29" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="D26" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E26" s="25">
-        <v>17145.405261099833</v>
-      </c>
-      <c r="F26" s="25">
-        <v>17104.193509052409</v>
-      </c>
-      <c r="G26" s="25">
-        <v>17311.070724486741</v>
-      </c>
-      <c r="H26" s="25">
-        <v>17524.916290063335</v>
-      </c>
-      <c r="I26" s="25">
-        <v>17486.590657990007</v>
-      </c>
-      <c r="J26" s="25">
-        <v>17861.516204535394</v>
-      </c>
-      <c r="K26" s="25">
-        <v>19209.18258733529</v>
-      </c>
-      <c r="L26" s="25">
-        <v>20872.595036384395</v>
-      </c>
-      <c r="M26" s="25">
-        <v>22450.162330151325</v>
-      </c>
-    </row>
-    <row r="27" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="C27" s="24" t="s">
+      <c r="D29" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E29" s="23">
+        <v>9220.1745491436777</v>
+      </c>
+      <c r="F29" s="23">
+        <v>9416.0670669519295</v>
+      </c>
+      <c r="G29" s="23">
+        <v>10119.674320803471</v>
+      </c>
+      <c r="H29" s="23">
+        <v>10633.445140084832</v>
+      </c>
+      <c r="I29" s="23">
+        <v>12101.450518908092</v>
+      </c>
+      <c r="J29" s="23">
+        <v>13902.252525127782</v>
+      </c>
+      <c r="K29" s="23">
+        <v>16778.884907329808</v>
+      </c>
+      <c r="L29" s="23">
+        <v>20034.487499665211</v>
+      </c>
+      <c r="M29" s="23">
+        <v>23441.765290077503</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="C30" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="D27" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E27" s="25">
-        <v>424.95130472783899</v>
-      </c>
-      <c r="F27" s="25">
-        <v>427.74022857287895</v>
-      </c>
-      <c r="G27" s="25">
-        <v>439.15459499397741</v>
-      </c>
-      <c r="H27" s="25">
-        <v>450.03121517399376</v>
-      </c>
-      <c r="I27" s="25">
-        <v>455.98010156530995</v>
-      </c>
-      <c r="J27" s="25">
-        <v>466.07629584265476</v>
-      </c>
-      <c r="K27" s="25">
-        <v>496.08036550802018</v>
-      </c>
-      <c r="L27" s="25">
-        <v>539.52940512733824</v>
-      </c>
-      <c r="M27" s="25">
-        <v>582.17574012868954</v>
-      </c>
-    </row>
-    <row r="28" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="C28" s="24" t="s">
+      <c r="D30" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E30" s="23">
+        <v>3015.830857597492</v>
+      </c>
+      <c r="F30" s="23">
+        <v>3010.9891684557342</v>
+      </c>
+      <c r="G30" s="23">
+        <v>2850.6202643641218</v>
+      </c>
+      <c r="H30" s="23">
+        <v>2846.2708498530001</v>
+      </c>
+      <c r="I30" s="23">
+        <v>3011.2100040154619</v>
+      </c>
+      <c r="J30" s="23">
+        <v>3097.4833217720575</v>
+      </c>
+      <c r="K30" s="23">
+        <v>3330.4225788176122</v>
+      </c>
+      <c r="L30" s="23">
+        <v>3597.2575730080712</v>
+      </c>
+      <c r="M30" s="23">
+        <v>3875.8955806692529</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="C31" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="D28" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E28" s="25">
-        <v>518.43406512570868</v>
-      </c>
-      <c r="F28" s="25">
-        <v>528.07535776992859</v>
-      </c>
-      <c r="G28" s="25">
-        <v>557.20106448667832</v>
-      </c>
-      <c r="H28" s="25">
-        <v>571.33240616188664</v>
-      </c>
-      <c r="I28" s="25">
-        <v>608.93531714370909</v>
-      </c>
-      <c r="J28" s="25">
-        <v>641.11080892305472</v>
-      </c>
-      <c r="K28" s="25">
-        <v>667.68208063794214</v>
-      </c>
-      <c r="L28" s="25">
-        <v>700.02392561793147</v>
-      </c>
-      <c r="M28" s="25">
-        <v>789.49197589240487</v>
-      </c>
-    </row>
-    <row r="29" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="C29" s="24" t="s">
+      <c r="D31" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E31" s="23">
+        <v>1127.9375661538616</v>
+      </c>
+      <c r="F31" s="23">
+        <v>1115.0437921483363</v>
+      </c>
+      <c r="G31" s="23">
+        <v>1142.4834728255896</v>
+      </c>
+      <c r="H31" s="23">
+        <v>1155.2829574588172</v>
+      </c>
+      <c r="I31" s="23">
+        <v>1228.7833518137388</v>
+      </c>
+      <c r="J31" s="23">
+        <v>1300.780060603998</v>
+      </c>
+      <c r="K31" s="23">
+        <v>1457.9901355782697</v>
+      </c>
+      <c r="L31" s="23">
+        <v>1580.2308182605771</v>
+      </c>
+      <c r="M31" s="23">
+        <v>1753.5396742825753</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="C32" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="D29" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E29" s="25">
-        <v>9220.1745491436777</v>
-      </c>
-      <c r="F29" s="25">
-        <v>9416.0670669519295</v>
-      </c>
-      <c r="G29" s="25">
-        <v>10119.674320803471</v>
-      </c>
-      <c r="H29" s="25">
-        <v>10633.445140084832</v>
-      </c>
-      <c r="I29" s="25">
-        <v>12101.450518908092</v>
-      </c>
-      <c r="J29" s="25">
-        <v>13902.252525127782</v>
-      </c>
-      <c r="K29" s="25">
-        <v>16778.884907329808</v>
-      </c>
-      <c r="L29" s="25">
-        <v>20034.487499665211</v>
-      </c>
-      <c r="M29" s="25">
-        <v>23441.765290077503</v>
-      </c>
-    </row>
-    <row r="30" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="C30" s="24" t="s">
+      <c r="D32" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E32" s="23">
+        <v>688.37087468549555</v>
+      </c>
+      <c r="F32" s="23">
+        <v>681.37789359066539</v>
+      </c>
+      <c r="G32" s="23">
+        <v>671.37804773866151</v>
+      </c>
+      <c r="H32" s="23">
+        <v>669.85305671208903</v>
+      </c>
+      <c r="I32" s="23">
+        <v>681.89120634372534</v>
+      </c>
+      <c r="J32" s="23">
+        <v>744.25171544029729</v>
+      </c>
+      <c r="K32" s="23">
+        <v>884.70675365868101</v>
+      </c>
+      <c r="L32" s="23">
+        <v>1071.0443987258536</v>
+      </c>
+      <c r="M32" s="23">
+        <v>1295.8482577436666</v>
+      </c>
+    </row>
+    <row r="33" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="C33" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="D30" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E30" s="25">
-        <v>3015.830857597492</v>
-      </c>
-      <c r="F30" s="25">
-        <v>3010.9891684557342</v>
-      </c>
-      <c r="G30" s="25">
-        <v>2850.6202643641218</v>
-      </c>
-      <c r="H30" s="25">
-        <v>2846.2708498530001</v>
-      </c>
-      <c r="I30" s="25">
-        <v>3011.2100040154619</v>
-      </c>
-      <c r="J30" s="25">
-        <v>3097.4833217720575</v>
-      </c>
-      <c r="K30" s="25">
-        <v>3330.4225788176122</v>
-      </c>
-      <c r="L30" s="25">
-        <v>3597.2575730080712</v>
-      </c>
-      <c r="M30" s="25">
-        <v>3875.8955806692529</v>
-      </c>
-    </row>
-    <row r="31" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="C31" s="24" t="s">
+      <c r="D33" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E33" s="23">
+        <v>1011.5972956086001</v>
+      </c>
+      <c r="F33" s="23">
+        <v>1008.7348225459173</v>
+      </c>
+      <c r="G33" s="23">
+        <v>1037.5508477478811</v>
+      </c>
+      <c r="H33" s="23">
+        <v>1064.0458184017075</v>
+      </c>
+      <c r="I33" s="23">
+        <v>1039.2219571600085</v>
+      </c>
+      <c r="J33" s="23">
+        <v>1075.2741086422773</v>
+      </c>
+      <c r="K33" s="23">
+        <v>1166.7719370751688</v>
+      </c>
+      <c r="L33" s="23">
+        <v>1289.6281077099202</v>
+      </c>
+      <c r="M33" s="23">
+        <v>1423.2936999667922</v>
+      </c>
+    </row>
+    <row r="34" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="C34" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="D31" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E31" s="25">
-        <v>1127.9375661538616</v>
-      </c>
-      <c r="F31" s="25">
-        <v>1115.0437921483363</v>
-      </c>
-      <c r="G31" s="25">
-        <v>1142.4834728255896</v>
-      </c>
-      <c r="H31" s="25">
-        <v>1155.2829574588172</v>
-      </c>
-      <c r="I31" s="25">
-        <v>1228.7833518137388</v>
-      </c>
-      <c r="J31" s="25">
-        <v>1300.780060603998</v>
-      </c>
-      <c r="K31" s="25">
-        <v>1457.9901355782697</v>
-      </c>
-      <c r="L31" s="25">
-        <v>1580.2308182605771</v>
-      </c>
-      <c r="M31" s="25">
-        <v>1753.5396742825753</v>
-      </c>
-    </row>
-    <row r="32" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="C32" s="24" t="s">
+      <c r="D34" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E34" s="23">
+        <v>837.06165177959838</v>
+      </c>
+      <c r="F34" s="23">
+        <v>838.9701740520668</v>
+      </c>
+      <c r="G34" s="23">
+        <v>838.14438128342704</v>
+      </c>
+      <c r="H34" s="23">
+        <v>843.16025634437585</v>
+      </c>
+      <c r="I34" s="23">
+        <v>871.47860501562286</v>
+      </c>
+      <c r="J34" s="23">
+        <v>914.81170370444579</v>
+      </c>
+      <c r="K34" s="23">
+        <v>974.56433098998912</v>
+      </c>
+      <c r="L34" s="23">
+        <v>1043.3053078417299</v>
+      </c>
+      <c r="M34" s="23">
+        <v>1111.7695348668212</v>
+      </c>
+    </row>
+    <row r="35" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="C35" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="D32" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E32" s="25">
-        <v>688.37087468549555</v>
-      </c>
-      <c r="F32" s="25">
-        <v>681.37789359066539</v>
-      </c>
-      <c r="G32" s="25">
-        <v>671.37804773866151</v>
-      </c>
-      <c r="H32" s="25">
-        <v>669.85305671208903</v>
-      </c>
-      <c r="I32" s="25">
-        <v>681.89120634372534</v>
-      </c>
-      <c r="J32" s="25">
-        <v>744.25171544029729</v>
-      </c>
-      <c r="K32" s="25">
-        <v>884.70675365868101</v>
-      </c>
-      <c r="L32" s="25">
-        <v>1071.0443987258536</v>
-      </c>
-      <c r="M32" s="25">
-        <v>1295.8482577436666</v>
-      </c>
-    </row>
-    <row r="33" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="C33" s="24" t="s">
+      <c r="D35" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E35" s="23">
+        <v>191.44130079511348</v>
+      </c>
+      <c r="F35" s="23">
+        <v>190.44347230387802</v>
+      </c>
+      <c r="G35" s="23">
+        <v>191.15088620439039</v>
+      </c>
+      <c r="H35" s="23">
+        <v>192.50918111596147</v>
+      </c>
+      <c r="I35" s="23">
+        <v>190.99030672566792</v>
+      </c>
+      <c r="J35" s="23">
+        <v>202.70954610439742</v>
+      </c>
+      <c r="K35" s="23">
+        <v>208.47554310835133</v>
+      </c>
+      <c r="L35" s="23">
+        <v>221.81687910390701</v>
+      </c>
+      <c r="M35" s="23">
+        <v>239.79020951356867</v>
+      </c>
+    </row>
+    <row r="36" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="C36" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="D33" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E33" s="25">
-        <v>1011.5972956086001</v>
-      </c>
-      <c r="F33" s="25">
-        <v>1008.7348225459173</v>
-      </c>
-      <c r="G33" s="25">
-        <v>1037.5508477478811</v>
-      </c>
-      <c r="H33" s="25">
-        <v>1064.0458184017075</v>
-      </c>
-      <c r="I33" s="25">
-        <v>1039.2219571600085</v>
-      </c>
-      <c r="J33" s="25">
-        <v>1075.2741086422773</v>
-      </c>
-      <c r="K33" s="25">
-        <v>1166.7719370751688</v>
-      </c>
-      <c r="L33" s="25">
-        <v>1289.6281077099202</v>
-      </c>
-      <c r="M33" s="25">
-        <v>1423.2936999667922</v>
-      </c>
-    </row>
-    <row r="34" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="C34" s="24" t="s">
+      <c r="D36" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E36" s="23">
+        <v>902.99225707081837</v>
+      </c>
+      <c r="F36" s="23">
+        <v>920.48579969381581</v>
+      </c>
+      <c r="G36" s="23">
+        <v>996.24993848302472</v>
+      </c>
+      <c r="H36" s="23">
+        <v>1045.0453296980902</v>
+      </c>
+      <c r="I36" s="23">
+        <v>1105.4257870034721</v>
+      </c>
+      <c r="J36" s="23">
+        <v>1177.6842510906959</v>
+      </c>
+      <c r="K36" s="23">
+        <v>1289.7751872940789</v>
+      </c>
+      <c r="L36" s="23">
+        <v>1395.3747172466587</v>
+      </c>
+      <c r="M36" s="23">
+        <v>1497.0814520140805</v>
+      </c>
+    </row>
+    <row r="37" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="C37" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="D34" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E34" s="25">
-        <v>837.06165177959838</v>
-      </c>
-      <c r="F34" s="25">
-        <v>838.9701740520668</v>
-      </c>
-      <c r="G34" s="25">
-        <v>838.14438128342704</v>
-      </c>
-      <c r="H34" s="25">
-        <v>843.16025634437585</v>
-      </c>
-      <c r="I34" s="25">
-        <v>871.47860501562286</v>
-      </c>
-      <c r="J34" s="25">
-        <v>914.81170370444579</v>
-      </c>
-      <c r="K34" s="25">
-        <v>974.56433098998912</v>
-      </c>
-      <c r="L34" s="25">
-        <v>1043.3053078417299</v>
-      </c>
-      <c r="M34" s="25">
-        <v>1111.7695348668212</v>
-      </c>
-    </row>
-    <row r="35" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="C35" s="24" t="s">
+      <c r="D37" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E37" s="23">
+        <v>1059.4924708932501</v>
+      </c>
+      <c r="F37" s="23">
+        <v>1053.1386696249981</v>
+      </c>
+      <c r="G37" s="23">
+        <v>1069.5136230658643</v>
+      </c>
+      <c r="H37" s="23">
+        <v>1102.8233576795149</v>
+      </c>
+      <c r="I37" s="23">
+        <v>1110.9877935942955</v>
+      </c>
+      <c r="J37" s="23">
+        <v>1142.0942630254028</v>
+      </c>
+      <c r="K37" s="23">
+        <v>1242.4096537920775</v>
+      </c>
+      <c r="L37" s="23">
+        <v>1399.1631471812057</v>
+      </c>
+      <c r="M37" s="23">
+        <v>1567.335319626412</v>
+      </c>
+    </row>
+    <row r="38" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="C38" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="D35" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E35" s="25">
-        <v>191.44130079511348</v>
-      </c>
-      <c r="F35" s="25">
-        <v>190.44347230387802</v>
-      </c>
-      <c r="G35" s="25">
-        <v>191.15088620439039</v>
-      </c>
-      <c r="H35" s="25">
-        <v>192.50918111596147</v>
-      </c>
-      <c r="I35" s="25">
-        <v>190.99030672566792</v>
-      </c>
-      <c r="J35" s="25">
-        <v>202.70954610439742</v>
-      </c>
-      <c r="K35" s="25">
-        <v>208.47554310835133</v>
-      </c>
-      <c r="L35" s="25">
-        <v>221.81687910390701</v>
-      </c>
-      <c r="M35" s="25">
-        <v>239.79020951356867</v>
-      </c>
-    </row>
-    <row r="36" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="C36" s="24" t="s">
+      <c r="D38" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E38" s="23">
+        <v>422.37829471301865</v>
+      </c>
+      <c r="F38" s="23">
+        <v>431.38548824142845</v>
+      </c>
+      <c r="G38" s="23">
+        <v>382.60099247369141</v>
+      </c>
+      <c r="H38" s="23">
+        <v>354.78506334834918</v>
+      </c>
+      <c r="I38" s="23">
+        <v>412.31956693474024</v>
+      </c>
+      <c r="J38" s="23">
+        <v>504.2244343224441</v>
+      </c>
+      <c r="K38" s="23">
+        <v>637.78278487581883</v>
+      </c>
+      <c r="L38" s="23">
+        <v>755.08712841736769</v>
+      </c>
+      <c r="M38" s="23">
+        <v>893.52071666851668</v>
+      </c>
+    </row>
+    <row r="39" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="C39" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="D36" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E36" s="25">
-        <v>902.99225707081837</v>
-      </c>
-      <c r="F36" s="25">
-        <v>920.48579969381581</v>
-      </c>
-      <c r="G36" s="25">
-        <v>996.24993848302472</v>
-      </c>
-      <c r="H36" s="25">
-        <v>1045.0453296980902</v>
-      </c>
-      <c r="I36" s="25">
-        <v>1105.4257870034721</v>
-      </c>
-      <c r="J36" s="25">
-        <v>1177.6842510906959</v>
-      </c>
-      <c r="K36" s="25">
-        <v>1289.7751872940789</v>
-      </c>
-      <c r="L36" s="25">
-        <v>1395.3747172466587</v>
-      </c>
-      <c r="M36" s="25">
-        <v>1497.0814520140805</v>
-      </c>
-    </row>
-    <row r="37" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="C37" s="24" t="s">
-        <v>131</v>
-      </c>
-      <c r="D37" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E37" s="25">
-        <v>1059.4924708932501</v>
-      </c>
-      <c r="F37" s="25">
-        <v>1053.1386696249981</v>
-      </c>
-      <c r="G37" s="25">
-        <v>1069.5136230658643</v>
-      </c>
-      <c r="H37" s="25">
-        <v>1102.8233576795149</v>
-      </c>
-      <c r="I37" s="25">
-        <v>1110.9877935942955</v>
-      </c>
-      <c r="J37" s="25">
-        <v>1142.0942630254028</v>
-      </c>
-      <c r="K37" s="25">
-        <v>1242.4096537920775</v>
-      </c>
-      <c r="L37" s="25">
-        <v>1399.1631471812057</v>
-      </c>
-      <c r="M37" s="25">
-        <v>1567.335319626412</v>
-      </c>
-    </row>
-    <row r="38" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="C38" s="24" t="s">
-        <v>132</v>
-      </c>
-      <c r="D38" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E38" s="25">
-        <v>422.37829471301865</v>
-      </c>
-      <c r="F38" s="25">
-        <v>431.38548824142845</v>
-      </c>
-      <c r="G38" s="25">
-        <v>382.60099247369141</v>
-      </c>
-      <c r="H38" s="25">
-        <v>354.78506334834918</v>
-      </c>
-      <c r="I38" s="25">
-        <v>412.31956693474024</v>
-      </c>
-      <c r="J38" s="25">
-        <v>504.2244343224441</v>
-      </c>
-      <c r="K38" s="25">
-        <v>637.78278487581883</v>
-      </c>
-      <c r="L38" s="25">
-        <v>755.08712841736769</v>
-      </c>
-      <c r="M38" s="25">
-        <v>893.52071666851668</v>
-      </c>
-    </row>
-    <row r="39" spans="3:13" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="C39" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="D39" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E39" s="25">
+      <c r="D39" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E39" s="23">
         <v>220.41235503124381</v>
       </c>
-      <c r="F39" s="25">
+      <c r="F39" s="23">
         <v>217.19954084768659</v>
       </c>
-      <c r="G39" s="25">
+      <c r="G39" s="23">
         <v>237.80764782906621</v>
       </c>
-      <c r="H39" s="25">
+      <c r="H39" s="23">
         <v>249.74522453868417</v>
       </c>
-      <c r="I39" s="25">
+      <c r="I39" s="23">
         <v>288.63181974143407</v>
       </c>
-      <c r="J39" s="25">
+      <c r="J39" s="23">
         <v>340.34925938833698</v>
       </c>
-      <c r="K39" s="25">
+      <c r="K39" s="23">
         <v>406.33291541286087</v>
       </c>
-      <c r="L39" s="25">
+      <c r="L39" s="23">
         <v>473.61493993757477</v>
       </c>
-      <c r="M39" s="25">
+      <c r="M39" s="23">
         <v>535.00954887193438</v>
       </c>
     </row>

--- a/BY_Trans.xlsx
+++ b/BY_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\KiNESYS_BattCircularity-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87CE23FE-8F80-422B-8E8F-673CF94C160A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D0B0D56-1B98-4162-8571-D356E4D83079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Elec" sheetId="22" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="137">
   <si>
     <t>~md-v_s:</t>
   </si>
@@ -481,6 +481,12 @@
   </si>
   <si>
     <t>E?_HPS*</t>
+  </si>
+  <si>
+    <t>ELCSPV</t>
+  </si>
+  <si>
+    <t>ELCWIN</t>
   </si>
 </sst>
 </file>
@@ -4192,7 +4198,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801E4010-C144-4149-95F4-80A0F3B7A676}">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="13.3984375" bestFit="1" customWidth="1"/>
@@ -4380,91 +4386,130 @@
         <v>131</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B14" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B15" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>7</v>
-      </c>
-      <c r="G15" t="s">
-        <v>8</v>
-      </c>
-      <c r="H15" t="s">
-        <v>9</v>
-      </c>
-      <c r="I15" t="s">
-        <v>11</v>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12">
+        <v>0.15</v>
+      </c>
+      <c r="J12" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13">
+        <v>0.25</v>
+      </c>
+      <c r="J13" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16">
-        <v>0.32</v>
-      </c>
-      <c r="I16" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17" t="s">
+        <v>7</v>
+      </c>
+      <c r="G17" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B18" t="s">
         <v>23</v>
       </c>
-      <c r="G17">
+      <c r="G18">
+        <v>0.32</v>
+      </c>
+      <c r="I18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19">
         <v>1</v>
       </c>
-      <c r="I17" t="s">
+      <c r="I19" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B24" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="C25" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" t="s">
+        <v>5</v>
+      </c>
+      <c r="E25" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25" t="s">
+        <v>7</v>
+      </c>
+      <c r="G25" t="s">
+        <v>8</v>
+      </c>
+      <c r="H25" t="s">
+        <v>9</v>
+      </c>
+      <c r="I25" t="s">
+        <v>11</v>
+      </c>
+      <c r="J25" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C26" t="s">
-        <v>4</v>
-      </c>
-      <c r="D26" t="s">
-        <v>5</v>
-      </c>
-      <c r="E26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" t="s">
-        <v>7</v>
-      </c>
-      <c r="G26" t="s">
-        <v>8</v>
+        <v>27</v>
+      </c>
+      <c r="G26" s="2">
+        <v>2882.65777101602</v>
       </c>
       <c r="H26" t="s">
-        <v>9</v>
-      </c>
-      <c r="I26" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="J26" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.35">
@@ -4475,13 +4520,13 @@
         <v>27</v>
       </c>
       <c r="G27" s="2">
-        <v>2882.65777101602</v>
+        <v>893.70913654846424</v>
       </c>
       <c r="H27" t="s">
         <v>28</v>
       </c>
       <c r="J27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.35">
@@ -4492,40 +4537,23 @@
         <v>27</v>
       </c>
       <c r="G28" s="2">
-        <v>893.70913654846424</v>
+        <v>3000</v>
       </c>
       <c r="H28" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J28" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
-        <v>26</v>
-      </c>
-      <c r="C29" t="s">
-        <v>27</v>
-      </c>
-      <c r="G29" s="2">
-        <v>3000</v>
-      </c>
-      <c r="H29" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="G29">
+        <v>30</v>
       </c>
       <c r="J29" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B30" t="s">
-        <v>33</v>
-      </c>
-      <c r="G30">
-        <v>30</v>
-      </c>
-      <c r="J30" t="s">
         <v>34</v>
       </c>
     </row>

--- a/BY_Trans.xlsx
+++ b/BY_Trans.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="8710" activeTab="6"/>
+    <workbookView windowWidth="18350" windowHeight="8710"/>
   </bookViews>
   <sheets>
     <sheet name="Elec" sheetId="22" r:id="rId1"/>
@@ -39,6 +39,28 @@
     <author>xli9</author>
   </authors>
   <commentList>
+    <comment ref="B32" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t>xli9:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t xml:space="preserve">
+I removed this one</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B35" authorId="0">
       <text>
         <r>
@@ -778,12 +800,17 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
-      <b/>
+      <sz val="9"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
@@ -794,13 +821,8 @@
       <name val="Tahoma"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -846,6 +868,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1245,13 +1273,13 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1261,82 +1289,82 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1358,9 +1386,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="55" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="53"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="53" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="53" applyFont="1" applyFill="1"/>
@@ -1392,6 +1417,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -4865,7 +4891,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -4936,7 +4962,7 @@
       <c r="D6" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="31">
+      <c r="G6" s="30">
         <v>31.536</v>
       </c>
       <c r="H6" t="s">
@@ -5093,7 +5119,7 @@
       <c r="C26" t="s">
         <v>26</v>
       </c>
-      <c r="G26" s="34">
+      <c r="G26" s="33">
         <v>2882.65777101602</v>
       </c>
       <c r="H26" t="s">
@@ -5110,7 +5136,7 @@
       <c r="C27" t="s">
         <v>26</v>
       </c>
-      <c r="G27" s="34">
+      <c r="G27" s="33">
         <v>893.709136548464</v>
       </c>
       <c r="H27" t="s">
@@ -5127,7 +5153,7 @@
       <c r="C28" t="s">
         <v>26</v>
       </c>
-      <c r="G28" s="34">
+      <c r="G28" s="33">
         <v>3000</v>
       </c>
       <c r="H28" t="s">
@@ -5137,14 +5163,20 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="2:10">
-      <c r="B29" t="s">
+    <row r="32" spans="2:10">
+      <c r="B32" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="G29">
+      <c r="C32" s="34"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="34"/>
+      <c r="G32" s="34">
         <v>30</v>
       </c>
-      <c r="J29" t="s">
+      <c r="H32" s="34"/>
+      <c r="I32" s="34"/>
+      <c r="J32" s="34" t="s">
         <v>33</v>
       </c>
     </row>
@@ -5246,7 +5278,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:15">
-      <c r="J1" s="30" t="s">
+      <c r="J1" s="29" t="s">
         <v>39</v>
       </c>
       <c r="K1" t="s">
@@ -5254,7 +5286,7 @@
       </c>
     </row>
     <row r="2" spans="2:15">
-      <c r="J2" s="31">
+      <c r="J2" s="30">
         <f>AVERAGE(J6:J25)</f>
         <v>0.593551382979919</v>
       </c>
@@ -5332,7 +5364,7 @@
         <f>SHAPES!A8</f>
         <v>1</v>
       </c>
-      <c r="J6" s="31">
+      <c r="J6" s="30">
         <f>SHAPES!D8</f>
         <v>0.938230830558969</v>
       </c>
@@ -5374,7 +5406,7 @@
         <f>SHAPES!A9</f>
         <v>2</v>
       </c>
-      <c r="J7" s="31">
+      <c r="J7" s="30">
         <f>SHAPES!D9</f>
         <v>0.925439283531944</v>
       </c>
@@ -5404,7 +5436,7 @@
         <f>SHAPES!A10</f>
         <v>3</v>
       </c>
-      <c r="J8" s="31">
+      <c r="J8" s="30">
         <f>SHAPES!D10</f>
         <v>0.910128364505219</v>
       </c>
@@ -5434,7 +5466,7 @@
         <f>SHAPES!A11</f>
         <v>4</v>
       </c>
-      <c r="J9" s="31">
+      <c r="J9" s="30">
         <f>SHAPES!D11</f>
         <v>0.891861795425706</v>
       </c>
@@ -5464,7 +5496,7 @@
         <f>SHAPES!A12</f>
         <v>5</v>
       </c>
-      <c r="J10" s="31">
+      <c r="J10" s="30">
         <f>SHAPES!D12</f>
         <v>0.870155573115599</v>
       </c>
@@ -5494,7 +5526,7 @@
         <f>SHAPES!A13</f>
         <v>6</v>
       </c>
-      <c r="J11" s="31">
+      <c r="J11" s="30">
         <f>SHAPES!D13</f>
         <v>0.844486434298216</v>
       </c>
@@ -5524,7 +5556,7 @@
         <f>SHAPES!A14</f>
         <v>7</v>
       </c>
-      <c r="J12" s="31">
+      <c r="J12" s="30">
         <f>SHAPES!D14</f>
         <v>0.814308706204866</v>
       </c>
@@ -5554,7 +5586,7 @@
         <f>SHAPES!A15</f>
         <v>8</v>
       </c>
-      <c r="J13" s="31">
+      <c r="J13" s="30">
         <f>SHAPES!D15</f>
         <v>0.779082860560271</v>
       </c>
@@ -5584,7 +5616,7 @@
         <f>SHAPES!A16</f>
         <v>9</v>
       </c>
-      <c r="J14" s="31">
+      <c r="J14" s="30">
         <f>SHAPES!D16</f>
         <v>0.7383195238711</v>
       </c>
@@ -5614,7 +5646,7 @@
         <f>SHAPES!A17</f>
         <v>10</v>
       </c>
-      <c r="J15" s="31">
+      <c r="J15" s="30">
         <f>SHAPES!D17</f>
         <v>0.691642583607144</v>
       </c>
@@ -5644,7 +5676,7 @@
         <f>SHAPES!A18</f>
         <v>11</v>
       </c>
-      <c r="J16" s="31">
+      <c r="J16" s="30">
         <f>SHAPES!D18</f>
         <v>0.638873803601385</v>
       </c>
@@ -5674,7 +5706,7 @@
         <f>SHAPES!A19</f>
         <v>12</v>
       </c>
-      <c r="J17" s="31">
+      <c r="J17" s="30">
         <f>SHAPES!D19</f>
         <v>0.580138223569736</v>
       </c>
@@ -5704,7 +5736,7 @@
         <f>SHAPES!A20</f>
         <v>13</v>
       </c>
-      <c r="J18" s="31">
+      <c r="J18" s="30">
         <f>SHAPES!D20</f>
         <v>0.515983628855313</v>
       </c>
@@ -5734,7 +5766,7 @@
         <f>SHAPES!A21</f>
         <v>14</v>
       </c>
-      <c r="J19" s="31">
+      <c r="J19" s="30">
         <f>SHAPES!D21</f>
         <v>0.447497806996866</v>
       </c>
@@ -5764,7 +5796,7 @@
         <f>SHAPES!A22</f>
         <v>15</v>
       </c>
-      <c r="J20" s="31">
+      <c r="J20" s="30">
         <f>SHAPES!D22</f>
         <v>0.376394405858965</v>
       </c>
@@ -5794,7 +5826,7 @@
         <f>SHAPES!A23</f>
         <v>16</v>
       </c>
-      <c r="J21" s="31">
+      <c r="J21" s="30">
         <f>SHAPES!D23</f>
         <v>0.305024495274644</v>
       </c>
@@ -5824,7 +5856,7 @@
         <f>SHAPES!A24</f>
         <v>17</v>
       </c>
-      <c r="J22" s="31">
+      <c r="J22" s="30">
         <f>SHAPES!D24</f>
         <v>0.236262757898913</v>
       </c>
@@ -5854,7 +5886,7 @@
         <f>SHAPES!A25</f>
         <v>18</v>
       </c>
-      <c r="J23" s="31">
+      <c r="J23" s="30">
         <f>SHAPES!D25</f>
         <v>0.173225455866289</v>
       </c>
@@ -5884,7 +5916,7 @@
         <f>SHAPES!A26</f>
         <v>19</v>
       </c>
-      <c r="J24" s="31">
+      <c r="J24" s="30">
         <f>SHAPES!D26</f>
         <v>0.118814738805559</v>
       </c>
@@ -5896,7 +5928,7 @@
       <c r="C25" t="s">
         <v>50</v>
       </c>
-      <c r="D25" s="32">
+      <c r="D25" s="31">
         <v>2000</v>
       </c>
       <c r="E25" t="str">
@@ -5913,7 +5945,7 @@
         <f>SHAPES!A27</f>
         <v>20</v>
       </c>
-      <c r="J25" s="31">
+      <c r="J25" s="30">
         <f>SHAPES!D27</f>
         <v>0.0751563871916662</v>
       </c>
@@ -5929,7 +5961,7 @@
         <f>SHAPES!A28</f>
         <v>21</v>
       </c>
-      <c r="J26" s="31">
+      <c r="J26" s="30">
         <f>SHAPES!D28</f>
         <v>0.0430894887796983</v>
       </c>
@@ -5945,7 +5977,7 @@
         <f>SHAPES!A29</f>
         <v>22</v>
       </c>
-      <c r="J27" s="31">
+      <c r="J27" s="30">
         <f>SHAPES!D29</f>
         <v>0.0219260148806106</v>
       </c>
@@ -5961,7 +5993,7 @@
         <f>SHAPES!A30</f>
         <v>23</v>
       </c>
-      <c r="J28" s="31">
+      <c r="J28" s="30">
         <f>SHAPES!D30</f>
         <v>0.00965316125123916</v>
       </c>
@@ -5977,7 +6009,7 @@
         <f>SHAPES!A31</f>
         <v>24</v>
       </c>
-      <c r="J29" s="31">
+      <c r="J29" s="30">
         <v>0</v>
       </c>
     </row>
@@ -5992,7 +6024,7 @@
         <f>SHAPES!A32</f>
         <v>25</v>
       </c>
-      <c r="J30" s="31">
+      <c r="J30" s="30">
         <v>0</v>
       </c>
     </row>
@@ -6007,7 +6039,7 @@
         <f>SHAPES!A33</f>
         <v>26</v>
       </c>
-      <c r="J31" s="31">
+      <c r="J31" s="30">
         <v>0</v>
       </c>
     </row>
@@ -6022,7 +6054,7 @@
         <f>SHAPES!A34</f>
         <v>27</v>
       </c>
-      <c r="J32" s="31">
+      <c r="J32" s="30">
         <v>0</v>
       </c>
     </row>
@@ -6037,7 +6069,7 @@
         <f>SHAPES!A35</f>
         <v>28</v>
       </c>
-      <c r="J33" s="31">
+      <c r="J33" s="30">
         <v>0</v>
       </c>
     </row>
@@ -6052,7 +6084,7 @@
         <f>SHAPES!A36</f>
         <v>29</v>
       </c>
-      <c r="J34" s="31">
+      <c r="J34" s="30">
         <v>0</v>
       </c>
     </row>
@@ -6067,7 +6099,7 @@
         <f>SHAPES!A37</f>
         <v>30</v>
       </c>
-      <c r="J35" s="31">
+      <c r="J35" s="30">
         <v>0</v>
       </c>
     </row>
@@ -6082,7 +6114,7 @@
         <f>SHAPES!A38</f>
         <v>31</v>
       </c>
-      <c r="J36" s="31">
+      <c r="J36" s="30">
         <v>0</v>
       </c>
     </row>
@@ -6097,7 +6129,7 @@
         <f>SHAPES!A39</f>
         <v>32</v>
       </c>
-      <c r="J37" s="31">
+      <c r="J37" s="30">
         <v>0</v>
       </c>
     </row>
@@ -6112,7 +6144,7 @@
         <f>SHAPES!A40</f>
         <v>33</v>
       </c>
-      <c r="J38" s="31">
+      <c r="J38" s="30">
         <v>0</v>
       </c>
     </row>
@@ -6127,7 +6159,7 @@
         <f>SHAPES!A41</f>
         <v>34</v>
       </c>
-      <c r="J39" s="31">
+      <c r="J39" s="30">
         <v>0</v>
       </c>
     </row>
@@ -6142,7 +6174,7 @@
         <f>SHAPES!A42</f>
         <v>35</v>
       </c>
-      <c r="J40" s="31">
+      <c r="J40" s="30">
         <v>0</v>
       </c>
     </row>
@@ -6157,7 +6189,7 @@
         <f>SHAPES!A43</f>
         <v>36</v>
       </c>
-      <c r="J41" s="31">
+      <c r="J41" s="30">
         <v>0</v>
       </c>
     </row>
@@ -6179,7 +6211,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="3:11">
-      <c r="J1" s="30" t="s">
+      <c r="J1" s="29" t="s">
         <v>39</v>
       </c>
       <c r="K1" t="s">
@@ -6447,1332 +6479,1332 @@
   <dimension ref="A4:K57"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="16384" width="9.13636363636364" style="14"/>
+    <col min="1" max="16384" width="9.13636363636364" style="13"/>
   </cols>
   <sheetData>
     <row r="4" spans="1:7">
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="18">
+      <c r="C4" s="17">
         <v>0.192</v>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="17">
         <v>0.195</v>
       </c>
-      <c r="E4" s="18">
+      <c r="E4" s="17">
         <v>0.131</v>
       </c>
-      <c r="F4" s="18">
+      <c r="F4" s="17">
         <v>0.13</v>
       </c>
-      <c r="G4" s="18"/>
+      <c r="G4" s="17"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="17">
         <v>1200</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="17">
         <v>900</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="17">
         <v>21</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="17">
         <v>52</v>
       </c>
-      <c r="G5" s="18"/>
+      <c r="G5" s="17"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="18">
         <f t="shared" ref="C7:F7" si="0">SUM(C8:C32)</f>
         <v>10.0234245384626</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="18">
         <f t="shared" si="0"/>
         <v>11.9503259310896</v>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="18">
         <f t="shared" si="0"/>
         <v>19.9589529077991</v>
       </c>
-      <c r="F7" s="19">
+      <c r="F7" s="18">
         <f t="shared" si="0"/>
         <v>15.0360677410005</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="G7" s="19" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="14">
+      <c r="A8" s="13">
         <v>1</v>
       </c>
-      <c r="B8" s="21">
+      <c r="B8" s="20">
         <v>0.98</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="21">
         <f>(1/(1+EXP(-(50-$A8)*C$4)))^C$5</f>
         <v>0.906219385211314</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="21">
         <f>(1/(1+EXP(-(50-$A8)*D$4)))^D$5</f>
         <v>0.938230830558969</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="21">
         <f>(1/(1+EXP(-(50-$A8)*E$4)))^E$5</f>
         <v>0.966370359922775</v>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="21">
         <f>(1/(1+EXP(-(50-$A8)*F$4)))^F$5</f>
         <v>0.914885692356098</v>
       </c>
-      <c r="G8" s="23"/>
+      <c r="G8" s="22"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="14">
+      <c r="A9" s="13">
         <v>2</v>
       </c>
-      <c r="B9" s="21">
+      <c r="B9" s="20">
         <v>0.970622580135159</v>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="21">
         <f t="shared" ref="C9:F57" si="1">(1/(1+EXP(-(50-$A9)*C$4)))^C$5</f>
         <v>0.887526560438355</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="21">
         <f t="shared" si="1"/>
         <v>0.925439283531944</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="21">
         <f t="shared" si="1"/>
         <v>0.961758676863334</v>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="21">
         <f t="shared" si="1"/>
         <v>0.903667527866718</v>
       </c>
-      <c r="G9" s="23"/>
+      <c r="G9" s="22"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="14">
+      <c r="A10" s="13">
         <v>3</v>
       </c>
-      <c r="B10" s="21">
+      <c r="B10" s="20">
         <v>0.962396435716511</v>
       </c>
-      <c r="C10" s="22">
+      <c r="C10" s="21">
         <f t="shared" si="1"/>
         <v>0.865393324683414</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="21">
         <f t="shared" si="1"/>
         <v>0.910128364505219</v>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="21">
         <f t="shared" si="1"/>
         <v>0.956529615654335</v>
       </c>
-      <c r="F10" s="22">
+      <c r="F10" s="21">
         <f t="shared" si="1"/>
         <v>0.891062569793048</v>
       </c>
-      <c r="G10" s="23"/>
+      <c r="G10" s="22"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="14">
+      <c r="A11" s="13">
         <v>4</v>
       </c>
-      <c r="B11" s="21">
+      <c r="B11" s="20">
         <v>0.962396435716511</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="21">
         <f t="shared" si="1"/>
         <v>0.839314002453786</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="21">
         <f t="shared" si="1"/>
         <v>0.891861795425706</v>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="21">
         <f t="shared" si="1"/>
         <v>0.950604963935119</v>
       </c>
-      <c r="F11" s="22">
+      <c r="F11" s="21">
         <f t="shared" si="1"/>
         <v>0.876925728837395</v>
       </c>
-      <c r="G11" s="23"/>
+      <c r="G11" s="22"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="14">
+      <c r="A12" s="13">
         <v>5</v>
       </c>
-      <c r="B12" s="21">
+      <c r="B12" s="20">
         <v>0.953348946865523</v>
       </c>
-      <c r="C12" s="22">
+      <c r="C12" s="21">
         <f t="shared" si="1"/>
         <v>0.808766111793418</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="21">
         <f t="shared" si="1"/>
         <v>0.870155573115599</v>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="21">
         <f t="shared" si="1"/>
         <v>0.943897915356145</v>
       </c>
-      <c r="F12" s="22">
+      <c r="F12" s="21">
         <f t="shared" si="1"/>
         <v>0.861104397852864</v>
       </c>
-      <c r="G12" s="23"/>
+      <c r="G12" s="22"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="14">
+      <c r="A13" s="13">
         <v>6</v>
       </c>
-      <c r="B13" s="21">
+      <c r="B13" s="20">
         <v>0.946947220933845</v>
       </c>
-      <c r="C13" s="22">
+      <c r="C13" s="21">
         <f t="shared" si="1"/>
         <v>0.773239215092304</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="21">
         <f t="shared" si="1"/>
         <v>0.844486434298216</v>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="21">
         <f t="shared" si="1"/>
         <v>0.936312523381613</v>
       </c>
-      <c r="F13" s="22">
+      <c r="F13" s="21">
         <f t="shared" si="1"/>
         <v>0.843440509350422</v>
       </c>
-      <c r="G13" s="23"/>
+      <c r="G13" s="22"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="14">
+      <c r="A14" s="13">
         <v>7</v>
       </c>
-      <c r="B14" s="21">
+      <c r="B14" s="20">
         <v>0.946947220933845</v>
       </c>
-      <c r="C14" s="22">
+      <c r="C14" s="21">
         <f t="shared" si="1"/>
         <v>0.732278494099783</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="21">
         <f t="shared" si="1"/>
         <v>0.814308706204866</v>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="21">
         <f t="shared" si="1"/>
         <v>0.927743253132952</v>
       </c>
-      <c r="F14" s="22">
+      <c r="F14" s="21">
         <f t="shared" si="1"/>
         <v>0.823773522375577</v>
       </c>
-      <c r="G14" s="23"/>
+      <c r="G14" s="22"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="14">
+      <c r="A15" s="13">
         <v>8</v>
       </c>
-      <c r="B15" s="21">
+      <c r="B15" s="20">
         <v>0.926261114788064</v>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="21">
         <f t="shared" si="1"/>
         <v>0.685546224575631</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="21">
         <f t="shared" si="1"/>
         <v>0.779082860560271</v>
       </c>
-      <c r="E15" s="22">
+      <c r="E15" s="21">
         <f t="shared" si="1"/>
         <v>0.918074687227548</v>
       </c>
-      <c r="F15" s="22">
+      <c r="F15" s="21">
         <f t="shared" si="1"/>
         <v>0.801944546687233</v>
       </c>
-      <c r="G15" s="23"/>
+      <c r="G15" s="22"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="14">
+      <c r="A16" s="13">
         <v>9</v>
       </c>
-      <c r="B16" s="21">
+      <c r="B16" s="20">
         <v>0.898162758045296</v>
       </c>
-      <c r="C16" s="22">
+      <c r="C16" s="21">
         <f t="shared" si="1"/>
         <v>0.632903023475913</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="21">
         <f t="shared" si="1"/>
         <v>0.7383195238711</v>
       </c>
-      <c r="E16" s="22">
+      <c r="E16" s="21">
         <f t="shared" si="1"/>
         <v>0.907181457650145</v>
       </c>
-      <c r="F16" s="22">
+      <c r="F16" s="21">
         <f t="shared" si="1"/>
         <v>0.777801823096523</v>
       </c>
-      <c r="G16" s="23"/>
+      <c r="G16" s="22"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="14">
+      <c r="A17" s="13">
         <v>10</v>
       </c>
-      <c r="B17" s="21">
+      <c r="B17" s="20">
         <v>0.898162758045296</v>
       </c>
-      <c r="C17" s="22">
+      <c r="C17" s="21">
         <f t="shared" si="1"/>
         <v>0.574507650216493</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="21">
         <f t="shared" si="1"/>
         <v>0.691642583607144</v>
       </c>
-      <c r="E17" s="22">
+      <c r="E17" s="21">
         <f t="shared" si="1"/>
         <v>0.894928494661952</v>
       </c>
-      <c r="F17" s="22">
+      <c r="F17" s="21">
         <f t="shared" si="1"/>
         <v>0.751207773296982</v>
       </c>
-      <c r="G17" s="23"/>
+      <c r="G17" s="22"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="14">
+      <c r="A18" s="13">
         <v>11</v>
       </c>
-      <c r="B18" s="21">
+      <c r="B18" s="20">
         <v>0.846189380878412</v>
       </c>
-      <c r="C18" s="22">
+      <c r="C18" s="21">
         <f t="shared" si="1"/>
         <v>0.510928455302216</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="21">
         <f t="shared" si="1"/>
         <v>0.638873803601385</v>
       </c>
-      <c r="E18" s="22">
+      <c r="E18" s="21">
         <f t="shared" si="1"/>
         <v>0.881171705489785</v>
       </c>
-      <c r="F18" s="22">
+      <c r="F18" s="21">
         <f t="shared" si="1"/>
         <v>0.722047800743682</v>
       </c>
-      <c r="G18" s="23"/>
+      <c r="G18" s="22"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="14">
+      <c r="A19" s="13">
         <v>12</v>
       </c>
-      <c r="B19" s="21">
+      <c r="B19" s="20">
         <v>0.836089965568855</v>
       </c>
-      <c r="C19" s="22">
+      <c r="C19" s="21">
         <f t="shared" si="1"/>
         <v>0.443250713618776</v>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="21">
         <f t="shared" si="1"/>
         <v>0.580138223569736</v>
       </c>
-      <c r="E19" s="22">
+      <c r="E19" s="21">
         <f t="shared" si="1"/>
         <v>0.865759219524715</v>
       </c>
-      <c r="F19" s="22">
+      <c r="F19" s="21">
         <f t="shared" si="1"/>
         <v>0.690240953567927</v>
       </c>
-      <c r="G19" s="23"/>
+      <c r="G19" s="22"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="14">
+      <c r="A20" s="13">
         <v>13</v>
       </c>
-      <c r="B20" s="21">
+      <c r="B20" s="20">
         <v>0.785347748818551</v>
       </c>
-      <c r="C20" s="22">
+      <c r="C20" s="21">
         <f t="shared" si="1"/>
         <v>0.373152419091481</v>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="21">
         <f t="shared" si="1"/>
         <v>0.515983628855313</v>
       </c>
-      <c r="E20" s="22">
+      <c r="E20" s="21">
         <f t="shared" si="1"/>
         <v>0.848533361850074</v>
       </c>
-      <c r="F20" s="22">
+      <c r="F20" s="21">
         <f t="shared" si="1"/>
         <v>0.655752436144864</v>
       </c>
-      <c r="G20" s="23"/>
+      <c r="G20" s="22"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="14">
+      <c r="A21" s="13">
         <v>14</v>
       </c>
-      <c r="B21" s="21">
+      <c r="B21" s="20">
         <v>0.765158424624948</v>
       </c>
-      <c r="C21" s="22">
+      <c r="C21" s="21">
         <f t="shared" si="1"/>
         <v>0.302909076264049</v>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="21">
         <f t="shared" si="1"/>
         <v>0.447497806996866</v>
       </c>
-      <c r="E21" s="22">
+      <c r="E21" s="21">
         <f t="shared" si="1"/>
         <v>0.829333541043553</v>
       </c>
-      <c r="F21" s="22">
+      <c r="F21" s="21">
         <f t="shared" si="1"/>
         <v>0.61860776150924</v>
       </c>
-      <c r="G21" s="23"/>
+      <c r="G21" s="22"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="14">
+      <c r="A22" s="13">
         <v>15</v>
       </c>
-      <c r="B22" s="21">
+      <c r="B22" s="20">
         <v>0.722888201491699</v>
       </c>
-      <c r="C22" s="22">
+      <c r="C22" s="21">
         <f t="shared" si="1"/>
         <v>0.23528138033045</v>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="21">
         <f t="shared" si="1"/>
         <v>0.376394405858965</v>
       </c>
-      <c r="E22" s="22">
+      <c r="E22" s="21">
         <f t="shared" si="1"/>
         <v>0.808000257000151</v>
       </c>
-      <c r="F22" s="22">
+      <c r="F22" s="21">
         <f t="shared" si="1"/>
         <v>0.578908057444174</v>
       </c>
-      <c r="G22" s="23"/>
+      <c r="G22" s="22"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="14">
+      <c r="A23" s="13">
         <v>16</v>
       </c>
-      <c r="B23" s="21">
+      <c r="B23" s="20">
         <v>0.662206654111213</v>
       </c>
-      <c r="C23" s="22">
+      <c r="C23" s="21">
         <f t="shared" si="1"/>
         <v>0.1732480236977</v>
       </c>
-      <c r="D23" s="22">
+      <c r="D23" s="21">
         <f t="shared" si="1"/>
         <v>0.305024495274644</v>
       </c>
-      <c r="E23" s="22">
+      <c r="E23" s="21">
         <f t="shared" si="1"/>
         <v>0.784380444928941</v>
       </c>
-      <c r="F23" s="22">
+      <c r="F23" s="21">
         <f t="shared" si="1"/>
         <v>0.536845665869112</v>
       </c>
-      <c r="G23" s="23"/>
+      <c r="G23" s="22"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="14">
+      <c r="A24" s="13">
         <v>17</v>
       </c>
-      <c r="B24" s="21">
+      <c r="B24" s="20">
         <v>0.623093147917535</v>
       </c>
-      <c r="C24" s="22">
+      <c r="C24" s="21">
         <f t="shared" si="1"/>
         <v>0.11958021751459</v>
       </c>
-      <c r="D24" s="22">
+      <c r="D24" s="21">
         <f t="shared" si="1"/>
         <v>0.236262757898913</v>
       </c>
-      <c r="E24" s="22">
+      <c r="E24" s="21">
         <f t="shared" si="1"/>
         <v>0.75833436545842</v>
       </c>
-      <c r="F24" s="22">
+      <c r="F24" s="21">
         <f t="shared" si="1"/>
         <v>0.492718712520419</v>
       </c>
-      <c r="G24" s="23"/>
+      <c r="G24" s="22"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="14">
+      <c r="A25" s="13">
         <v>18</v>
       </c>
-      <c r="B25" s="21">
+      <c r="B25" s="20">
         <v>0.537592092285781</v>
       </c>
-      <c r="C25" s="22">
+      <c r="C25" s="21">
         <f t="shared" si="1"/>
         <v>0.0763196147056263</v>
       </c>
-      <c r="D25" s="22">
+      <c r="D25" s="21">
         <f t="shared" si="1"/>
         <v>0.173225455866289</v>
       </c>
-      <c r="E25" s="22">
+      <c r="E25" s="21">
         <f t="shared" si="1"/>
         <v>0.729744218200363</v>
       </c>
-      <c r="F25" s="22">
+      <c r="F25" s="21">
         <f t="shared" si="1"/>
         <v>0.446942799578822</v>
       </c>
-      <c r="G25" s="23"/>
+      <c r="G25" s="22"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="14">
+      <c r="A26" s="13">
         <v>19</v>
       </c>
-      <c r="B26" s="21">
+      <c r="B26" s="20">
         <v>0.474189219095591</v>
       </c>
-      <c r="C26" s="22">
+      <c r="C26" s="21">
         <f t="shared" si="1"/>
         <v>0.0443026892620923</v>
       </c>
-      <c r="D26" s="22">
+      <c r="D26" s="21">
         <f t="shared" si="1"/>
         <v>0.118814738805559</v>
       </c>
-      <c r="E26" s="22">
+      <c r="E26" s="21">
         <f t="shared" si="1"/>
         <v>0.698524584808679</v>
       </c>
-      <c r="F26" s="22">
+      <c r="F26" s="21">
         <f t="shared" si="1"/>
         <v>0.400057451000559</v>
       </c>
-      <c r="G26" s="23"/>
+      <c r="G26" s="22"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="14">
+      <c r="A27" s="13">
         <v>20</v>
       </c>
-      <c r="B27" s="21">
+      <c r="B27" s="20">
         <v>0.422091220937619</v>
       </c>
-      <c r="C27" s="22">
+      <c r="C27" s="21">
         <f t="shared" si="1"/>
         <v>0.0229281766898145</v>
       </c>
-      <c r="D27" s="22">
+      <c r="D27" s="21">
         <f t="shared" si="1"/>
         <v>0.0751563871916662</v>
       </c>
-      <c r="E27" s="22">
+      <c r="E27" s="21">
         <f t="shared" si="1"/>
         <v>0.664634682968127</v>
       </c>
-      <c r="F27" s="22">
+      <c r="F27" s="21">
         <f t="shared" si="1"/>
         <v>0.352724529092067</v>
       </c>
-      <c r="G27" s="23"/>
+      <c r="G27" s="22"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="14">
+      <c r="A28" s="13">
         <v>21</v>
       </c>
-      <c r="B28" s="21">
+      <c r="B28" s="20">
         <v>0.346971016058413</v>
       </c>
-      <c r="C28" s="22">
+      <c r="C28" s="21">
         <f t="shared" si="1"/>
         <v>0.0103268678591589</v>
       </c>
-      <c r="D28" s="22">
+      <c r="D28" s="21">
         <f t="shared" si="1"/>
         <v>0.0430894887796983</v>
       </c>
-      <c r="E28" s="22">
+      <c r="E28" s="21">
         <f t="shared" si="1"/>
         <v>0.628092219448125</v>
       </c>
-      <c r="F28" s="22">
+      <c r="F28" s="21">
         <f t="shared" si="1"/>
         <v>0.305715704765527</v>
       </c>
-      <c r="G28" s="23"/>
+      <c r="G28" s="22"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="14">
+      <c r="A29" s="13">
         <v>22</v>
       </c>
-      <c r="B29" s="21">
+      <c r="B29" s="20">
         <v>0.293064361762058</v>
       </c>
-      <c r="C29" s="22">
+      <c r="C29" s="21">
         <f t="shared" si="1"/>
         <v>0.00393145344541023</v>
       </c>
-      <c r="D29" s="22">
+      <c r="D29" s="21">
         <f t="shared" si="1"/>
         <v>0.0219260148806106</v>
       </c>
-      <c r="E29" s="22">
+      <c r="E29" s="21">
         <f t="shared" si="1"/>
         <v>0.588988354885599</v>
       </c>
-      <c r="F29" s="22">
+      <c r="F29" s="21">
         <f t="shared" si="1"/>
         <v>0.25988641177864</v>
       </c>
-      <c r="G29" s="23"/>
+      <c r="G29" s="22"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="14">
+      <c r="A30" s="13">
         <v>23</v>
       </c>
-      <c r="B30" s="21">
+      <c r="B30" s="20">
         <v>0.232858040357466</v>
       </c>
-      <c r="C30" s="22">
+      <c r="C30" s="21">
         <f t="shared" si="1"/>
         <v>0.00122126980138214</v>
       </c>
-      <c r="D30" s="22">
+      <c r="D30" s="21">
         <f t="shared" si="1"/>
         <v>0.00965316125123916</v>
       </c>
-      <c r="E30" s="22">
+      <c r="E30" s="21">
         <f t="shared" si="1"/>
         <v>0.547502928572496</v>
       </c>
-      <c r="F30" s="22">
+      <c r="F30" s="21">
         <f t="shared" si="1"/>
         <v>0.216134768758909</v>
       </c>
-      <c r="G30" s="23"/>
+      <c r="G30" s="22"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="14">
+      <c r="A31" s="13">
         <v>24</v>
       </c>
-      <c r="B31" s="21">
+      <c r="B31" s="20">
         <v>0.190942528947818</v>
       </c>
-      <c r="C31" s="22">
+      <c r="C31" s="21">
         <f t="shared" si="1"/>
         <v>0.000296659508114373</v>
       </c>
-      <c r="D31" s="22">
+      <c r="D31" s="21">
         <f t="shared" si="1"/>
         <v>0.00356535659104143</v>
       </c>
-      <c r="E31" s="22">
+      <c r="E31" s="21">
         <f t="shared" si="1"/>
         <v>0.503918645433383</v>
       </c>
-      <c r="F31" s="22">
+      <c r="F31" s="21">
         <f t="shared" si="1"/>
         <v>0.17534587855983</v>
       </c>
-      <c r="G31" s="23"/>
+      <c r="G31" s="22"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="14">
+      <c r="A32" s="13">
         <v>25</v>
       </c>
-      <c r="B32" s="21">
+      <c r="B32" s="20">
         <v>0.164653096923697</v>
       </c>
-      <c r="C32" s="22">
+      <c r="C32" s="21">
         <f t="shared" si="1"/>
         <v>5.35293312880216e-5</v>
       </c>
-      <c r="D32" s="22">
+      <c r="D32" s="21">
         <f t="shared" si="1"/>
         <v>0.00106424998867156</v>
       </c>
-      <c r="E32" s="22">
+      <c r="E32" s="21">
         <f t="shared" si="1"/>
         <v>0.458632430400759</v>
       </c>
-      <c r="F32" s="22">
+      <c r="F32" s="21">
         <f t="shared" si="1"/>
         <v>0.138324718153866</v>
       </c>
-      <c r="G32" s="23"/>
+      <c r="G32" s="22"/>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="14">
+      <c r="A33" s="13">
         <v>26</v>
       </c>
-      <c r="B33" s="21">
+      <c r="B33" s="20">
         <v>0.148868327448333</v>
       </c>
-      <c r="C33" s="22">
+      <c r="C33" s="21">
         <f t="shared" si="1"/>
         <v>6.74423475754726e-6</v>
       </c>
-      <c r="D33" s="22">
+      <c r="D33" s="21">
         <f t="shared" si="1"/>
         <v>0.000245403816057935</v>
       </c>
-      <c r="E33" s="22">
+      <c r="E33" s="21">
         <f t="shared" si="1"/>
         <v>0.412161672924921</v>
       </c>
-      <c r="F33" s="22">
+      <c r="F33" s="21">
         <f t="shared" si="1"/>
         <v>0.105724230407663</v>
       </c>
-      <c r="G33" s="23"/>
+      <c r="G33" s="22"/>
     </row>
     <row r="34" spans="1:11">
-      <c r="A34" s="14">
+      <c r="A34" s="13">
         <v>27</v>
       </c>
-      <c r="B34" s="21">
+      <c r="B34" s="20">
         <v>0.11454490726822</v>
       </c>
-      <c r="C34" s="22">
+      <c r="C34" s="21">
         <f t="shared" si="1"/>
         <v>5.50705105352367e-7</v>
       </c>
-      <c r="D34" s="22">
+      <c r="D34" s="21">
         <f t="shared" si="1"/>
         <v>4.13929618796038e-5</v>
       </c>
-      <c r="E34" s="22">
+      <c r="E34" s="21">
         <f t="shared" si="1"/>
         <v>0.365142725874107</v>
       </c>
-      <c r="F34" s="22">
+      <c r="F34" s="21">
         <f t="shared" si="1"/>
         <v>0.0779785453058308</v>
       </c>
-      <c r="G34" s="23"/>
+      <c r="G34" s="22"/>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="14">
+      <c r="A35" s="13">
         <v>28</v>
       </c>
-      <c r="B35" s="21">
+      <c r="B35" s="20">
         <v>0.103054577939045</v>
       </c>
-      <c r="C35" s="22">
+      <c r="C35" s="21">
         <f t="shared" si="1"/>
         <v>2.6646577225688e-8</v>
       </c>
-      <c r="D35" s="22">
+      <c r="D35" s="21">
         <f t="shared" si="1"/>
         <v>4.78188415507316e-6</v>
       </c>
-      <c r="E35" s="22">
+      <c r="E35" s="21">
         <f t="shared" si="1"/>
         <v>0.318318944915169</v>
       </c>
-      <c r="F35" s="22">
+      <c r="F35" s="21">
         <f t="shared" si="1"/>
         <v>0.0552534242125428</v>
       </c>
-      <c r="G35" s="23"/>
+      <c r="G35" s="22"/>
     </row>
     <row r="36" ht="15.25" spans="1:11">
-      <c r="A36" s="14">
+      <c r="A36" s="13">
         <v>29</v>
       </c>
-      <c r="B36" s="21">
+      <c r="B36" s="20">
         <v>0.0950979000353695</v>
       </c>
-      <c r="C36" s="22">
+      <c r="C36" s="21">
         <f t="shared" si="1"/>
         <v>6.86109253935805e-10</v>
       </c>
-      <c r="D36" s="22">
+      <c r="D36" s="21">
         <f t="shared" si="1"/>
         <v>3.49520200309893e-7</v>
       </c>
-      <c r="E36" s="22">
+      <c r="E36" s="21">
         <f t="shared" si="1"/>
         <v>0.272515947885678</v>
       </c>
-      <c r="F36" s="22">
+      <c r="F36" s="21">
         <f t="shared" si="1"/>
         <v>0.0374257781970897</v>
       </c>
-      <c r="G36" s="23"/>
+      <c r="G36" s="22"/>
     </row>
     <row r="37" ht="15.5" spans="1:11">
-      <c r="A37" s="14">
+      <c r="A37" s="13">
         <v>30</v>
       </c>
-      <c r="B37" s="21">
+      <c r="B37" s="20">
         <v>0.0950979000353695</v>
       </c>
-      <c r="C37" s="22">
+      <c r="C37" s="21">
         <f t="shared" si="1"/>
         <v>8.2645524853028e-12</v>
       </c>
-      <c r="D37" s="22">
+      <c r="D37" s="21">
         <f t="shared" si="1"/>
         <v>1.46945298074594e-8</v>
       </c>
-      <c r="E37" s="22">
+      <c r="E37" s="21">
         <f t="shared" si="1"/>
         <v>0.228602829015039</v>
       </c>
-      <c r="F37" s="22">
+      <c r="F37" s="21">
         <f t="shared" si="1"/>
         <v>0.024100468898179</v>
       </c>
-      <c r="G37" s="23"/>
-      <c r="I37" s="24">
+      <c r="G37" s="22"/>
+      <c r="I37" s="23">
         <v>20</v>
       </c>
-      <c r="J37" s="25" t="s">
+      <c r="J37" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="K37" s="26"/>
+      <c r="K37" s="25"/>
     </row>
     <row r="38" ht="16.25" spans="1:11">
-      <c r="A38" s="14">
+      <c r="A38" s="13">
         <v>31</v>
       </c>
-      <c r="B38" s="21">
+      <c r="B38" s="20">
         <v>0.0794965091942965</v>
       </c>
-      <c r="C38" s="22">
+      <c r="C38" s="21">
         <f t="shared" si="1"/>
         <v>3.99248227801898e-14</v>
       </c>
-      <c r="D38" s="22">
+      <c r="D38" s="21">
         <f t="shared" si="1"/>
         <v>3.16957251470982e-10</v>
       </c>
-      <c r="E38" s="22">
+      <c r="E38" s="21">
         <f t="shared" si="1"/>
         <v>0.1874399026682</v>
       </c>
-      <c r="F38" s="22">
+      <c r="F38" s="21">
         <f t="shared" si="1"/>
         <v>0.0146654724946527</v>
       </c>
-      <c r="G38" s="23"/>
-      <c r="I38" s="27">
+      <c r="G38" s="22"/>
+      <c r="I38" s="26">
         <v>15</v>
       </c>
-      <c r="J38" s="28" t="s">
+      <c r="J38" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="K38" s="29"/>
+      <c r="K38" s="28"/>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" s="14">
+      <c r="A39" s="13">
         <v>32</v>
       </c>
-      <c r="B39" s="21">
+      <c r="B39" s="20">
         <v>0.0568420433598065</v>
       </c>
-      <c r="C39" s="22">
+      <c r="C39" s="21">
         <f t="shared" si="1"/>
         <v>6.43818749795908e-17</v>
       </c>
-      <c r="D39" s="22">
+      <c r="D39" s="21">
         <f t="shared" si="1"/>
         <v>3.05927625547114e-12</v>
       </c>
-      <c r="E39" s="22">
+      <c r="E39" s="21">
         <f t="shared" si="1"/>
         <v>0.149816134662246</v>
       </c>
-      <c r="F39" s="22">
+      <c r="F39" s="21">
         <f t="shared" si="1"/>
         <v>0.00837724347223734</v>
       </c>
-      <c r="G39" s="23"/>
+      <c r="G39" s="22"/>
     </row>
     <row r="40" spans="1:11">
-      <c r="A40" s="14">
+      <c r="A40" s="13">
         <v>33</v>
       </c>
-      <c r="B40" s="21">
+      <c r="B40" s="20">
         <v>0.0542540888865057</v>
       </c>
-      <c r="C40" s="22">
+      <c r="C40" s="21">
         <f t="shared" si="1"/>
         <v>2.78692808868817e-20</v>
       </c>
-      <c r="D40" s="22">
+      <c r="D40" s="21">
         <f t="shared" si="1"/>
         <v>1.12256021557371e-14</v>
       </c>
-      <c r="E40" s="22">
+      <c r="E40" s="21">
         <f t="shared" si="1"/>
         <v>0.116382437982868</v>
       </c>
-      <c r="F40" s="22">
+      <c r="F40" s="21">
         <f t="shared" si="1"/>
         <v>0.00445960432889931</v>
       </c>
-      <c r="G40" s="23"/>
+      <c r="G40" s="22"/>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" s="14">
+      <c r="A41" s="13">
         <v>34</v>
       </c>
-      <c r="B41" s="21">
+      <c r="B41" s="20">
         <v>0.0542540888865057</v>
       </c>
-      <c r="C41" s="22">
+      <c r="C41" s="21">
         <f t="shared" si="1"/>
         <v>2.50254185482109e-24</v>
       </c>
-      <c r="D41" s="22">
+      <c r="D41" s="21">
         <f t="shared" si="1"/>
         <v>1.29036644913749e-17</v>
       </c>
-      <c r="E41" s="22">
+      <c r="E41" s="21">
         <f t="shared" si="1"/>
         <v>0.0875898228328662</v>
       </c>
-      <c r="F41" s="22">
+      <c r="F41" s="21">
         <f t="shared" si="1"/>
         <v>0.00219517829753202</v>
       </c>
-      <c r="G41" s="23"/>
+      <c r="G41" s="22"/>
     </row>
     <row r="42" spans="1:11">
-      <c r="A42" s="14">
+      <c r="A42" s="13">
         <v>35</v>
       </c>
-      <c r="B42" s="21">
+      <c r="B42" s="20">
         <v>0.0542540888865057</v>
       </c>
-      <c r="C42" s="22">
+      <c r="C42" s="21">
         <f t="shared" si="1"/>
         <v>3.44187211361019e-29</v>
       </c>
-      <c r="D42" s="22">
+      <c r="D42" s="21">
         <f t="shared" si="1"/>
         <v>3.69671135557014e-21</v>
       </c>
-      <c r="E42" s="22">
+      <c r="E42" s="21">
         <f t="shared" si="1"/>
         <v>0.0636430653415445</v>
       </c>
-      <c r="F42" s="22">
+      <c r="F42" s="21">
         <f t="shared" si="1"/>
         <v>0.000990702863321507</v>
       </c>
-      <c r="G42" s="23"/>
+      <c r="G42" s="22"/>
     </row>
     <row r="43" spans="1:11">
-      <c r="A43" s="14">
+      <c r="A43" s="13">
         <v>36</v>
       </c>
-      <c r="B43" s="21">
+      <c r="B43" s="20">
         <v>0.0453752228971555</v>
       </c>
-      <c r="C43" s="22">
+      <c r="C43" s="21">
         <f t="shared" si="1"/>
         <v>5.08488119352033e-35</v>
       </c>
-      <c r="D43" s="22">
+      <c r="D43" s="21">
         <f t="shared" si="1"/>
         <v>2.01780834205926e-25</v>
       </c>
-      <c r="E43" s="22">
+      <c r="E43" s="21">
         <f t="shared" si="1"/>
         <v>0.0444800833434214</v>
       </c>
-      <c r="F43" s="22">
+      <c r="F43" s="21">
         <f t="shared" si="1"/>
         <v>0.000406238313725398</v>
       </c>
-      <c r="G43" s="23"/>
+      <c r="G43" s="22"/>
     </row>
     <row r="44" spans="1:11">
-      <c r="A44" s="14">
+      <c r="A44" s="13">
         <v>37</v>
       </c>
-      <c r="B44" s="21">
+      <c r="B44" s="20">
         <v>0.0330173163442898</v>
       </c>
-      <c r="C44" s="22">
+      <c r="C44" s="21">
         <f t="shared" si="1"/>
         <v>5.34466962894203e-42</v>
       </c>
-      <c r="D44" s="22">
+      <c r="D44" s="21">
         <f t="shared" si="1"/>
         <v>1.5342782793287e-30</v>
       </c>
-      <c r="E44" s="22">
+      <c r="E44" s="21">
         <f t="shared" si="1"/>
         <v>0.0297838898972336</v>
       </c>
-      <c r="F44" s="22">
+      <c r="F44" s="21">
         <f t="shared" si="1"/>
         <v>0.000149900948741295</v>
       </c>
-      <c r="G44" s="23"/>
+      <c r="G44" s="22"/>
     </row>
     <row r="45" spans="1:11">
-      <c r="A45" s="14">
+      <c r="A45" s="13">
         <v>38</v>
       </c>
-      <c r="B45" s="21">
+      <c r="B45" s="20">
         <v>0.0330173163442898</v>
       </c>
-      <c r="C45" s="22">
+      <c r="C45" s="21">
         <f t="shared" si="1"/>
         <v>2.48753719707069e-50</v>
       </c>
-      <c r="D45" s="22">
+      <c r="D45" s="21">
         <f t="shared" si="1"/>
         <v>1.13154945051616e-36</v>
       </c>
-      <c r="E45" s="22">
+      <c r="E45" s="21">
         <f t="shared" si="1"/>
         <v>0.0190279481314734</v>
       </c>
-      <c r="F45" s="22">
+      <c r="F45" s="21">
         <f t="shared" si="1"/>
         <v>4.92743912646851e-5</v>
       </c>
-      <c r="G45" s="23"/>
+      <c r="G45" s="22"/>
     </row>
     <row r="46" spans="1:11">
-      <c r="A46" s="14">
+      <c r="A46" s="13">
         <v>39</v>
       </c>
-      <c r="B46" s="21">
+      <c r="B46" s="20">
         <v>0.031841483991343</v>
       </c>
-      <c r="C46" s="22">
+      <c r="C46" s="21">
         <f t="shared" si="1"/>
         <v>2.98709273777631e-60</v>
       </c>
-      <c r="D46" s="22">
+      <c r="D46" s="21">
         <f t="shared" si="1"/>
         <v>5.34979488148274e-44</v>
       </c>
-      <c r="E46" s="22">
+      <c r="E46" s="21">
         <f t="shared" si="1"/>
         <v>0.011548223188478</v>
       </c>
-      <c r="F46" s="22">
+      <c r="F46" s="21">
         <f t="shared" si="1"/>
         <v>1.42778241771178e-5</v>
       </c>
-      <c r="G46" s="23"/>
+      <c r="G46" s="22"/>
     </row>
     <row r="47" spans="1:11">
-      <c r="A47" s="14">
+      <c r="A47" s="13">
         <v>40</v>
       </c>
-      <c r="B47" s="21">
+      <c r="B47" s="20">
         <v>0.0289468036284937</v>
       </c>
-      <c r="C47" s="22">
+      <c r="C47" s="21">
         <f t="shared" si="1"/>
         <v>5.04092981981214e-72</v>
       </c>
-      <c r="D47" s="22">
+      <c r="D47" s="21">
         <f t="shared" si="1"/>
         <v>1.0155773516225e-52</v>
       </c>
-      <c r="E47" s="22">
+      <c r="E47" s="21">
         <f t="shared" si="1"/>
         <v>0.00662848337086842</v>
       </c>
-      <c r="F47" s="22">
+      <c r="F47" s="21">
         <f t="shared" si="1"/>
         <v>3.60770183438638e-6</v>
       </c>
-      <c r="G47" s="23"/>
+      <c r="G47" s="22"/>
     </row>
     <row r="48" spans="1:11">
-      <c r="A48" s="14">
+      <c r="A48" s="13">
         <v>41</v>
       </c>
-      <c r="B48" s="21">
+      <c r="B48" s="20">
         <v>0.0260521232656443</v>
       </c>
-      <c r="C48" s="22">
+      <c r="C48" s="21">
         <f t="shared" si="1"/>
         <v>6.09869056937694e-86</v>
       </c>
-      <c r="D48" s="22">
+      <c r="D48" s="21">
         <f t="shared" si="1"/>
         <v>4.59937564837077e-63</v>
       </c>
-      <c r="E48" s="22">
+      <c r="E48" s="21">
         <f t="shared" si="1"/>
         <v>0.00358198121587089</v>
       </c>
-      <c r="F48" s="22">
+      <c r="F48" s="21">
         <f t="shared" si="1"/>
         <v>7.86262836388685e-7</v>
       </c>
-      <c r="G48" s="23"/>
+      <c r="G48" s="22"/>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="14">
+      <c r="A49" s="13">
         <v>42</v>
       </c>
-      <c r="B49" s="21">
+      <c r="B49" s="20">
         <v>0.0231574429027949</v>
       </c>
-      <c r="C49" s="22">
+      <c r="C49" s="21">
         <f t="shared" si="1"/>
         <v>2.54322977557799e-102</v>
       </c>
-      <c r="D49" s="22">
+      <c r="D49" s="21">
         <f t="shared" si="1"/>
         <v>2.81328835742251e-75</v>
       </c>
-      <c r="E49" s="22">
+      <c r="E49" s="21">
         <f t="shared" si="1"/>
         <v>0.00181417657127675</v>
       </c>
-      <c r="F49" s="22">
+      <c r="F49" s="21">
         <f t="shared" si="1"/>
         <v>1.46193015454287e-7</v>
       </c>
-      <c r="G49" s="23"/>
+      <c r="G49" s="22"/>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" s="14">
+      <c r="A50" s="13">
         <v>43</v>
       </c>
-      <c r="B50" s="21">
+      <c r="B50" s="20">
         <v>0.0202627625399456</v>
       </c>
-      <c r="C50" s="22">
+      <c r="C50" s="21">
         <f t="shared" si="1"/>
         <v>1.67650027026223e-121</v>
       </c>
-      <c r="D50" s="22">
+      <c r="D50" s="21">
         <f t="shared" si="1"/>
         <v>1.26504110236933e-89</v>
       </c>
-      <c r="E50" s="22">
+      <c r="E50" s="21">
         <f t="shared" si="1"/>
         <v>0.000857351614537152</v>
       </c>
-      <c r="F50" s="22">
+      <c r="F50" s="21">
         <f t="shared" si="1"/>
         <v>2.29435548157318e-8</v>
       </c>
-      <c r="G50" s="23"/>
+      <c r="G50" s="22"/>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="14">
+      <c r="A51" s="13">
         <v>44</v>
       </c>
-      <c r="B51" s="21">
+      <c r="B51" s="20">
         <v>0.0173680821770962</v>
       </c>
-      <c r="C51" s="22">
+      <c r="C51" s="21">
         <f t="shared" si="1"/>
         <v>7.78570335510438e-144</v>
       </c>
-      <c r="D51" s="22">
+      <c r="D51" s="21">
         <f t="shared" si="1"/>
         <v>2.22006086811815e-106</v>
       </c>
-      <c r="E51" s="22">
+      <c r="E51" s="21">
         <f t="shared" si="1"/>
         <v>0.000376458594281512</v>
       </c>
-      <c r="F51" s="22">
+      <c r="F51" s="21">
         <f t="shared" si="1"/>
         <v>3.00829776838304e-9</v>
       </c>
-      <c r="G51" s="23"/>
+      <c r="G51" s="22"/>
     </row>
     <row r="52" spans="1:7">
-      <c r="A52" s="14">
+      <c r="A52" s="13">
         <v>45</v>
       </c>
-      <c r="B52" s="21">
+      <c r="B52" s="20">
         <v>0.0144734018142468</v>
       </c>
-      <c r="C52" s="22">
+      <c r="C52" s="21">
         <f t="shared" si="1"/>
         <v>1.13174612312143e-169</v>
       </c>
-      <c r="D52" s="22">
+      <c r="D52" s="21">
         <f t="shared" si="1"/>
         <v>8.03262555274651e-126</v>
       </c>
-      <c r="E52" s="22">
+      <c r="E52" s="21">
         <f t="shared" si="1"/>
         <v>0.000152979402302229</v>
       </c>
-      <c r="F52" s="22">
+      <c r="F52" s="21">
         <f t="shared" si="1"/>
         <v>3.26406539912992e-10</v>
       </c>
-      <c r="G52" s="23"/>
+      <c r="G52" s="22"/>
     </row>
     <row r="53" spans="1:7">
-      <c r="A53" s="14">
+      <c r="A53" s="13">
         <v>46</v>
       </c>
-      <c r="B53" s="21">
+      <c r="B53" s="20">
         <v>0.0115787214513975</v>
       </c>
-      <c r="C53" s="22">
+      <c r="C53" s="21">
         <f t="shared" si="1"/>
         <v>2.35537253900522e-199</v>
       </c>
-      <c r="D53" s="22">
+      <c r="D53" s="21">
         <f t="shared" si="1"/>
         <v>3.23146037062183e-148</v>
       </c>
-      <c r="E53" s="22">
+      <c r="E53" s="21">
         <f t="shared" si="1"/>
         <v>5.73260931245053e-5</v>
       </c>
-      <c r="F53" s="22">
+      <c r="F53" s="21">
         <f t="shared" si="1"/>
         <v>2.90558610240178e-11</v>
       </c>
-      <c r="G53" s="23"/>
+      <c r="G53" s="22"/>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="14">
+      <c r="A54" s="13">
         <v>47</v>
       </c>
-      <c r="B54" s="21">
+      <c r="B54" s="20">
         <v>0.00868404108854809</v>
       </c>
-      <c r="C54" s="22">
+      <c r="C54" s="21">
         <f t="shared" si="1"/>
         <v>3.42957733088786e-233</v>
       </c>
-      <c r="D54" s="22">
+      <c r="D54" s="21">
         <f t="shared" si="1"/>
         <v>8.19736610112632e-174</v>
       </c>
-      <c r="E54" s="22">
+      <c r="E54" s="21">
         <f t="shared" si="1"/>
         <v>1.97484236454548e-5</v>
       </c>
-      <c r="F54" s="22">
+      <c r="F54" s="21">
         <f t="shared" si="1"/>
         <v>2.10627395377568e-12</v>
       </c>
-      <c r="G54" s="23"/>
+      <c r="G54" s="22"/>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="14">
+      <c r="A55" s="13">
         <v>48</v>
       </c>
-      <c r="B55" s="21">
+      <c r="B55" s="20">
         <v>0.00578936072569872</v>
       </c>
-      <c r="C55" s="22">
+      <c r="C55" s="21">
         <f t="shared" si="1"/>
         <v>1.89670438496799e-271</v>
       </c>
-      <c r="D55" s="22">
+      <c r="D55" s="21">
         <f t="shared" si="1"/>
         <v>8.07212567278304e-203</v>
       </c>
-      <c r="E55" s="22">
+      <c r="E55" s="21">
         <f t="shared" si="1"/>
         <v>6.23851575799832e-6</v>
       </c>
-      <c r="F55" s="22">
+      <c r="F55" s="21">
         <f t="shared" si="1"/>
         <v>1.23588203550676e-13</v>
       </c>
-      <c r="G55" s="23"/>
+      <c r="G55" s="22"/>
     </row>
     <row r="56" spans="1:7">
-      <c r="A56" s="14">
+      <c r="A56" s="13">
         <v>49</v>
       </c>
-      <c r="B56" s="21">
+      <c r="B56" s="20">
         <v>0.00289468036284934</v>
       </c>
-      <c r="C56" s="22">
+      <c r="C56" s="21">
         <f t="shared" si="1"/>
         <v>2.49421781354134e-314</v>
       </c>
-      <c r="D56" s="22">
+      <c r="D56" s="21">
         <f t="shared" si="1"/>
         <v>2.12544751796573e-235</v>
       </c>
-      <c r="E56" s="22">
+      <c r="E56" s="21">
         <f t="shared" si="1"/>
         <v>1.80381580962101e-6</v>
       </c>
-      <c r="F56" s="22">
+      <c r="F56" s="21">
         <f t="shared" si="1"/>
         <v>5.84361885257411e-15</v>
       </c>
-      <c r="G56" s="23"/>
+      <c r="G56" s="22"/>
     </row>
     <row r="57" spans="1:7">
-      <c r="A57" s="14">
+      <c r="A57" s="13">
         <v>50</v>
       </c>
-      <c r="B57" s="21">
+      <c r="B57" s="20">
         <v>0</v>
       </c>
-      <c r="C57" s="22">
+      <c r="C57" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D57" s="22">
+      <c r="D57" s="21">
         <f t="shared" si="1"/>
         <v>1.18305218616677e-271</v>
       </c>
-      <c r="E57" s="22">
+      <c r="E57" s="21">
         <f t="shared" si="1"/>
         <v>4.76837158203125e-7</v>
       </c>
-      <c r="F57" s="22">
+      <c r="F57" s="21">
         <f t="shared" si="1"/>
         <v>2.22044604925031e-16</v>
       </c>
-      <c r="G57" s="23"/>
+      <c r="G57" s="22"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7855,27 +7887,27 @@
       </c>
     </row>
     <row r="14" ht="14.5" spans="2:9">
-      <c r="C14" s="13"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
     </row>
     <row r="15" ht="14.5" spans="2:9">
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="I15" s="15"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="I15" s="14"/>
     </row>
     <row r="16" ht="14.5" spans="2:9">
       <c r="B16" t="s">
         <v>75</v>
       </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="I16" s="15"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="I16" s="14"/>
     </row>
     <row r="17" spans="2:8">
       <c r="B17" t="s">
@@ -7996,7 +8028,7 @@
       <c r="F31" t="s">
         <v>73</v>
       </c>
-      <c r="H31" s="16" t="s">
+      <c r="H31" s="15" t="s">
         <v>88</v>
       </c>
     </row>
@@ -8013,395 +8045,395 @@
   <dimension ref="A1:L18"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="2" width="9.13636363636364" style="6"/>
-    <col min="3" max="3" width="26" style="6" customWidth="1"/>
-    <col min="4" max="4" width="11.8636363636364" style="6" customWidth="1"/>
-    <col min="5" max="5" width="7.72727272727273" style="6" customWidth="1"/>
-    <col min="6" max="6" width="8.26363636363636" style="6" customWidth="1"/>
-    <col min="7" max="7" width="26" style="6" customWidth="1"/>
-    <col min="8" max="8" width="9.6" style="6" customWidth="1"/>
-    <col min="9" max="9" width="9.13636363636364" style="6"/>
-    <col min="10" max="10" width="6.86363636363636" style="6" customWidth="1"/>
-    <col min="11" max="16384" width="9.13636363636364" style="6"/>
+    <col min="1" max="2" width="9.13636363636364" style="5"/>
+    <col min="3" max="3" width="26" style="5" customWidth="1"/>
+    <col min="4" max="4" width="11.8636363636364" style="5" customWidth="1"/>
+    <col min="5" max="5" width="7.72727272727273" style="5" customWidth="1"/>
+    <col min="6" max="6" width="8.26363636363636" style="5" customWidth="1"/>
+    <col min="7" max="7" width="26" style="5" customWidth="1"/>
+    <col min="8" max="8" width="9.6" style="5" customWidth="1"/>
+    <col min="9" max="9" width="9.13636363636364" style="5"/>
+    <col min="10" max="10" width="6.86363636363636" style="5" customWidth="1"/>
+    <col min="11" max="16384" width="9.13636363636364" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="7"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="8" t="s">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7" t="s">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7" t="s">
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="9" t="s">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="10">
+      <c r="E5" s="8"/>
+      <c r="F5" s="9">
         <v>0.25</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9" t="s">
+      <c r="H5" s="8"/>
+      <c r="I5" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7" t="s">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="11">
+      <c r="E6" s="6"/>
+      <c r="F6" s="10">
         <v>0.25</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7" t="s">
+      <c r="H6" s="6"/>
+      <c r="I6" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7" t="s">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="10">
         <v>0.31</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7" t="s">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="10">
         <v>1</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7" t="s">
+      <c r="H8" s="6"/>
+      <c r="I8" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7" t="s">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="10">
         <v>1</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7" t="s">
+      <c r="H9" s="6"/>
+      <c r="I9" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7" t="s">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="10">
         <v>0.67</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7" t="s">
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7" t="s">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="11">
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="10">
         <v>0.8</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7" t="s">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7">
+      <c r="E12" s="6"/>
+      <c r="F12" s="6">
         <v>1.25</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="12" t="s">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12">
+      <c r="E13" s="11"/>
+      <c r="F13" s="11">
         <v>0.8</v>
       </c>
-      <c r="G13" s="12" t="s">
+      <c r="G13" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="H13" s="12" t="s">
+      <c r="H13" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="I13" s="12"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="8" t="s">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7" t="s">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7" t="s">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10014,1586 +10046,1586 @@
       </c>
     </row>
     <row r="47" ht="14.5" spans="3:37">
-      <c r="X47" s="5" t="s">
+      <c r="X47" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="Y47" s="5" t="s">
+      <c r="Y47" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="Z47" s="5">
+      <c r="Z47" s="1">
         <v>2019</v>
       </c>
-      <c r="AA47" s="5">
+      <c r="AA47" s="1">
         <v>2020</v>
       </c>
-      <c r="AB47" s="5">
+      <c r="AB47" s="1">
         <v>2023</v>
       </c>
-      <c r="AC47" s="5">
+      <c r="AC47" s="1">
         <v>2025</v>
       </c>
-      <c r="AD47" s="5">
+      <c r="AD47" s="1">
         <v>2030</v>
       </c>
-      <c r="AE47" s="5">
+      <c r="AE47" s="1">
         <v>2035</v>
       </c>
-      <c r="AF47" s="5">
+      <c r="AF47" s="1">
         <v>2040</v>
       </c>
-      <c r="AG47" s="5">
+      <c r="AG47" s="1">
         <v>2045</v>
       </c>
-      <c r="AH47" s="5">
+      <c r="AH47" s="1">
         <v>2050</v>
       </c>
-      <c r="AI47" s="5">
+      <c r="AI47" s="1">
         <v>2070</v>
       </c>
-      <c r="AJ47" s="5">
+      <c r="AJ47" s="1">
         <v>2090</v>
       </c>
-      <c r="AK47" s="5">
+      <c r="AK47" s="1">
         <v>2100</v>
       </c>
     </row>
     <row r="48" ht="14.5" spans="3:37">
-      <c r="X48" s="5" t="s">
+      <c r="X48" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="Y48" s="5" t="s">
+      <c r="Y48" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Z48" s="5">
+      <c r="Z48" s="1">
         <v>1015.12</v>
       </c>
-      <c r="AA48" s="5">
+      <c r="AA48" s="1">
         <v>1036.33</v>
       </c>
-      <c r="AB48" s="5">
+      <c r="AB48" s="1">
         <v>1125.42</v>
       </c>
-      <c r="AC48" s="5">
+      <c r="AC48" s="1">
         <v>1186.93</v>
       </c>
-      <c r="AD48" s="5">
+      <c r="AD48" s="1">
         <v>1349.51</v>
       </c>
-      <c r="AE48" s="5">
+      <c r="AE48" s="1">
         <v>1615.9</v>
       </c>
-      <c r="AF48" s="5">
+      <c r="AF48" s="1">
         <v>2106.97</v>
       </c>
-      <c r="AG48" s="5">
+      <c r="AG48" s="1">
         <v>2776.66</v>
       </c>
-      <c r="AH48" s="5">
+      <c r="AH48" s="1">
         <v>3579.56</v>
       </c>
-      <c r="AI48" s="5">
+      <c r="AI48" s="1">
         <v>6154.98</v>
       </c>
-      <c r="AJ48" s="5">
+      <c r="AJ48" s="1">
         <v>8131.8</v>
       </c>
-      <c r="AK48" s="5">
+      <c r="AK48" s="1">
         <v>8599.64</v>
       </c>
     </row>
     <row r="49" ht="14.5" spans="24:37">
-      <c r="X49" s="5" t="s">
+      <c r="X49" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="Y49" s="5" t="s">
+      <c r="Y49" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Z49" s="5">
+      <c r="Z49" s="1">
         <v>700.19</v>
       </c>
-      <c r="AA49" s="5">
+      <c r="AA49" s="1">
         <v>707.72</v>
       </c>
-      <c r="AB49" s="5">
+      <c r="AB49" s="1">
         <v>761.97</v>
       </c>
-      <c r="AC49" s="5">
+      <c r="AC49" s="1">
         <v>805.83</v>
       </c>
-      <c r="AD49" s="5">
+      <c r="AD49" s="1">
         <v>969.54</v>
       </c>
-      <c r="AE49" s="5">
+      <c r="AE49" s="1">
         <v>1229.86</v>
       </c>
-      <c r="AF49" s="5">
+      <c r="AF49" s="1">
         <v>1672.16</v>
       </c>
-      <c r="AG49" s="5">
+      <c r="AG49" s="1">
         <v>2304.13</v>
       </c>
-      <c r="AH49" s="5">
+      <c r="AH49" s="1">
         <v>3091.17</v>
       </c>
-      <c r="AI49" s="5">
+      <c r="AI49" s="1">
         <v>5797.91</v>
       </c>
-      <c r="AJ49" s="5">
+      <c r="AJ49" s="1">
         <v>8005.51</v>
       </c>
-      <c r="AK49" s="5">
+      <c r="AK49" s="1">
         <v>8541.77</v>
       </c>
     </row>
     <row r="50" ht="14.5" spans="24:37">
-      <c r="X50" s="5" t="s">
+      <c r="X50" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="Y50" s="5" t="s">
+      <c r="Y50" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Z50" s="5">
+      <c r="Z50" s="1">
         <v>810.91</v>
       </c>
-      <c r="AA50" s="5">
+      <c r="AA50" s="1">
         <v>802.4</v>
       </c>
-      <c r="AB50" s="5">
+      <c r="AB50" s="1">
         <v>813.02</v>
       </c>
-      <c r="AC50" s="5">
+      <c r="AC50" s="1">
         <v>820.1</v>
       </c>
-      <c r="AD50" s="5">
+      <c r="AD50" s="1">
         <v>844.51</v>
       </c>
-      <c r="AE50" s="5">
+      <c r="AE50" s="1">
         <v>885.83</v>
       </c>
-      <c r="AF50" s="5">
+      <c r="AF50" s="1">
         <v>964.1</v>
       </c>
-      <c r="AG50" s="5">
+      <c r="AG50" s="1">
         <v>1070.34</v>
       </c>
-      <c r="AH50" s="5">
+      <c r="AH50" s="1">
         <v>1191.29</v>
       </c>
-      <c r="AI50" s="5">
+      <c r="AI50" s="1">
         <v>1485.54</v>
       </c>
-      <c r="AJ50" s="5">
+      <c r="AJ50" s="1">
         <v>1675.77</v>
       </c>
-      <c r="AK50" s="5">
+      <c r="AK50" s="1">
         <v>1716.72</v>
       </c>
     </row>
     <row r="51" ht="14.5" spans="24:37">
-      <c r="X51" s="5" t="s">
+      <c r="X51" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="Y51" s="5" t="s">
+      <c r="Y51" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Z51" s="5">
+      <c r="Z51" s="1">
         <v>224.34</v>
       </c>
-      <c r="AA51" s="5">
+      <c r="AA51" s="1">
         <v>221.17</v>
       </c>
-      <c r="AB51" s="5">
+      <c r="AB51" s="1">
         <v>227.72</v>
       </c>
-      <c r="AC51" s="5">
+      <c r="AC51" s="1">
         <v>226.82</v>
       </c>
-      <c r="AD51" s="5">
+      <c r="AD51" s="1">
         <v>222.45</v>
       </c>
-      <c r="AE51" s="5">
+      <c r="AE51" s="1">
         <v>217.88</v>
       </c>
-      <c r="AF51" s="5">
+      <c r="AF51" s="1">
         <v>217.82</v>
       </c>
-      <c r="AG51" s="5">
+      <c r="AG51" s="1">
         <v>226.57</v>
       </c>
-      <c r="AH51" s="5">
+      <c r="AH51" s="1">
         <v>236.27</v>
       </c>
-      <c r="AI51" s="5">
+      <c r="AI51" s="1">
         <v>259.87</v>
       </c>
-      <c r="AJ51" s="5">
+      <c r="AJ51" s="1">
         <v>277.61</v>
       </c>
-      <c r="AK51" s="5">
+      <c r="AK51" s="1">
         <v>281.31</v>
       </c>
     </row>
     <row r="52" ht="14.5" spans="24:37">
-      <c r="X52" s="5" t="s">
+      <c r="X52" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="Y52" s="5" t="s">
+      <c r="Y52" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Z52" s="5">
+      <c r="Z52" s="1">
         <v>91.18</v>
       </c>
-      <c r="AA52" s="5">
+      <c r="AA52" s="1">
         <v>92.44</v>
       </c>
-      <c r="AB52" s="5">
+      <c r="AB52" s="1">
         <v>92</v>
       </c>
-      <c r="AC52" s="5">
+      <c r="AC52" s="1">
         <v>90.07</v>
       </c>
-      <c r="AD52" s="5">
+      <c r="AD52" s="1">
         <v>89.54</v>
       </c>
-      <c r="AE52" s="5">
+      <c r="AE52" s="1">
         <v>87.71</v>
       </c>
-      <c r="AF52" s="5">
+      <c r="AF52" s="1">
         <v>89.02</v>
       </c>
-      <c r="AG52" s="5">
+      <c r="AG52" s="1">
         <v>93.29</v>
       </c>
-      <c r="AH52" s="5">
+      <c r="AH52" s="1">
         <v>96.54</v>
       </c>
-      <c r="AI52" s="5">
+      <c r="AI52" s="1">
         <v>106.15</v>
       </c>
-      <c r="AJ52" s="5">
+      <c r="AJ52" s="1">
         <v>113.37</v>
       </c>
-      <c r="AK52" s="5">
+      <c r="AK52" s="1">
         <v>114.88</v>
       </c>
     </row>
     <row r="53" ht="14.5" spans="24:37">
-      <c r="X53" s="5" t="s">
+      <c r="X53" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="Y53" s="5" t="s">
+      <c r="Y53" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Z53" s="5">
+      <c r="Z53" s="1">
         <v>718.98</v>
       </c>
-      <c r="AA53" s="5">
+      <c r="AA53" s="1">
         <v>717.98</v>
       </c>
-      <c r="AB53" s="5">
+      <c r="AB53" s="1">
         <v>728.6</v>
       </c>
-      <c r="AC53" s="5">
+      <c r="AC53" s="1">
         <v>730.59</v>
       </c>
-      <c r="AD53" s="5">
+      <c r="AD53" s="1">
         <v>723.02</v>
       </c>
-      <c r="AE53" s="5">
+      <c r="AE53" s="1">
         <v>705.74</v>
       </c>
-      <c r="AF53" s="5">
+      <c r="AF53" s="1">
         <v>711.47</v>
       </c>
-      <c r="AG53" s="5">
+      <c r="AG53" s="1">
         <v>733.91</v>
       </c>
-      <c r="AH53" s="5">
+      <c r="AH53" s="1">
         <v>767.88</v>
       </c>
-      <c r="AI53" s="5">
+      <c r="AI53" s="1">
         <v>840.34</v>
       </c>
-      <c r="AJ53" s="5">
+      <c r="AJ53" s="1">
         <v>895.45</v>
       </c>
-      <c r="AK53" s="5">
+      <c r="AK53" s="1">
         <v>906.9</v>
       </c>
     </row>
     <row r="54" ht="14.5" spans="24:37">
-      <c r="X54" s="5" t="s">
+      <c r="X54" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="Y54" s="5" t="s">
+      <c r="Y54" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Z54" s="5">
+      <c r="Z54" s="1">
         <v>1889.35</v>
       </c>
-      <c r="AA54" s="5">
+      <c r="AA54" s="1">
         <v>1859.56</v>
       </c>
-      <c r="AB54" s="5">
+      <c r="AB54" s="1">
         <v>1980.49</v>
       </c>
-      <c r="AC54" s="5">
+      <c r="AC54" s="1">
         <v>2044.67</v>
       </c>
-      <c r="AD54" s="5">
+      <c r="AD54" s="1">
         <v>2077.79</v>
       </c>
-      <c r="AE54" s="5">
+      <c r="AE54" s="1">
         <v>2244.32</v>
       </c>
-      <c r="AF54" s="5">
+      <c r="AF54" s="1">
         <v>2677.68</v>
       </c>
-      <c r="AG54" s="5">
+      <c r="AG54" s="1">
         <v>3327.77</v>
       </c>
-      <c r="AH54" s="5">
+      <c r="AH54" s="1">
         <v>4085.59</v>
       </c>
-      <c r="AI54" s="5">
+      <c r="AI54" s="1">
         <v>6282.09</v>
       </c>
-      <c r="AJ54" s="5">
+      <c r="AJ54" s="1">
         <v>7827.71</v>
       </c>
-      <c r="AK54" s="5">
+      <c r="AK54" s="1">
         <v>8180.95</v>
       </c>
     </row>
     <row r="55" ht="14.5" spans="24:37">
-      <c r="X55" s="5" t="s">
+      <c r="X55" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="Y55" s="5" t="s">
+      <c r="Y55" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Z55" s="5">
+      <c r="Z55" s="1">
         <v>22703.29</v>
       </c>
-      <c r="AA55" s="5">
+      <c r="AA55" s="1">
         <v>23544.65</v>
       </c>
-      <c r="AB55" s="5">
+      <c r="AB55" s="1">
         <v>24259.55</v>
       </c>
-      <c r="AC55" s="5">
+      <c r="AC55" s="1">
         <v>24683.07</v>
       </c>
-      <c r="AD55" s="5">
+      <c r="AD55" s="1">
         <v>25213.46</v>
       </c>
-      <c r="AE55" s="5">
+      <c r="AE55" s="1">
         <v>24909.82</v>
       </c>
-      <c r="AF55" s="5">
+      <c r="AF55" s="1">
         <v>24971.51</v>
       </c>
-      <c r="AG55" s="5">
+      <c r="AG55" s="1">
         <v>25396.6</v>
       </c>
-      <c r="AH55" s="5">
+      <c r="AH55" s="1">
         <v>25817.58</v>
       </c>
-      <c r="AI55" s="5">
+      <c r="AI55" s="1">
         <v>26997.49</v>
       </c>
-      <c r="AJ55" s="5">
+      <c r="AJ55" s="1">
         <v>28020.51</v>
       </c>
-      <c r="AK55" s="5">
+      <c r="AK55" s="1">
         <v>28229.83</v>
       </c>
     </row>
     <row r="56" ht="14.5" spans="24:37">
-      <c r="X56" s="5" t="s">
+      <c r="X56" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="Y56" s="5" t="s">
+      <c r="Y56" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Z56" s="5">
+      <c r="Z56" s="1">
         <v>106.55</v>
       </c>
-      <c r="AA56" s="5">
+      <c r="AA56" s="1">
         <v>105.63</v>
       </c>
-      <c r="AB56" s="5">
+      <c r="AB56" s="1">
         <v>111.04</v>
       </c>
-      <c r="AC56" s="5">
+      <c r="AC56" s="1">
         <v>113.65</v>
       </c>
-      <c r="AD56" s="5">
+      <c r="AD56" s="1">
         <v>115.25</v>
       </c>
-      <c r="AE56" s="5">
+      <c r="AE56" s="1">
         <v>114.73</v>
       </c>
-      <c r="AF56" s="5">
+      <c r="AF56" s="1">
         <v>117.18</v>
       </c>
-      <c r="AG56" s="5">
+      <c r="AG56" s="1">
         <v>119.73</v>
       </c>
-      <c r="AH56" s="5">
+      <c r="AH56" s="1">
         <v>121.97</v>
       </c>
-      <c r="AI56" s="5">
+      <c r="AI56" s="1">
         <v>128.7</v>
       </c>
-      <c r="AJ56" s="5">
+      <c r="AJ56" s="1">
         <v>134.66</v>
       </c>
-      <c r="AK56" s="5">
+      <c r="AK56" s="1">
         <v>135.88</v>
       </c>
     </row>
     <row r="57" ht="14.5" spans="24:37">
-      <c r="X57" s="5" t="s">
+      <c r="X57" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="Y57" s="5" t="s">
+      <c r="Y57" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Z57" s="5">
+      <c r="Z57" s="1">
         <v>297.98</v>
       </c>
-      <c r="AA57" s="5">
+      <c r="AA57" s="1">
         <v>302.22</v>
       </c>
-      <c r="AB57" s="5">
+      <c r="AB57" s="1">
         <v>301.62</v>
       </c>
-      <c r="AC57" s="5">
+      <c r="AC57" s="1">
         <v>301.54</v>
       </c>
-      <c r="AD57" s="5">
+      <c r="AD57" s="1">
         <v>296.21</v>
       </c>
-      <c r="AE57" s="5">
+      <c r="AE57" s="1">
         <v>290.2</v>
       </c>
-      <c r="AF57" s="5">
+      <c r="AF57" s="1">
         <v>307.75</v>
       </c>
-      <c r="AG57" s="5">
+      <c r="AG57" s="1">
         <v>319.69</v>
       </c>
-      <c r="AH57" s="5">
+      <c r="AH57" s="1">
         <v>337.04</v>
       </c>
-      <c r="AI57" s="5">
+      <c r="AI57" s="1">
         <v>374.31</v>
       </c>
-      <c r="AJ57" s="5">
+      <c r="AJ57" s="1">
         <v>401.81</v>
       </c>
-      <c r="AK57" s="5">
+      <c r="AK57" s="1">
         <v>407.55</v>
       </c>
     </row>
     <row r="58" ht="14.5" spans="24:37">
-      <c r="X58" s="5" t="s">
+      <c r="X58" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="Y58" s="5" t="s">
+      <c r="Y58" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Z58" s="5">
+      <c r="Z58" s="1">
         <v>1521.04</v>
       </c>
-      <c r="AA58" s="5">
+      <c r="AA58" s="1">
         <v>1514.69</v>
       </c>
-      <c r="AB58" s="5">
+      <c r="AB58" s="1">
         <v>1541.02</v>
       </c>
-      <c r="AC58" s="5">
+      <c r="AC58" s="1">
         <v>1565.64</v>
       </c>
-      <c r="AD58" s="5">
+      <c r="AD58" s="1">
         <v>1497.74</v>
       </c>
-      <c r="AE58" s="5">
+      <c r="AE58" s="1">
         <v>1443.51</v>
       </c>
-      <c r="AF58" s="5">
+      <c r="AF58" s="1">
         <v>1430.72</v>
       </c>
-      <c r="AG58" s="5">
+      <c r="AG58" s="1">
         <v>1521.6</v>
       </c>
-      <c r="AH58" s="5">
+      <c r="AH58" s="1">
         <v>1643.33</v>
       </c>
-      <c r="AI58" s="5">
+      <c r="AI58" s="1">
         <v>1914.86</v>
       </c>
-      <c r="AJ58" s="5">
+      <c r="AJ58" s="1">
         <v>2105.7</v>
       </c>
-      <c r="AK58" s="5">
+      <c r="AK58" s="1">
         <v>2146.15</v>
       </c>
     </row>
     <row r="59" ht="14.5" spans="24:37">
-      <c r="X59" s="5" t="s">
+      <c r="X59" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="Y59" s="5" t="s">
+      <c r="Y59" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Z59" s="5">
+      <c r="Z59" s="1">
         <v>1749.2</v>
       </c>
-      <c r="AA59" s="5">
+      <c r="AA59" s="1">
         <v>1737.39</v>
       </c>
-      <c r="AB59" s="5">
+      <c r="AB59" s="1">
         <v>1737.22</v>
       </c>
-      <c r="AC59" s="5">
+      <c r="AC59" s="1">
         <v>1746.19</v>
       </c>
-      <c r="AD59" s="5">
+      <c r="AD59" s="1">
         <v>1671.67</v>
       </c>
-      <c r="AE59" s="5">
+      <c r="AE59" s="1">
         <v>1612.7</v>
       </c>
-      <c r="AF59" s="5">
+      <c r="AF59" s="1">
         <v>1658.71</v>
       </c>
-      <c r="AG59" s="5">
+      <c r="AG59" s="1">
         <v>1785.42</v>
       </c>
-      <c r="AH59" s="5">
+      <c r="AH59" s="1">
         <v>1843.56</v>
       </c>
-      <c r="AI59" s="5">
+      <c r="AI59" s="1">
         <v>2078.07</v>
       </c>
-      <c r="AJ59" s="5">
+      <c r="AJ59" s="1">
         <v>2247.43</v>
       </c>
-      <c r="AK59" s="5">
+      <c r="AK59" s="1">
         <v>2282.97</v>
       </c>
     </row>
     <row r="60" ht="14.5" spans="24:37">
-      <c r="X60" s="5" t="s">
+      <c r="X60" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="Y60" s="5" t="s">
+      <c r="Y60" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Z60" s="5">
+      <c r="Z60" s="1">
         <v>202.67</v>
       </c>
-      <c r="AA60" s="5">
+      <c r="AA60" s="1">
         <v>200.36</v>
       </c>
-      <c r="AB60" s="5">
+      <c r="AB60" s="1">
         <v>210.32</v>
       </c>
-      <c r="AC60" s="5">
+      <c r="AC60" s="1">
         <v>215.96</v>
       </c>
-      <c r="AD60" s="5">
+      <c r="AD60" s="1">
         <v>214.08</v>
       </c>
-      <c r="AE60" s="5">
+      <c r="AE60" s="1">
         <v>212.5</v>
       </c>
-      <c r="AF60" s="5">
+      <c r="AF60" s="1">
         <v>220.08</v>
       </c>
-      <c r="AG60" s="5">
+      <c r="AG60" s="1">
         <v>231.97</v>
       </c>
-      <c r="AH60" s="5">
+      <c r="AH60" s="1">
         <v>244.43</v>
       </c>
-      <c r="AI60" s="5">
+      <c r="AI60" s="1">
         <v>275.32</v>
       </c>
-      <c r="AJ60" s="5">
+      <c r="AJ60" s="1">
         <v>297.64</v>
       </c>
-      <c r="AK60" s="5">
+      <c r="AK60" s="1">
         <v>302.32</v>
       </c>
     </row>
     <row r="61" ht="14.5" spans="24:37">
-      <c r="X61" s="5" t="s">
+      <c r="X61" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="Y61" s="5" t="s">
+      <c r="Y61" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Z61" s="5">
+      <c r="Z61" s="1">
         <v>421.52</v>
       </c>
-      <c r="AA61" s="5">
+      <c r="AA61" s="1">
         <v>423.28</v>
       </c>
-      <c r="AB61" s="5">
+      <c r="AB61" s="1">
         <v>435.28</v>
       </c>
-      <c r="AC61" s="5">
+      <c r="AC61" s="1">
         <v>441.49</v>
       </c>
-      <c r="AD61" s="5">
+      <c r="AD61" s="1">
         <v>447.87</v>
       </c>
-      <c r="AE61" s="5">
+      <c r="AE61" s="1">
         <v>451.45</v>
       </c>
-      <c r="AF61" s="5">
+      <c r="AF61" s="1">
         <v>467.26</v>
       </c>
-      <c r="AG61" s="5">
+      <c r="AG61" s="1">
         <v>487.02</v>
       </c>
-      <c r="AH61" s="5">
+      <c r="AH61" s="1">
         <v>503.06</v>
       </c>
-      <c r="AI61" s="5">
+      <c r="AI61" s="1">
         <v>549.17</v>
       </c>
-      <c r="AJ61" s="5">
+      <c r="AJ61" s="1">
         <v>584.45</v>
       </c>
-      <c r="AK61" s="5">
+      <c r="AK61" s="1">
         <v>591.78</v>
       </c>
     </row>
     <row r="62" ht="14.5" spans="24:37">
-      <c r="X62" s="5" t="s">
+      <c r="X62" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="Y62" s="5" t="s">
+      <c r="Y62" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Z62" s="5">
+      <c r="Z62" s="1">
         <v>60.36</v>
       </c>
-      <c r="AA62" s="5">
+      <c r="AA62" s="1">
         <v>60.46</v>
       </c>
-      <c r="AB62" s="5">
+      <c r="AB62" s="1">
         <v>64.96</v>
       </c>
-      <c r="AC62" s="5">
+      <c r="AC62" s="1">
         <v>67.64</v>
       </c>
-      <c r="AD62" s="5">
+      <c r="AD62" s="1">
         <v>73.1</v>
       </c>
-      <c r="AE62" s="5">
+      <c r="AE62" s="1">
         <v>77.55</v>
       </c>
-      <c r="AF62" s="5">
+      <c r="AF62" s="1">
         <v>82.77</v>
       </c>
-      <c r="AG62" s="5">
+      <c r="AG62" s="1">
         <v>87.96</v>
       </c>
-      <c r="AH62" s="5">
+      <c r="AH62" s="1">
         <v>93.88</v>
       </c>
-      <c r="AI62" s="5">
+      <c r="AI62" s="1">
         <v>108.02</v>
       </c>
-      <c r="AJ62" s="5">
+      <c r="AJ62" s="1">
         <v>118.03</v>
       </c>
-      <c r="AK62" s="5">
+      <c r="AK62" s="1">
         <v>120.14</v>
       </c>
     </row>
     <row r="63" ht="14.5" spans="24:37">
-      <c r="X63" s="5" t="s">
+      <c r="X63" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="Y63" s="5" t="s">
+      <c r="Y63" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Z63" s="5">
+      <c r="Z63" s="1">
         <v>4501.03</v>
       </c>
-      <c r="AA63" s="5">
+      <c r="AA63" s="1">
         <v>4570.6</v>
       </c>
-      <c r="AB63" s="5">
+      <c r="AB63" s="1">
         <v>5487.58</v>
       </c>
-      <c r="AC63" s="5">
+      <c r="AC63" s="1">
         <v>6053.45</v>
       </c>
-      <c r="AD63" s="5">
+      <c r="AD63" s="1">
         <v>7542.66</v>
       </c>
-      <c r="AE63" s="5">
+      <c r="AE63" s="1">
         <v>9351.09</v>
       </c>
-      <c r="AF63" s="5">
+      <c r="AF63" s="1">
         <v>11757.3</v>
       </c>
-      <c r="AG63" s="5">
+      <c r="AG63" s="1">
         <v>14502.08</v>
       </c>
-      <c r="AH63" s="5">
+      <c r="AH63" s="1">
         <v>17634.77</v>
       </c>
-      <c r="AI63" s="5">
+      <c r="AI63" s="1">
         <v>26654.56</v>
       </c>
-      <c r="AJ63" s="5">
+      <c r="AJ63" s="1">
         <v>32938.65</v>
       </c>
-      <c r="AK63" s="5">
+      <c r="AK63" s="1">
         <v>34367.74</v>
       </c>
     </row>
     <row r="64" ht="14.5" spans="24:37">
-      <c r="X64" s="5" t="s">
+      <c r="X64" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="Y64" s="5" t="s">
+      <c r="Y64" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Z64" s="5">
+      <c r="Z64" s="1">
         <v>101.36</v>
       </c>
-      <c r="AA64" s="5">
+      <c r="AA64" s="1">
         <v>106.8</v>
       </c>
-      <c r="AB64" s="5">
+      <c r="AB64" s="1">
         <v>109.62</v>
       </c>
-      <c r="AC64" s="5">
+      <c r="AC64" s="1">
         <v>113.19</v>
       </c>
-      <c r="AD64" s="5">
+      <c r="AD64" s="1">
         <v>112.71</v>
       </c>
-      <c r="AE64" s="5">
+      <c r="AE64" s="1">
         <v>112.07</v>
       </c>
-      <c r="AF64" s="5">
+      <c r="AF64" s="1">
         <v>118</v>
       </c>
-      <c r="AG64" s="5">
+      <c r="AG64" s="1">
         <v>129.42</v>
       </c>
-      <c r="AH64" s="5">
+      <c r="AH64" s="1">
         <v>141.34</v>
       </c>
-      <c r="AI64" s="5">
+      <c r="AI64" s="1">
         <v>171.81</v>
       </c>
-      <c r="AJ64" s="5">
+      <c r="AJ64" s="1">
         <v>193</v>
       </c>
-      <c r="AK64" s="5">
+      <c r="AK64" s="1">
         <v>197.55</v>
       </c>
     </row>
     <row r="65" ht="14.5" spans="24:37">
-      <c r="X65" s="5" t="s">
+      <c r="X65" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="Y65" s="5" t="s">
+      <c r="Y65" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Z65" s="5">
+      <c r="Z65" s="1">
         <v>1013.79</v>
       </c>
-      <c r="AA65" s="5">
+      <c r="AA65" s="1">
         <v>1000.35</v>
       </c>
-      <c r="AB65" s="5">
+      <c r="AB65" s="1">
         <v>1012.9</v>
       </c>
-      <c r="AC65" s="5">
+      <c r="AC65" s="1">
         <v>1015.96</v>
       </c>
-      <c r="AD65" s="5">
+      <c r="AD65" s="1">
         <v>959.33</v>
       </c>
-      <c r="AE65" s="5">
+      <c r="AE65" s="1">
         <v>941.17</v>
       </c>
-      <c r="AF65" s="5">
+      <c r="AF65" s="1">
         <v>957.27</v>
       </c>
-      <c r="AG65" s="5">
+      <c r="AG65" s="1">
         <v>994.04</v>
       </c>
-      <c r="AH65" s="5">
+      <c r="AH65" s="1">
         <v>1045.1</v>
       </c>
-      <c r="AI65" s="5">
+      <c r="AI65" s="1">
         <v>1157.02</v>
       </c>
-      <c r="AJ65" s="5">
+      <c r="AJ65" s="1">
         <v>1240.05</v>
       </c>
-      <c r="AK65" s="5">
+      <c r="AK65" s="1">
         <v>1257.38</v>
       </c>
     </row>
     <row r="66" ht="14.5" spans="24:37">
-      <c r="X66" s="5" t="s">
+      <c r="X66" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="Y66" s="5" t="s">
+      <c r="Y66" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Z66" s="5">
+      <c r="Z66" s="1">
         <v>3272.23</v>
       </c>
-      <c r="AA66" s="5">
+      <c r="AA66" s="1">
         <v>3210.89</v>
       </c>
-      <c r="AB66" s="5">
+      <c r="AB66" s="1">
         <v>3237.72</v>
       </c>
-      <c r="AC66" s="5">
+      <c r="AC66" s="1">
         <v>3233.22</v>
       </c>
-      <c r="AD66" s="5">
+      <c r="AD66" s="1">
         <v>3197.84</v>
       </c>
-      <c r="AE66" s="5">
+      <c r="AE66" s="1">
         <v>3223.57</v>
       </c>
-      <c r="AF66" s="5">
+      <c r="AF66" s="1">
         <v>3408.01</v>
       </c>
-      <c r="AG66" s="5">
+      <c r="AG66" s="1">
         <v>3678.42</v>
       </c>
-      <c r="AH66" s="5">
+      <c r="AH66" s="1">
         <v>3950.87</v>
       </c>
-      <c r="AI66" s="5">
+      <c r="AI66" s="1">
         <v>4589.8</v>
       </c>
-      <c r="AJ66" s="5">
+      <c r="AJ66" s="1">
         <v>4956.61</v>
       </c>
-      <c r="AK66" s="5">
+      <c r="AK66" s="1">
         <v>5033.5</v>
       </c>
     </row>
     <row r="67" ht="14.5" spans="24:37">
-      <c r="X67" s="5" t="s">
+      <c r="X67" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="Y67" s="5" t="s">
+      <c r="Y67" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Z67" s="5">
+      <c r="Z67" s="1">
         <v>1881.22</v>
       </c>
-      <c r="AA67" s="5">
+      <c r="AA67" s="1">
         <v>1905.21</v>
       </c>
-      <c r="AB67" s="5">
+      <c r="AB67" s="1">
         <v>1995.04</v>
       </c>
-      <c r="AC67" s="5">
+      <c r="AC67" s="1">
         <v>2100.4</v>
       </c>
-      <c r="AD67" s="5">
+      <c r="AD67" s="1">
         <v>2323.91</v>
       </c>
-      <c r="AE67" s="5">
+      <c r="AE67" s="1">
         <v>2678.11</v>
       </c>
-      <c r="AF67" s="5">
+      <c r="AF67" s="1">
         <v>3220.88</v>
       </c>
-      <c r="AG67" s="5">
+      <c r="AG67" s="1">
         <v>3879.19</v>
       </c>
-      <c r="AH67" s="5">
+      <c r="AH67" s="1">
         <v>4637.71</v>
       </c>
-      <c r="AI67" s="5">
+      <c r="AI67" s="1">
         <v>6721.68</v>
       </c>
-      <c r="AJ67" s="5">
+      <c r="AJ67" s="1">
         <v>8129.04</v>
       </c>
-      <c r="AK67" s="5">
+      <c r="AK67" s="1">
         <v>8444.99</v>
       </c>
     </row>
     <row r="68" ht="14.5" spans="24:37">
-      <c r="X68" s="5" t="s">
+      <c r="X68" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="Y68" s="5" t="s">
+      <c r="Y68" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Z68" s="5">
+      <c r="Z68" s="1">
         <v>2674.06</v>
       </c>
-      <c r="AA68" s="5">
+      <c r="AA68" s="1">
         <v>2677.86</v>
       </c>
-      <c r="AB68" s="5">
+      <c r="AB68" s="1">
         <v>2848.42</v>
       </c>
-      <c r="AC68" s="5">
+      <c r="AC68" s="1">
         <v>2999.96</v>
       </c>
-      <c r="AD68" s="5">
+      <c r="AD68" s="1">
         <v>3271.9</v>
       </c>
-      <c r="AE68" s="5">
+      <c r="AE68" s="1">
         <v>3661.02</v>
       </c>
-      <c r="AF68" s="5">
+      <c r="AF68" s="1">
         <v>4346.88</v>
       </c>
-      <c r="AG68" s="5">
+      <c r="AG68" s="1">
         <v>5186.09</v>
       </c>
-      <c r="AH68" s="5">
+      <c r="AH68" s="1">
         <v>5945</v>
       </c>
-      <c r="AI68" s="5">
+      <c r="AI68" s="1">
         <v>8190.15</v>
       </c>
-      <c r="AJ68" s="5">
+      <c r="AJ68" s="1">
         <v>9673.68</v>
       </c>
-      <c r="AK68" s="5">
+      <c r="AK68" s="1">
         <v>10002.02</v>
       </c>
     </row>
     <row r="69" ht="14.5" spans="24:37">
-      <c r="X69" s="5" t="s">
+      <c r="X69" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="Y69" s="5" t="s">
+      <c r="Y69" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Z69" s="5">
+      <c r="Z69" s="1">
         <v>17129.98</v>
       </c>
-      <c r="AA69" s="5">
+      <c r="AA69" s="1">
         <v>17081.61</v>
       </c>
-      <c r="AB69" s="5">
+      <c r="AB69" s="1">
         <v>17243.56</v>
       </c>
-      <c r="AC69" s="5">
+      <c r="AC69" s="1">
         <v>17373.04</v>
       </c>
-      <c r="AD69" s="5">
+      <c r="AD69" s="1">
         <v>17101.89</v>
       </c>
-      <c r="AE69" s="5">
+      <c r="AE69" s="1">
         <v>17075.61</v>
       </c>
-      <c r="AF69" s="5">
+      <c r="AF69" s="1">
         <v>18025.89</v>
       </c>
-      <c r="AG69" s="5">
+      <c r="AG69" s="1">
         <v>19311.33</v>
       </c>
-      <c r="AH69" s="5">
+      <c r="AH69" s="1">
         <v>20573.33</v>
       </c>
-      <c r="AI69" s="5">
+      <c r="AI69" s="1">
         <v>23654.77</v>
       </c>
-      <c r="AJ69" s="5">
+      <c r="AJ69" s="1">
         <v>25584.24</v>
       </c>
-      <c r="AK69" s="5">
+      <c r="AK69" s="1">
         <v>25989.1</v>
       </c>
     </row>
     <row r="70" ht="14.5" spans="24:37">
-      <c r="X70" s="5" t="s">
+      <c r="X70" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="Y70" s="5" t="s">
+      <c r="Y70" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Z70" s="5">
+      <c r="Z70" s="1">
         <v>424.31</v>
       </c>
-      <c r="AA70" s="5">
+      <c r="AA70" s="1">
         <v>426.8</v>
       </c>
-      <c r="AB70" s="5">
+      <c r="AB70" s="1">
         <v>436.3</v>
       </c>
-      <c r="AC70" s="5">
+      <c r="AC70" s="1">
         <v>443.05</v>
       </c>
-      <c r="AD70" s="5">
+      <c r="AD70" s="1">
         <v>436.37</v>
       </c>
-      <c r="AE70" s="5">
+      <c r="AE70" s="1">
         <v>426</v>
       </c>
-      <c r="AF70" s="5">
+      <c r="AF70" s="1">
         <v>436.35</v>
       </c>
-      <c r="AG70" s="5">
+      <c r="AG70" s="1">
         <v>460.65</v>
       </c>
-      <c r="AH70" s="5">
+      <c r="AH70" s="1">
         <v>487.05</v>
       </c>
-      <c r="AI70" s="5">
+      <c r="AI70" s="1">
         <v>551.37</v>
       </c>
-      <c r="AJ70" s="5">
+      <c r="AJ70" s="1">
         <v>597.6</v>
       </c>
-      <c r="AK70" s="5">
+      <c r="AK70" s="1">
         <v>607.31</v>
       </c>
     </row>
     <row r="71" ht="14.5" spans="24:37">
-      <c r="X71" s="5" t="s">
+      <c r="X71" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="Y71" s="5" t="s">
+      <c r="Y71" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Z71" s="5">
+      <c r="Z71" s="1">
         <v>517.65</v>
       </c>
-      <c r="AA71" s="5">
+      <c r="AA71" s="1">
         <v>526.92</v>
       </c>
-      <c r="AB71" s="5">
+      <c r="AB71" s="1">
         <v>553.58</v>
       </c>
-      <c r="AC71" s="5">
+      <c r="AC71" s="1">
         <v>562.47</v>
       </c>
-      <c r="AD71" s="5">
+      <c r="AD71" s="1">
         <v>582.76</v>
       </c>
-      <c r="AE71" s="5">
+      <c r="AE71" s="1">
         <v>585.97</v>
       </c>
-      <c r="AF71" s="5">
+      <c r="AF71" s="1">
         <v>587.29</v>
       </c>
-      <c r="AG71" s="5">
+      <c r="AG71" s="1">
         <v>597.68</v>
       </c>
-      <c r="AH71" s="5">
+      <c r="AH71" s="1">
         <v>660.49</v>
       </c>
-      <c r="AI71" s="5">
+      <c r="AI71" s="1">
         <v>753.41</v>
       </c>
-      <c r="AJ71" s="5">
+      <c r="AJ71" s="1">
         <v>819.7</v>
       </c>
-      <c r="AK71" s="5">
+      <c r="AK71" s="1">
         <v>833.65</v>
       </c>
     </row>
     <row r="72" ht="14.5" spans="24:37">
-      <c r="X72" s="5" t="s">
+      <c r="X72" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="Y72" s="5" t="s">
+      <c r="Y72" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Z72" s="5">
+      <c r="Z72" s="1">
         <v>9216.02</v>
       </c>
-      <c r="AA72" s="5">
+      <c r="AA72" s="1">
         <v>9409.86</v>
       </c>
-      <c r="AB72" s="5">
+      <c r="AB72" s="1">
         <v>10099.94</v>
       </c>
-      <c r="AC72" s="5">
+      <c r="AC72" s="1">
         <v>10580.28</v>
       </c>
-      <c r="AD72" s="5">
+      <c r="AD72" s="1">
         <v>11919.93</v>
       </c>
-      <c r="AE72" s="5">
+      <c r="AE72" s="1">
         <v>13485.18</v>
       </c>
-      <c r="AF72" s="5">
+      <c r="AF72" s="1">
         <v>16074.17</v>
       </c>
-      <c r="AG72" s="5">
+      <c r="AG72" s="1">
         <v>19012.73</v>
       </c>
-      <c r="AH72" s="5">
+      <c r="AH72" s="1">
         <v>22105.59</v>
       </c>
-      <c r="AI72" s="5">
+      <c r="AI72" s="1">
         <v>30625.33</v>
       </c>
-      <c r="AJ72" s="5">
+      <c r="AJ72" s="1">
         <v>36275.22</v>
       </c>
-      <c r="AK72" s="5">
+      <c r="AK72" s="1">
         <v>37527.82</v>
       </c>
     </row>
     <row r="73" ht="14.5" spans="24:37">
-      <c r="X73" s="5" t="s">
+      <c r="X73" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="Y73" s="5" t="s">
+      <c r="Y73" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Z73" s="5">
+      <c r="Z73" s="1">
         <v>3014.47</v>
       </c>
-      <c r="AA73" s="5">
+      <c r="AA73" s="1">
         <v>3009</v>
       </c>
-      <c r="AB73" s="5">
+      <c r="AB73" s="1">
         <v>2845.06</v>
       </c>
-      <c r="AC73" s="5">
+      <c r="AC73" s="1">
         <v>2832.04</v>
       </c>
-      <c r="AD73" s="5">
+      <c r="AD73" s="1">
         <v>2966.04</v>
       </c>
-      <c r="AE73" s="5">
+      <c r="AE73" s="1">
         <v>3004.56</v>
       </c>
-      <c r="AF73" s="5">
+      <c r="AF73" s="1">
         <v>3190.54</v>
       </c>
-      <c r="AG73" s="5">
+      <c r="AG73" s="1">
         <v>3413.8</v>
       </c>
-      <c r="AH73" s="5">
+      <c r="AH73" s="1">
         <v>3654.97</v>
       </c>
-      <c r="AI73" s="5">
+      <c r="AI73" s="1">
         <v>4208.67</v>
       </c>
-      <c r="AJ73" s="5">
+      <c r="AJ73" s="1">
         <v>4542.23</v>
       </c>
-      <c r="AK73" s="5">
+      <c r="AK73" s="1">
         <v>4612.13</v>
       </c>
     </row>
     <row r="74" ht="14.5" spans="24:37">
-      <c r="X74" s="5" t="s">
+      <c r="X74" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="Y74" s="5" t="s">
+      <c r="Y74" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Z74" s="5">
+      <c r="Z74" s="1">
         <v>1127.43</v>
       </c>
-      <c r="AA74" s="5">
+      <c r="AA74" s="1">
         <v>1114.3</v>
       </c>
-      <c r="AB74" s="5">
+      <c r="AB74" s="1">
         <v>1140.25</v>
       </c>
-      <c r="AC74" s="5">
+      <c r="AC74" s="1">
         <v>1149.5</v>
       </c>
-      <c r="AD74" s="5">
+      <c r="AD74" s="1">
         <v>1210.35</v>
       </c>
-      <c r="AE74" s="5">
+      <c r="AE74" s="1">
         <v>1261.76</v>
       </c>
-      <c r="AF74" s="5">
+      <c r="AF74" s="1">
         <v>1396.75</v>
       </c>
-      <c r="AG74" s="5">
+      <c r="AG74" s="1">
         <v>1499.64</v>
       </c>
-      <c r="AH74" s="5">
+      <c r="AH74" s="1">
         <v>1653.59</v>
       </c>
-      <c r="AI74" s="5">
+      <c r="AI74" s="1">
         <v>1968.32</v>
       </c>
-      <c r="AJ74" s="5">
+      <c r="AJ74" s="1">
         <v>2160</v>
       </c>
-      <c r="AK74" s="5">
+      <c r="AK74" s="1">
         <v>2200.58</v>
       </c>
     </row>
     <row r="75" ht="14.5" spans="24:37">
-      <c r="X75" s="5" t="s">
+      <c r="X75" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="Y75" s="5" t="s">
+      <c r="Y75" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Z75" s="5">
+      <c r="Z75" s="1">
         <v>688.06</v>
       </c>
-      <c r="AA75" s="5">
+      <c r="AA75" s="1">
         <v>680.93</v>
       </c>
-      <c r="AB75" s="5">
+      <c r="AB75" s="1">
         <v>670.07</v>
       </c>
-      <c r="AC75" s="5">
+      <c r="AC75" s="1">
         <v>666.5</v>
       </c>
-      <c r="AD75" s="5">
+      <c r="AD75" s="1">
         <v>671.66</v>
       </c>
-      <c r="AE75" s="5">
+      <c r="AE75" s="1">
         <v>721.92</v>
       </c>
-      <c r="AF75" s="5">
+      <c r="AF75" s="1">
         <v>847.55</v>
       </c>
-      <c r="AG75" s="5">
+      <c r="AG75" s="1">
         <v>1016.42</v>
       </c>
-      <c r="AH75" s="5">
+      <c r="AH75" s="1">
         <v>1221.99</v>
       </c>
-      <c r="AI75" s="5">
+      <c r="AI75" s="1">
         <v>1776.39</v>
       </c>
-      <c r="AJ75" s="5">
+      <c r="AJ75" s="1">
         <v>2155.8</v>
       </c>
-      <c r="AK75" s="5">
+      <c r="AK75" s="1">
         <v>2241.16</v>
       </c>
     </row>
     <row r="76" ht="14.5" spans="24:37">
-      <c r="X76" s="5" t="s">
+      <c r="X76" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="Y76" s="5" t="s">
+      <c r="Y76" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Z76" s="5">
+      <c r="Z76" s="1">
         <v>1010.08</v>
       </c>
-      <c r="AA76" s="5">
+      <c r="AA76" s="1">
         <v>1006.51</v>
       </c>
-      <c r="AB76" s="5">
+      <c r="AB76" s="1">
         <v>1030.81</v>
       </c>
-      <c r="AC76" s="5">
+      <c r="AC76" s="1">
         <v>1047.56</v>
       </c>
-      <c r="AD76" s="5">
+      <c r="AD76" s="1">
         <v>994.53</v>
       </c>
-      <c r="AE76" s="5">
+      <c r="AE76" s="1">
         <v>982.8</v>
       </c>
-      <c r="AF76" s="5">
+      <c r="AF76" s="1">
         <v>1026.29</v>
       </c>
-      <c r="AG76" s="5">
+      <c r="AG76" s="1">
         <v>1101.09</v>
       </c>
-      <c r="AH76" s="5">
+      <c r="AH76" s="1">
         <v>1190.72</v>
       </c>
-      <c r="AI76" s="5">
+      <c r="AI76" s="1">
         <v>1401.63</v>
       </c>
-      <c r="AJ76" s="5">
+      <c r="AJ76" s="1">
         <v>1549.21</v>
       </c>
-      <c r="AK76" s="5">
+      <c r="AK76" s="1">
         <v>1580.59</v>
       </c>
     </row>
     <row r="77" ht="14.5" spans="24:37">
-      <c r="X77" s="5" t="s">
+      <c r="X77" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="Y77" s="5" t="s">
+      <c r="Y77" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Z77" s="5">
+      <c r="Z77" s="1">
         <v>835.8</v>
       </c>
-      <c r="AA77" s="5">
+      <c r="AA77" s="1">
         <v>837.12</v>
       </c>
-      <c r="AB77" s="5">
+      <c r="AB77" s="1">
         <v>832.69</v>
       </c>
-      <c r="AC77" s="5">
+      <c r="AC77" s="1">
         <v>830.09</v>
       </c>
-      <c r="AD77" s="5">
+      <c r="AD77" s="1">
         <v>834.01</v>
       </c>
-      <c r="AE77" s="5">
+      <c r="AE77" s="1">
         <v>836.14</v>
       </c>
-      <c r="AF77" s="5">
+      <c r="AF77" s="1">
         <v>857.22</v>
       </c>
-      <c r="AG77" s="5">
+      <c r="AG77" s="1">
         <v>890.78</v>
       </c>
-      <c r="AH77" s="5">
+      <c r="AH77" s="1">
         <v>930.11</v>
       </c>
-      <c r="AI77" s="5">
+      <c r="AI77" s="1">
         <v>1023.33</v>
       </c>
-      <c r="AJ77" s="5">
+      <c r="AJ77" s="1">
         <v>1093.35</v>
       </c>
-      <c r="AK77" s="5">
+      <c r="AK77" s="1">
         <v>1107.93</v>
       </c>
     </row>
     <row r="78" ht="14.5" spans="24:37">
-      <c r="X78" s="5" t="s">
+      <c r="X78" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="Y78" s="5" t="s">
+      <c r="Y78" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Z78" s="5">
+      <c r="Z78" s="1">
         <v>191.15</v>
       </c>
-      <c r="AA78" s="5">
+      <c r="AA78" s="1">
         <v>190.02</v>
       </c>
-      <c r="AB78" s="5">
+      <c r="AB78" s="1">
         <v>189.91</v>
       </c>
-      <c r="AC78" s="5">
+      <c r="AC78" s="1">
         <v>189.53</v>
       </c>
-      <c r="AD78" s="5">
+      <c r="AD78" s="1">
         <v>182.78</v>
       </c>
-      <c r="AE78" s="5">
+      <c r="AE78" s="1">
         <v>185.28</v>
       </c>
-      <c r="AF78" s="5">
+      <c r="AF78" s="1">
         <v>183.38</v>
       </c>
-      <c r="AG78" s="5">
+      <c r="AG78" s="1">
         <v>189.39</v>
       </c>
-      <c r="AH78" s="5">
+      <c r="AH78" s="1">
         <v>200.61</v>
       </c>
-      <c r="AI78" s="5">
+      <c r="AI78" s="1">
         <v>222.54</v>
       </c>
-      <c r="AJ78" s="5">
+      <c r="AJ78" s="1">
         <v>238.76</v>
       </c>
-      <c r="AK78" s="5">
+      <c r="AK78" s="1">
         <v>242.14</v>
       </c>
     </row>
     <row r="79" ht="14.5" spans="24:37">
-      <c r="X79" s="5" t="s">
+      <c r="X79" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="Y79" s="5" t="s">
+      <c r="Y79" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Z79" s="5">
+      <c r="Z79" s="1">
         <v>901.64</v>
       </c>
-      <c r="AA79" s="5">
+      <c r="AA79" s="1">
         <v>918.46</v>
       </c>
-      <c r="AB79" s="5">
+      <c r="AB79" s="1">
         <v>989.77</v>
       </c>
-      <c r="AC79" s="5">
+      <c r="AC79" s="1">
         <v>1028.85</v>
       </c>
-      <c r="AD79" s="5">
+      <c r="AD79" s="1">
         <v>1057.9</v>
       </c>
-      <c r="AE79" s="5">
+      <c r="AE79" s="1">
         <v>1076.4</v>
       </c>
-      <c r="AF79" s="5">
+      <c r="AF79" s="1">
         <v>1134.49</v>
       </c>
-      <c r="AG79" s="5">
+      <c r="AG79" s="1">
         <v>1191.37</v>
       </c>
-      <c r="AH79" s="5">
+      <c r="AH79" s="1">
         <v>1252.46</v>
       </c>
-      <c r="AI79" s="5">
+      <c r="AI79" s="1">
         <v>1402.23</v>
       </c>
-      <c r="AJ79" s="5">
+      <c r="AJ79" s="1">
         <v>1511.35</v>
       </c>
-      <c r="AK79" s="5">
+      <c r="AK79" s="1">
         <v>1534.2</v>
       </c>
     </row>
     <row r="80" ht="14.5" spans="24:37">
-      <c r="X80" s="5" t="s">
+      <c r="X80" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="Y80" s="5" t="s">
+      <c r="Y80" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Z80" s="5">
+      <c r="Z80" s="1">
         <v>1057.9</v>
       </c>
-      <c r="AA80" s="5">
+      <c r="AA80" s="1">
         <v>1050.82</v>
       </c>
-      <c r="AB80" s="5">
+      <c r="AB80" s="1">
         <v>1062.56</v>
       </c>
-      <c r="AC80" s="5">
+      <c r="AC80" s="1">
         <v>1085.73</v>
       </c>
-      <c r="AD80" s="5">
+      <c r="AD80" s="1">
         <v>1063.22</v>
       </c>
-      <c r="AE80" s="5">
+      <c r="AE80" s="1">
         <v>1043.87</v>
       </c>
-      <c r="AF80" s="5">
+      <c r="AF80" s="1">
         <v>1092.82</v>
       </c>
-      <c r="AG80" s="5">
+      <c r="AG80" s="1">
         <v>1194.6</v>
       </c>
-      <c r="AH80" s="5">
+      <c r="AH80" s="1">
         <v>1311.24</v>
       </c>
-      <c r="AI80" s="5">
+      <c r="AI80" s="1">
         <v>1596.81</v>
       </c>
-      <c r="AJ80" s="5">
+      <c r="AJ80" s="1">
         <v>1795.32</v>
       </c>
-      <c r="AK80" s="5">
+      <c r="AK80" s="1">
         <v>1837.97</v>
       </c>
     </row>
     <row r="81" ht="14.5" spans="24:37">
-      <c r="X81" s="5" t="s">
+      <c r="X81" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="Y81" s="5" t="s">
+      <c r="Y81" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Z81" s="5">
+      <c r="Z81" s="1">
         <v>421.75</v>
       </c>
-      <c r="AA81" s="5">
+      <c r="AA81" s="1">
         <v>430.44</v>
       </c>
-      <c r="AB81" s="5">
+      <c r="AB81" s="1">
         <v>380.11</v>
       </c>
-      <c r="AC81" s="5">
+      <c r="AC81" s="1">
         <v>349.29</v>
       </c>
-      <c r="AD81" s="5">
+      <c r="AD81" s="1">
         <v>394.59</v>
       </c>
-      <c r="AE81" s="5">
+      <c r="AE81" s="1">
         <v>460.86</v>
       </c>
-      <c r="AF81" s="5">
+      <c r="AF81" s="1">
         <v>560.99</v>
       </c>
-      <c r="AG81" s="5">
+      <c r="AG81" s="1">
         <v>644.7</v>
       </c>
-      <c r="AH81" s="5">
+      <c r="AH81" s="1">
         <v>747.52</v>
       </c>
-      <c r="AI81" s="5">
+      <c r="AI81" s="1">
         <v>1012.46</v>
       </c>
-      <c r="AJ81" s="5">
+      <c r="AJ81" s="1">
         <v>1200.95</v>
       </c>
-      <c r="AK81" s="5">
+      <c r="AK81" s="1">
         <v>1242.77</v>
       </c>
     </row>
     <row r="82" ht="14.5" spans="24:37">
-      <c r="X82" s="5" t="s">
+      <c r="X82" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="Y82" s="5" t="s">
+      <c r="Y82" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Z82" s="5">
+      <c r="Z82" s="1">
         <v>220.08</v>
       </c>
-      <c r="AA82" s="5">
+      <c r="AA82" s="1">
         <v>216.72</v>
       </c>
-      <c r="AB82" s="5">
+      <c r="AB82" s="1">
         <v>236.26</v>
       </c>
-      <c r="AC82" s="5">
+      <c r="AC82" s="1">
         <v>245.88</v>
       </c>
-      <c r="AD82" s="5">
+      <c r="AD82" s="1">
         <v>276.22</v>
       </c>
-      <c r="AE82" s="5">
+      <c r="AE82" s="1">
         <v>311.08</v>
       </c>
-      <c r="AF82" s="5">
+      <c r="AF82" s="1">
         <v>357.41</v>
       </c>
-      <c r="AG82" s="5">
+      <c r="AG82" s="1">
         <v>404.37</v>
       </c>
-      <c r="AH82" s="5">
+      <c r="AH82" s="1">
         <v>447.59</v>
       </c>
-      <c r="AI82" s="5">
+      <c r="AI82" s="1">
         <v>569.21</v>
       </c>
-      <c r="AJ82" s="5">
+      <c r="AJ82" s="1">
         <v>654.08</v>
       </c>
-      <c r="AK82" s="5">
+      <c r="AK82" s="1">
         <v>672.56</v>
       </c>
     </row>
